--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="F14" t="n">
-        <v>7.15</v>
+        <v>8.08</v>
       </c>
       <c r="G14" t="n">
-        <v>88.3</v>
+        <v>82.8</v>
       </c>
       <c r="H14" t="n">
-        <v>42.8</v>
+        <v>45.9</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>35.85</v>
+        <v>-17.74</v>
       </c>
       <c r="K14" t="n">
-        <v>-58.54</v>
+        <v>59.27</v>
       </c>
       <c r="L14" t="n">
-        <v>68.65000000000001</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:35:14</t>
+          <t>06:33:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="F15" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="G15" t="n">
-        <v>74.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="H15" t="n">
-        <v>45.6</v>
+        <v>42</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>9.52</v>
+        <v>138.86</v>
       </c>
       <c r="K15" t="n">
-        <v>64.8</v>
+        <v>-42.58</v>
       </c>
       <c r="L15" t="n">
-        <v>65.5</v>
+        <v>145.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:36:16</t>
+          <t>06:36:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="F16" t="n">
-        <v>7.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>79.7</v>
+        <v>58.5</v>
       </c>
       <c r="H16" t="n">
-        <v>47</v>
+        <v>41.7</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>21.88</v>
+        <v>-0.64</v>
       </c>
       <c r="K16" t="n">
-        <v>9.17</v>
+        <v>-59.59</v>
       </c>
       <c r="L16" t="n">
-        <v>23.73</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:40:19</t>
+          <t>06:41:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="F17" t="n">
-        <v>7.77</v>
+        <v>7.32</v>
       </c>
       <c r="G17" t="n">
-        <v>73.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-58.21</v>
+        <v>-151.53</v>
       </c>
       <c r="K17" t="n">
-        <v>7.72</v>
+        <v>-44.37</v>
       </c>
       <c r="L17" t="n">
-        <v>58.72</v>
+        <v>157.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:41:24</t>
+          <t>06:42:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="F18" t="n">
-        <v>8.029999999999999</v>
+        <v>7.34</v>
       </c>
       <c r="G18" t="n">
-        <v>83.8</v>
+        <v>73.5</v>
       </c>
       <c r="H18" t="n">
-        <v>41.4</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>282.01</v>
+        <v>155.96</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.31</v>
+        <v>-48.65</v>
       </c>
       <c r="L18" t="n">
-        <v>282.81</v>
+        <v>163.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:42:32</t>
+          <t>06:43:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="F19" t="n">
-        <v>8.31</v>
+        <v>6.89</v>
       </c>
       <c r="G19" t="n">
-        <v>72.8</v>
+        <v>77.8</v>
       </c>
       <c r="H19" t="n">
-        <v>49.2</v>
+        <v>52.2</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>34.1</v>
+        <v>151.13</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.01</v>
+        <v>-25.81</v>
       </c>
       <c r="L19" t="n">
-        <v>36.86</v>
+        <v>153.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:48:11</t>
+          <t>06:48:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.13</v>
+        <v>2.52</v>
       </c>
       <c r="F20" t="n">
-        <v>7.02</v>
+        <v>6.9</v>
       </c>
       <c r="G20" t="n">
-        <v>71.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="H20" t="n">
-        <v>56.6</v>
+        <v>40</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>78.15000000000001</v>
+        <v>218.47</v>
       </c>
       <c r="K20" t="n">
-        <v>99.23999999999999</v>
+        <v>-307.18</v>
       </c>
       <c r="L20" t="n">
-        <v>126.31</v>
+        <v>376.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:50:04</t>
+          <t>06:50:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="F21" t="n">
-        <v>7.12</v>
+        <v>7.98</v>
       </c>
       <c r="G21" t="n">
-        <v>66.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>43.4</v>
+        <v>44.4</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>8.44</v>
+        <v>34.38</v>
       </c>
       <c r="K21" t="n">
-        <v>90.34</v>
+        <v>70.48</v>
       </c>
       <c r="L21" t="n">
-        <v>90.73</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:51:44</t>
+          <t>06:51:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="F22" t="n">
-        <v>7.75</v>
+        <v>8.07</v>
       </c>
       <c r="G22" t="n">
-        <v>78.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>46.6</v>
+        <v>41.5</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>56.31</v>
+        <v>-21.57</v>
       </c>
       <c r="K22" t="n">
-        <v>74.79000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>93.62</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:56:35</t>
+          <t>06:56:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="n">
-        <v>7.03</v>
+        <v>7.57</v>
       </c>
       <c r="G23" t="n">
-        <v>62.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>44.5</v>
+        <v>45.7</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-22.55</v>
+        <v>-31.09</v>
       </c>
       <c r="K23" t="n">
-        <v>207.16</v>
+        <v>29.26</v>
       </c>
       <c r="L23" t="n">
-        <v>208.39</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:59:03</t>
+          <t>06:57:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="F24" t="n">
-        <v>7.37</v>
+        <v>7.67</v>
       </c>
       <c r="G24" t="n">
-        <v>70.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="H24" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>93.34</v>
+        <v>-321.57</v>
       </c>
       <c r="K24" t="n">
-        <v>-64.31</v>
+        <v>41.93</v>
       </c>
       <c r="L24" t="n">
-        <v>113.35</v>
+        <v>324.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:00:22</t>
+          <t>06:59:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="F25" t="n">
-        <v>7.58</v>
+        <v>7.09</v>
       </c>
       <c r="G25" t="n">
-        <v>74</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>43.7</v>
+        <v>45.2</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>106.77</v>
+        <v>-227.39</v>
       </c>
       <c r="K25" t="n">
-        <v>-323.34</v>
+        <v>321.9</v>
       </c>
       <c r="L25" t="n">
-        <v>340.51</v>
+        <v>394.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:04:49</t>
+          <t>07:04:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="F26" t="n">
-        <v>7.63</v>
+        <v>7.51</v>
       </c>
       <c r="G26" t="n">
-        <v>85.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>49.9</v>
+        <v>44.3</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-233.21</v>
+        <v>399.49</v>
       </c>
       <c r="K26" t="n">
-        <v>-308.68</v>
+        <v>-216.64</v>
       </c>
       <c r="L26" t="n">
-        <v>386.87</v>
+        <v>454.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:05:35</t>
+          <t>07:06:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="F27" t="n">
-        <v>7.42</v>
+        <v>8.02</v>
       </c>
       <c r="G27" t="n">
-        <v>62.1</v>
+        <v>83</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-172.56</v>
+        <v>-16.38</v>
       </c>
       <c r="K27" t="n">
-        <v>190.16</v>
+        <v>274.67</v>
       </c>
       <c r="L27" t="n">
-        <v>256.79</v>
+        <v>275.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:07:46</t>
+          <t>07:09:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="F28" t="n">
-        <v>8.050000000000001</v>
+        <v>7.12</v>
       </c>
       <c r="G28" t="n">
-        <v>64.5</v>
+        <v>82.3</v>
       </c>
       <c r="H28" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>149.13</v>
+        <v>199.86</v>
       </c>
       <c r="K28" t="n">
-        <v>104.54</v>
+        <v>314.94</v>
       </c>
       <c r="L28" t="n">
-        <v>182.12</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:20:12</t>
+          <t>07:17:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.16</v>
+        <v>2.57</v>
       </c>
       <c r="F29" t="n">
-        <v>7.58</v>
+        <v>7.38</v>
       </c>
       <c r="G29" t="n">
-        <v>82.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="H29" t="n">
-        <v>46.6</v>
+        <v>43.8</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>27.21</v>
+        <v>-152.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-46.19</v>
+        <v>148.93</v>
       </c>
       <c r="L29" t="n">
-        <v>53.61</v>
+        <v>213.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:22:33</t>
+          <t>07:19:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="F30" t="n">
-        <v>7.16</v>
+        <v>7.5</v>
       </c>
       <c r="G30" t="n">
-        <v>74.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="H30" t="n">
-        <v>44.6</v>
+        <v>49.8</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>31.63</v>
+        <v>-34.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-183.46</v>
+        <v>222.22</v>
       </c>
       <c r="L30" t="n">
-        <v>186.17</v>
+        <v>224.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:23:13</t>
+          <t>07:20:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="F31" t="n">
-        <v>7.53</v>
+        <v>7.34</v>
       </c>
       <c r="G31" t="n">
-        <v>71.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H31" t="n">
-        <v>50.2</v>
+        <v>41.9</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>51.71</v>
+        <v>106.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-129.09</v>
+        <v>38.07</v>
       </c>
       <c r="L31" t="n">
-        <v>139.06</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:27:26</t>
+          <t>07:25:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="F32" t="n">
-        <v>7.38</v>
+        <v>7.42</v>
       </c>
       <c r="G32" t="n">
-        <v>79.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>52.9</v>
+        <v>45.7</v>
       </c>
       <c r="I32" t="n">
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-106.3</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>85.78</v>
+        <v>-93.7</v>
       </c>
       <c r="L32" t="n">
-        <v>136.59</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:28:59</t>
+          <t>07:25:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="F33" t="n">
-        <v>7.82</v>
+        <v>7.5</v>
       </c>
       <c r="G33" t="n">
-        <v>69.7</v>
+        <v>78.2</v>
       </c>
       <c r="H33" t="n">
-        <v>47</v>
+        <v>43.6</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.52</v>
+        <v>-77.54000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-38.31</v>
+        <v>-31.95</v>
       </c>
       <c r="L33" t="n">
-        <v>38.39</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:30:07</t>
+          <t>07:27:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="F34" t="n">
-        <v>7.99</v>
+        <v>7.64</v>
       </c>
       <c r="G34" t="n">
-        <v>81.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>54.1</v>
+        <v>42</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>63.09</v>
+        <v>-205</v>
       </c>
       <c r="K34" t="n">
-        <v>-84.77</v>
+        <v>31.63</v>
       </c>
       <c r="L34" t="n">
-        <v>105.67</v>
+        <v>207.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:35:21</t>
+          <t>07:32:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="F35" t="n">
-        <v>8.029999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G35" t="n">
-        <v>74.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>45.2</v>
+        <v>44.2</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>156.53</v>
+        <v>-222.01</v>
       </c>
       <c r="K35" t="n">
-        <v>102.64</v>
+        <v>125.16</v>
       </c>
       <c r="L35" t="n">
-        <v>187.18</v>
+        <v>254.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:36:54</t>
+          <t>07:33:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="F36" t="n">
-        <v>7.96</v>
+        <v>7.87</v>
       </c>
       <c r="G36" t="n">
-        <v>79.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>46.6</v>
+        <v>39.7</v>
       </c>
       <c r="I36" t="n">
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-79.34999999999999</v>
+        <v>27.33</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.86</v>
+        <v>-38.98</v>
       </c>
       <c r="L36" t="n">
-        <v>85.51000000000001</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:37:35</t>
+          <t>07:34:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="F37" t="n">
-        <v>7.49</v>
+        <v>7.99</v>
       </c>
       <c r="G37" t="n">
-        <v>74.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>44.3</v>
+        <v>55.9</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-209.42</v>
+        <v>-174.39</v>
       </c>
       <c r="K37" t="n">
-        <v>-52.5</v>
+        <v>97.61</v>
       </c>
       <c r="L37" t="n">
-        <v>215.9</v>
+        <v>199.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:42:59</t>
+          <t>07:38:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="F38" t="n">
-        <v>7.51</v>
+        <v>7.63</v>
       </c>
       <c r="G38" t="n">
-        <v>62</v>
+        <v>83.3</v>
       </c>
       <c r="H38" t="n">
-        <v>49</v>
+        <v>46.8</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-242.8</v>
+        <v>246.55</v>
       </c>
       <c r="K38" t="n">
-        <v>25.01</v>
+        <v>123.03</v>
       </c>
       <c r="L38" t="n">
-        <v>244.09</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:44:30</t>
+          <t>07:40:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="F39" t="n">
-        <v>7.35</v>
+        <v>7.91</v>
       </c>
       <c r="G39" t="n">
-        <v>52.1</v>
+        <v>68.7</v>
       </c>
       <c r="H39" t="n">
-        <v>44.5</v>
+        <v>43.6</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-22.92</v>
+        <v>-14.36</v>
       </c>
       <c r="K39" t="n">
-        <v>-494.71</v>
+        <v>320.4</v>
       </c>
       <c r="L39" t="n">
-        <v>495.24</v>
+        <v>320.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:45:57</t>
+          <t>07:41:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.49</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="G40" t="n">
-        <v>63.4</v>
+        <v>73.2</v>
       </c>
       <c r="H40" t="n">
-        <v>47.8</v>
+        <v>52.2</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-56.01</v>
+        <v>-215.9</v>
       </c>
       <c r="K40" t="n">
-        <v>-360.97</v>
+        <v>-406.69</v>
       </c>
       <c r="L40" t="n">
-        <v>365.29</v>
+        <v>460.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:51:20</t>
+          <t>07:45:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.09</v>
+        <v>2.59</v>
       </c>
       <c r="F41" t="n">
-        <v>7.49</v>
+        <v>7.8</v>
       </c>
       <c r="G41" t="n">
-        <v>78.7</v>
+        <v>63.6</v>
       </c>
       <c r="H41" t="n">
-        <v>43.5</v>
+        <v>41.6</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>84.52</v>
+        <v>64.8</v>
       </c>
       <c r="K41" t="n">
-        <v>508.77</v>
+        <v>227.95</v>
       </c>
       <c r="L41" t="n">
-        <v>515.74</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:52:54</t>
+          <t>07:47:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.86</v>
+        <v>1.99</v>
       </c>
       <c r="F42" t="n">
-        <v>6.98</v>
+        <v>7.65</v>
       </c>
       <c r="G42" t="n">
-        <v>69.7</v>
+        <v>58.5</v>
       </c>
       <c r="H42" t="n">
-        <v>45.8</v>
+        <v>41.6</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-301.59</v>
+        <v>-358.64</v>
       </c>
       <c r="K42" t="n">
-        <v>-403.49</v>
+        <v>-140.72</v>
       </c>
       <c r="L42" t="n">
-        <v>503.75</v>
+        <v>385.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:55:13</t>
+          <t>07:48:13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="F43" t="n">
-        <v>7.4</v>
+        <v>8.06</v>
       </c>
       <c r="G43" t="n">
-        <v>58.8</v>
+        <v>79.7</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9</v>
+        <v>49.5</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>358.65</v>
+        <v>130.4</v>
       </c>
       <c r="K43" t="n">
-        <v>-507.19</v>
+        <v>168.15</v>
       </c>
       <c r="L43" t="n">
-        <v>621.1900000000001</v>
+        <v>212.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:40</t>
+          <t>07:59:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="F44" t="n">
-        <v>7.58</v>
+        <v>7.77</v>
       </c>
       <c r="G44" t="n">
-        <v>77.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="H44" t="n">
-        <v>52.6</v>
+        <v>44.6</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-29.87</v>
+        <v>-77.56</v>
       </c>
       <c r="K44" t="n">
-        <v>-71.79000000000001</v>
+        <v>-78.63</v>
       </c>
       <c r="L44" t="n">
-        <v>77.75</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:06:33</t>
+          <t>08:01:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="F45" t="n">
-        <v>7.6</v>
+        <v>7.38</v>
       </c>
       <c r="G45" t="n">
-        <v>83.5</v>
+        <v>80.2</v>
       </c>
       <c r="H45" t="n">
-        <v>46.4</v>
+        <v>42.4</v>
       </c>
       <c r="I45" t="n">
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>214.68</v>
+        <v>89.23</v>
       </c>
       <c r="K45" t="n">
-        <v>24.43</v>
+        <v>-45.98</v>
       </c>
       <c r="L45" t="n">
-        <v>216.07</v>
+        <v>100.38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:08:40</t>
+          <t>08:03:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="F46" t="n">
-        <v>6.96</v>
+        <v>7.12</v>
       </c>
       <c r="G46" t="n">
-        <v>80</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>53.4</v>
+        <v>50.5</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-84.54000000000001</v>
+        <v>-40.39</v>
       </c>
       <c r="K46" t="n">
-        <v>34.76</v>
+        <v>163.33</v>
       </c>
       <c r="L46" t="n">
-        <v>91.41</v>
+        <v>168.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:13:20</t>
+          <t>08:07:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="F47" t="n">
-        <v>7.62</v>
+        <v>8.33</v>
       </c>
       <c r="G47" t="n">
-        <v>89.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="H47" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-31.56</v>
+        <v>98.16</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.49</v>
+        <v>-74.97</v>
       </c>
       <c r="L47" t="n">
-        <v>46.02</v>
+        <v>123.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:14:35</t>
+          <t>08:08:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="F48" t="n">
-        <v>7.88</v>
+        <v>7.96</v>
       </c>
       <c r="G48" t="n">
-        <v>61</v>
+        <v>68.3</v>
       </c>
       <c r="H48" t="n">
-        <v>45.7</v>
+        <v>43.3</v>
       </c>
       <c r="I48" t="n">
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-82.03</v>
+        <v>35.15</v>
       </c>
       <c r="K48" t="n">
-        <v>31.56</v>
+        <v>-153.81</v>
       </c>
       <c r="L48" t="n">
-        <v>87.89</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:16:30</t>
+          <t>08:10:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="F49" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="G49" t="n">
-        <v>62.4</v>
+        <v>82.2</v>
       </c>
       <c r="H49" t="n">
-        <v>46.3</v>
+        <v>50.6</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>112.02</v>
+        <v>-167</v>
       </c>
       <c r="K49" t="n">
-        <v>-144.42</v>
+        <v>137.03</v>
       </c>
       <c r="L49" t="n">
-        <v>182.77</v>
+        <v>216.02</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:21:28</t>
+          <t>08:14:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="F50" t="n">
-        <v>8.039999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="G50" t="n">
-        <v>71.3</v>
+        <v>83.8</v>
       </c>
       <c r="H50" t="n">
-        <v>39.7</v>
+        <v>52.5</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-376.21</v>
+        <v>-15.92</v>
       </c>
       <c r="K50" t="n">
-        <v>-32.7</v>
+        <v>50.85</v>
       </c>
       <c r="L50" t="n">
-        <v>377.63</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:23:04</t>
+          <t>08:16:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="F51" t="n">
-        <v>8.119999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="G51" t="n">
-        <v>81.5</v>
+        <v>64.3</v>
       </c>
       <c r="H51" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>60.87</v>
+        <v>-41.23</v>
       </c>
       <c r="K51" t="n">
-        <v>23.89</v>
+        <v>-388.43</v>
       </c>
       <c r="L51" t="n">
-        <v>65.39</v>
+        <v>390.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:24:22</t>
+          <t>08:17:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="G52" t="n">
-        <v>71.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>42.1</v>
+        <v>48</v>
       </c>
       <c r="I52" t="n">
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>140.35</v>
+        <v>-165.9</v>
       </c>
       <c r="K52" t="n">
-        <v>-23.38</v>
+        <v>-1.95</v>
       </c>
       <c r="L52" t="n">
-        <v>142.28</v>
+        <v>165.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:28:06</t>
+          <t>08:23:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="F53" t="n">
-        <v>7.66</v>
+        <v>7.33</v>
       </c>
       <c r="G53" t="n">
-        <v>64.2</v>
+        <v>85</v>
       </c>
       <c r="H53" t="n">
-        <v>48.4</v>
+        <v>39.5</v>
       </c>
       <c r="I53" t="n">
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>131.87</v>
+        <v>14.28</v>
       </c>
       <c r="K53" t="n">
-        <v>-247.43</v>
+        <v>234.37</v>
       </c>
       <c r="L53" t="n">
-        <v>280.38</v>
+        <v>234.81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:30:10</t>
+          <t>08:25:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="F54" t="n">
-        <v>7.74</v>
+        <v>7.73</v>
       </c>
       <c r="G54" t="n">
-        <v>82.3</v>
+        <v>74.7</v>
       </c>
       <c r="H54" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>8.960000000000001</v>
+        <v>-272.52</v>
       </c>
       <c r="K54" t="n">
-        <v>153.13</v>
+        <v>-164.99</v>
       </c>
       <c r="L54" t="n">
-        <v>153.39</v>
+        <v>318.58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:32:32</t>
+          <t>08:27:12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="F55" t="n">
-        <v>7.75</v>
+        <v>7.52</v>
       </c>
       <c r="G55" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>42.2</v>
+        <v>45.5</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>412.45</v>
+        <v>-243.9</v>
       </c>
       <c r="K55" t="n">
-        <v>-53.29</v>
+        <v>-87.48</v>
       </c>
       <c r="L55" t="n">
-        <v>415.88</v>
+        <v>259.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:37:00</t>
+          <t>08:32:13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="F56" t="n">
-        <v>7.98</v>
+        <v>7.86</v>
       </c>
       <c r="G56" t="n">
-        <v>63</v>
+        <v>84.8</v>
       </c>
       <c r="H56" t="n">
-        <v>47.8</v>
+        <v>46.8</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>79.29000000000001</v>
+        <v>20.91</v>
       </c>
       <c r="K56" t="n">
-        <v>111.16</v>
+        <v>733.87</v>
       </c>
       <c r="L56" t="n">
-        <v>136.54</v>
+        <v>734.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:38:06</t>
+          <t>08:32:48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="F57" t="n">
-        <v>8.02</v>
+        <v>7.47</v>
       </c>
       <c r="G57" t="n">
-        <v>86.5</v>
+        <v>80.3</v>
       </c>
       <c r="H57" t="n">
-        <v>43.3</v>
+        <v>55.2</v>
       </c>
       <c r="I57" t="n">
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-332.87</v>
+        <v>221.95</v>
       </c>
       <c r="K57" t="n">
-        <v>287.86</v>
+        <v>547.23</v>
       </c>
       <c r="L57" t="n">
-        <v>440.07</v>
+        <v>590.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:39:20</t>
+          <t>08:34:42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="F58" t="n">
-        <v>7.76</v>
+        <v>8.02</v>
       </c>
       <c r="G58" t="n">
-        <v>72</v>
+        <v>57.9</v>
       </c>
       <c r="H58" t="n">
-        <v>44.9</v>
+        <v>44</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>21.03</v>
+        <v>229.93</v>
       </c>
       <c r="K58" t="n">
-        <v>-341.93</v>
+        <v>669.08</v>
       </c>
       <c r="L58" t="n">
-        <v>342.58</v>
+        <v>707.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:49:34</t>
+          <t>08:47:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="F59" t="n">
-        <v>7.8</v>
+        <v>7.35</v>
       </c>
       <c r="G59" t="n">
-        <v>64.2</v>
+        <v>69.2</v>
       </c>
       <c r="H59" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>29.63</v>
+        <v>32.81</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.38</v>
+        <v>-168.94</v>
       </c>
       <c r="L59" t="n">
-        <v>29.73</v>
+        <v>172.09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:51:20</t>
+          <t>08:48:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="F60" t="n">
-        <v>7.82</v>
+        <v>7.53</v>
       </c>
       <c r="G60" t="n">
-        <v>75.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>6.87</v>
+        <v>-44.44</v>
       </c>
       <c r="K60" t="n">
-        <v>2.53</v>
+        <v>62.34</v>
       </c>
       <c r="L60" t="n">
-        <v>7.33</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:53:52</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.67</v>
+        <v>2.26</v>
       </c>
       <c r="F61" t="n">
-        <v>7.38</v>
+        <v>7.11</v>
       </c>
       <c r="G61" t="n">
-        <v>67.3</v>
+        <v>78.3</v>
       </c>
       <c r="H61" t="n">
-        <v>46.7</v>
+        <v>45.5</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>35.33</v>
+        <v>90.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-19.5</v>
+        <v>40.13</v>
       </c>
       <c r="L61" t="n">
-        <v>40.35</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:59:58</t>
+          <t>08:54:57</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.22</v>
+        <v>2.64</v>
       </c>
       <c r="F62" t="n">
-        <v>8.16</v>
+        <v>8.1</v>
       </c>
       <c r="G62" t="n">
-        <v>59.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>43.6</v>
+        <v>42.6</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>173.99</v>
+        <v>-97.27</v>
       </c>
       <c r="K62" t="n">
-        <v>0.24</v>
+        <v>-54.69</v>
       </c>
       <c r="L62" t="n">
-        <v>173.99</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:01:07</t>
+          <t>08:57:18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="F63" t="n">
-        <v>7.86</v>
+        <v>8.17</v>
       </c>
       <c r="G63" t="n">
-        <v>73.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="H63" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-188.33</v>
+        <v>-101.86</v>
       </c>
       <c r="K63" t="n">
-        <v>84.13</v>
+        <v>-101.45</v>
       </c>
       <c r="L63" t="n">
-        <v>206.26</v>
+        <v>143.77</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:02:16</t>
+          <t>08:59:25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="F64" t="n">
-        <v>7.73</v>
+        <v>7.41</v>
       </c>
       <c r="G64" t="n">
-        <v>71.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="H64" t="n">
-        <v>47.3</v>
+        <v>41.3</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-13.04</v>
+        <v>-34.31</v>
       </c>
       <c r="K64" t="n">
-        <v>255.75</v>
+        <v>142.77</v>
       </c>
       <c r="L64" t="n">
-        <v>256.08</v>
+        <v>146.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:06:09</t>
+          <t>09:05:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="F65" t="n">
-        <v>8.08</v>
+        <v>7.7</v>
       </c>
       <c r="G65" t="n">
-        <v>79.5</v>
+        <v>73.7</v>
       </c>
       <c r="H65" t="n">
-        <v>48.4</v>
+        <v>44.7</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-181.83</v>
+        <v>349.46</v>
       </c>
       <c r="K65" t="n">
-        <v>-38.17</v>
+        <v>-135.04</v>
       </c>
       <c r="L65" t="n">
-        <v>185.8</v>
+        <v>374.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:07:19</t>
+          <t>09:06:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="F66" t="n">
-        <v>8.27</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>61.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-244.95</v>
+        <v>11.25</v>
       </c>
       <c r="K66" t="n">
-        <v>229.44</v>
+        <v>-321.84</v>
       </c>
       <c r="L66" t="n">
-        <v>335.62</v>
+        <v>322.04</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:09:15</t>
+          <t>09:08:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="F67" t="n">
-        <v>7.94</v>
+        <v>7.39</v>
       </c>
       <c r="G67" t="n">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="H67" t="n">
-        <v>51.6</v>
+        <v>41.5</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-34.2</v>
+        <v>125.91</v>
       </c>
       <c r="K67" t="n">
-        <v>332.57</v>
+        <v>-181.81</v>
       </c>
       <c r="L67" t="n">
-        <v>334.33</v>
+        <v>221.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:13:53</t>
+          <t>09:12:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2896,31 +2896,31 @@
         <v>2.42</v>
       </c>
       <c r="F68" t="n">
-        <v>7.43</v>
+        <v>7.33</v>
       </c>
       <c r="G68" t="n">
-        <v>76.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>46</v>
+        <v>49.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>0.99</v>
+        <v>-145.8</v>
       </c>
       <c r="K68" t="n">
-        <v>-304.16</v>
+        <v>385.02</v>
       </c>
       <c r="L68" t="n">
-        <v>304.16</v>
+        <v>411.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:15:10</t>
+          <t>09:14:01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="F69" t="n">
-        <v>6.83</v>
+        <v>7.19</v>
       </c>
       <c r="G69" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>174.06</v>
+        <v>172.03</v>
       </c>
       <c r="K69" t="n">
-        <v>-180.55</v>
+        <v>212.38</v>
       </c>
       <c r="L69" t="n">
-        <v>250.79</v>
+        <v>273.31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:16:10</t>
+          <t>09:15:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="F70" t="n">
-        <v>7.42</v>
+        <v>7.08</v>
       </c>
       <c r="G70" t="n">
         <v>74.8</v>
       </c>
       <c r="H70" t="n">
-        <v>48.1</v>
+        <v>48.9</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>121.29</v>
+        <v>70.81</v>
       </c>
       <c r="K70" t="n">
-        <v>701.59</v>
+        <v>267.21</v>
       </c>
       <c r="L70" t="n">
-        <v>712</v>
+        <v>276.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:21:36</t>
+          <t>09:20:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="F71" t="n">
-        <v>8.109999999999999</v>
+        <v>7.54</v>
       </c>
       <c r="G71" t="n">
-        <v>63.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>38.1</v>
+        <v>48.9</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-364.43</v>
+        <v>-406.17</v>
       </c>
       <c r="K71" t="n">
-        <v>-410.95</v>
+        <v>142.39</v>
       </c>
       <c r="L71" t="n">
-        <v>549.27</v>
+        <v>430.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:23:20</t>
+          <t>09:22:33</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="F72" t="n">
-        <v>7.81</v>
+        <v>7.82</v>
       </c>
       <c r="G72" t="n">
-        <v>67.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>42.9</v>
+        <v>48.1</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-46.2</v>
+        <v>192.94</v>
       </c>
       <c r="K72" t="n">
-        <v>-77.23</v>
+        <v>-246.63</v>
       </c>
       <c r="L72" t="n">
-        <v>89.98999999999999</v>
+        <v>313.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:25:21</t>
+          <t>09:24:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="F73" t="n">
-        <v>7.26</v>
+        <v>7.39</v>
       </c>
       <c r="G73" t="n">
-        <v>67.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="H73" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>110.17</v>
+        <v>414.77</v>
       </c>
       <c r="K73" t="n">
-        <v>25.26</v>
+        <v>332.21</v>
       </c>
       <c r="L73" t="n">
-        <v>113.02</v>
+        <v>531.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:33:52</t>
+          <t>09:36:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="F74" t="n">
-        <v>8.15</v>
+        <v>7.51</v>
       </c>
       <c r="G74" t="n">
-        <v>72.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="H74" t="n">
-        <v>49.5</v>
+        <v>45.1</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>24.67</v>
+        <v>-46.21</v>
       </c>
       <c r="K74" t="n">
-        <v>-63.42</v>
+        <v>45.26</v>
       </c>
       <c r="L74" t="n">
-        <v>68.05</v>
+        <v>64.68000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:35:24</t>
+          <t>09:38:08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="F75" t="n">
-        <v>7.4</v>
+        <v>7.24</v>
       </c>
       <c r="G75" t="n">
-        <v>70.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>46.2</v>
+        <v>46.9</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-123.17</v>
+        <v>-13.72</v>
       </c>
       <c r="K75" t="n">
-        <v>-59.38</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>136.73</v>
+        <v>74.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:36:43</t>
+          <t>09:40:25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.27</v>
+        <v>2.51</v>
       </c>
       <c r="F76" t="n">
-        <v>6.93</v>
+        <v>7.32</v>
       </c>
       <c r="G76" t="n">
-        <v>70.8</v>
+        <v>62</v>
       </c>
       <c r="H76" t="n">
-        <v>57.1</v>
+        <v>44.8</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.61</v>
+        <v>54.13</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.09</v>
+        <v>54.17</v>
       </c>
       <c r="L76" t="n">
-        <v>40.2</v>
+        <v>76.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:41:21</t>
+          <t>09:46:06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="F77" t="n">
-        <v>7.09</v>
+        <v>7.23</v>
       </c>
       <c r="G77" t="n">
-        <v>72.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H77" t="n">
-        <v>43.9</v>
+        <v>42.4</v>
       </c>
       <c r="I77" t="n">
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>58.39</v>
+        <v>130.57</v>
       </c>
       <c r="K77" t="n">
-        <v>24.45</v>
+        <v>83.48</v>
       </c>
       <c r="L77" t="n">
-        <v>63.31</v>
+        <v>154.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:42:52</t>
+          <t>09:48:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="F78" t="n">
-        <v>7.78</v>
+        <v>7.95</v>
       </c>
       <c r="G78" t="n">
-        <v>81.09999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="H78" t="n">
-        <v>50.6</v>
+        <v>49</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>-132.57</v>
+        <v>81.86</v>
       </c>
       <c r="K78" t="n">
-        <v>40.56</v>
+        <v>49.53</v>
       </c>
       <c r="L78" t="n">
-        <v>138.64</v>
+        <v>95.68000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:43:26</t>
+          <t>09:50:05</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="F79" t="n">
-        <v>7.57</v>
+        <v>7.05</v>
       </c>
       <c r="G79" t="n">
-        <v>77.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H79" t="n">
-        <v>42.3</v>
+        <v>48.2</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-108.01</v>
+        <v>-78.39</v>
       </c>
       <c r="K79" t="n">
-        <v>147.22</v>
+        <v>-39.75</v>
       </c>
       <c r="L79" t="n">
-        <v>182.6</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:49:24</t>
+          <t>09:55:07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="F80" t="n">
-        <v>8.31</v>
+        <v>7.13</v>
       </c>
       <c r="G80" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>44.6</v>
+        <v>42.6</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-84</v>
+        <v>177.43</v>
       </c>
       <c r="K80" t="n">
-        <v>169.88</v>
+        <v>-204.59</v>
       </c>
       <c r="L80" t="n">
-        <v>189.51</v>
+        <v>270.81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:50:18</t>
+          <t>09:56:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="F81" t="n">
-        <v>7.94</v>
+        <v>7.48</v>
       </c>
       <c r="G81" t="n">
-        <v>65.3</v>
+        <v>83</v>
       </c>
       <c r="H81" t="n">
-        <v>39.3</v>
+        <v>43.6</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-38.07</v>
+        <v>96.95</v>
       </c>
       <c r="K81" t="n">
-        <v>43.09</v>
+        <v>-65.69</v>
       </c>
       <c r="L81" t="n">
-        <v>57.5</v>
+        <v>117.11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:51:31</t>
+          <t>09:58:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="F82" t="n">
-        <v>7.56</v>
+        <v>7.62</v>
       </c>
       <c r="G82" t="n">
-        <v>75</v>
+        <v>69.3</v>
       </c>
       <c r="H82" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-102.61</v>
+        <v>135.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-52.24</v>
+        <v>-176.62</v>
       </c>
       <c r="L82" t="n">
-        <v>115.14</v>
+        <v>222.82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:56:31</t>
+          <t>10:02:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="F83" t="n">
-        <v>7.48</v>
+        <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>86.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>46.6</v>
+        <v>50.7</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-40.35</v>
+        <v>45.03</v>
       </c>
       <c r="K83" t="n">
-        <v>-91.84</v>
+        <v>-383.65</v>
       </c>
       <c r="L83" t="n">
-        <v>100.31</v>
+        <v>386.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:59:01</t>
+          <t>10:04:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.66</v>
+        <v>3.46</v>
       </c>
       <c r="F84" t="n">
-        <v>7.15</v>
+        <v>7.85</v>
       </c>
       <c r="G84" t="n">
-        <v>75.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H84" t="n">
-        <v>46.8</v>
+        <v>42.2</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-151.86</v>
+        <v>-82.84</v>
       </c>
       <c r="K84" t="n">
-        <v>325.36</v>
+        <v>392.37</v>
       </c>
       <c r="L84" t="n">
-        <v>359.06</v>
+        <v>401.02</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:01:06</t>
+          <t>10:05:56</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="F85" t="n">
-        <v>7.05</v>
+        <v>7.9</v>
       </c>
       <c r="G85" t="n">
-        <v>72.3</v>
+        <v>82.5</v>
       </c>
       <c r="H85" t="n">
-        <v>44.6</v>
+        <v>48.1</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>29.95</v>
+        <v>-209.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-647.9400000000001</v>
+        <v>222.69</v>
       </c>
       <c r="L85" t="n">
-        <v>648.63</v>
+        <v>306.01</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:05:23</t>
+          <t>10:10:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.71</v>
+        <v>2.54</v>
       </c>
       <c r="F86" t="n">
-        <v>7.84</v>
+        <v>7.73</v>
       </c>
       <c r="G86" t="n">
-        <v>67.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>49.4</v>
+        <v>46.9</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>9.529999999999999</v>
+        <v>-346.78</v>
       </c>
       <c r="K86" t="n">
-        <v>-675.48</v>
+        <v>253.99</v>
       </c>
       <c r="L86" t="n">
-        <v>675.54</v>
+        <v>429.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:07:23</t>
+          <t>10:12:32</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.46</v>
+        <v>2.79</v>
       </c>
       <c r="F87" t="n">
-        <v>7.89</v>
+        <v>7.45</v>
       </c>
       <c r="G87" t="n">
-        <v>64</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>47.5</v>
+        <v>40.3</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-302.82</v>
+        <v>-150.53</v>
       </c>
       <c r="K87" t="n">
-        <v>100.1</v>
+        <v>489.8</v>
       </c>
       <c r="L87" t="n">
-        <v>318.94</v>
+        <v>512.41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:08:21</t>
+          <t>10:14:23</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="F88" t="n">
-        <v>7.19</v>
+        <v>7.73</v>
       </c>
       <c r="G88" t="n">
-        <v>73.8</v>
+        <v>65</v>
       </c>
       <c r="H88" t="n">
-        <v>48.2</v>
+        <v>46.3</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>125.79</v>
+        <v>-133.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-433.15</v>
+        <v>158.88</v>
       </c>
       <c r="L88" t="n">
-        <v>451.05</v>
+        <v>207.68</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.74</v>
+        <v>-17.56</v>
       </c>
       <c r="K14" t="n">
-        <v>59.27</v>
+        <v>58.68</v>
       </c>
       <c r="L14" t="n">
-        <v>61.87</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>138.86</v>
+        <v>100.84</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.58</v>
+        <v>-30.92</v>
       </c>
       <c r="L15" t="n">
-        <v>145.24</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.64</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-59.59</v>
+        <v>-64.16</v>
       </c>
       <c r="L16" t="n">
-        <v>59.6</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-151.53</v>
+        <v>-127.75</v>
       </c>
       <c r="K17" t="n">
-        <v>-44.37</v>
+        <v>-37.41</v>
       </c>
       <c r="L17" t="n">
-        <v>157.89</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>155.96</v>
+        <v>128.86</v>
       </c>
       <c r="K18" t="n">
-        <v>-48.65</v>
+        <v>-40.2</v>
       </c>
       <c r="L18" t="n">
-        <v>163.37</v>
+        <v>134.98</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>151.13</v>
+        <v>143.67</v>
       </c>
       <c r="K19" t="n">
-        <v>-25.81</v>
+        <v>-24.53</v>
       </c>
       <c r="L19" t="n">
-        <v>153.32</v>
+        <v>145.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>218.47</v>
+        <v>184.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-307.18</v>
+        <v>-259.61</v>
       </c>
       <c r="L20" t="n">
-        <v>376.95</v>
+        <v>318.57</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>34.38</v>
+        <v>46.63</v>
       </c>
       <c r="K21" t="n">
-        <v>70.48</v>
+        <v>95.59</v>
       </c>
       <c r="L21" t="n">
-        <v>78.42</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-21.57</v>
+        <v>-26.75</v>
       </c>
       <c r="K22" t="n">
-        <v>70.15000000000001</v>
+        <v>87</v>
       </c>
       <c r="L22" t="n">
-        <v>73.39</v>
+        <v>91.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-31.09</v>
+        <v>-87.56</v>
       </c>
       <c r="K23" t="n">
-        <v>29.26</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>42.69</v>
+        <v>120.23</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-321.57</v>
+        <v>-290.02</v>
       </c>
       <c r="K24" t="n">
-        <v>41.93</v>
+        <v>37.81</v>
       </c>
       <c r="L24" t="n">
-        <v>324.3</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-227.39</v>
+        <v>-191.46</v>
       </c>
       <c r="K25" t="n">
-        <v>321.9</v>
+        <v>271.03</v>
       </c>
       <c r="L25" t="n">
-        <v>394.11</v>
+        <v>331.84</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>399.49</v>
+        <v>373.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-216.64</v>
+        <v>-202.4</v>
       </c>
       <c r="L26" t="n">
-        <v>454.45</v>
+        <v>424.57</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-16.38</v>
+        <v>-23.45</v>
       </c>
       <c r="K27" t="n">
-        <v>274.67</v>
+        <v>393.26</v>
       </c>
       <c r="L27" t="n">
-        <v>275.16</v>
+        <v>393.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>199.86</v>
+        <v>293</v>
       </c>
       <c r="K28" t="n">
-        <v>314.94</v>
+        <v>461.7</v>
       </c>
       <c r="L28" t="n">
-        <v>373</v>
+        <v>546.83</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-152.91</v>
+        <v>-101.52</v>
       </c>
       <c r="K29" t="n">
-        <v>148.93</v>
+        <v>98.87</v>
       </c>
       <c r="L29" t="n">
-        <v>213.45</v>
+        <v>141.71</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-34.45</v>
+        <v>-22.53</v>
       </c>
       <c r="K30" t="n">
-        <v>222.22</v>
+        <v>145.33</v>
       </c>
       <c r="L30" t="n">
-        <v>224.87</v>
+        <v>147.07</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>106.9</v>
+        <v>95.44</v>
       </c>
       <c r="K31" t="n">
-        <v>38.07</v>
+        <v>33.99</v>
       </c>
       <c r="L31" t="n">
-        <v>113.47</v>
+        <v>101.31</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.779999999999999</v>
+        <v>-10.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-93.7</v>
+        <v>-98.88</v>
       </c>
       <c r="L32" t="n">
-        <v>94.20999999999999</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-77.54000000000001</v>
+        <v>-88.15000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.95</v>
+        <v>-36.32</v>
       </c>
       <c r="L33" t="n">
-        <v>83.87</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-205</v>
+        <v>-161.72</v>
       </c>
       <c r="K34" t="n">
-        <v>31.63</v>
+        <v>24.95</v>
       </c>
       <c r="L34" t="n">
-        <v>207.42</v>
+        <v>163.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-222.01</v>
+        <v>-200.57</v>
       </c>
       <c r="K35" t="n">
-        <v>125.16</v>
+        <v>113.07</v>
       </c>
       <c r="L35" t="n">
-        <v>254.86</v>
+        <v>230.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>27.33</v>
+        <v>67.86</v>
       </c>
       <c r="K36" t="n">
-        <v>-38.98</v>
+        <v>-96.78</v>
       </c>
       <c r="L36" t="n">
-        <v>47.61</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-174.39</v>
+        <v>-189.24</v>
       </c>
       <c r="K37" t="n">
-        <v>97.61</v>
+        <v>105.92</v>
       </c>
       <c r="L37" t="n">
-        <v>199.85</v>
+        <v>216.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>246.55</v>
+        <v>247.47</v>
       </c>
       <c r="K38" t="n">
-        <v>123.03</v>
+        <v>123.49</v>
       </c>
       <c r="L38" t="n">
-        <v>275.54</v>
+        <v>276.57</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.36</v>
+        <v>-14.56</v>
       </c>
       <c r="K39" t="n">
-        <v>320.4</v>
+        <v>324.86</v>
       </c>
       <c r="L39" t="n">
-        <v>320.72</v>
+        <v>325.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-215.9</v>
+        <v>-246.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-406.69</v>
+        <v>-463.66</v>
       </c>
       <c r="L40" t="n">
-        <v>460.45</v>
+        <v>524.95</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>64.8</v>
+        <v>95.36</v>
       </c>
       <c r="K41" t="n">
-        <v>227.95</v>
+        <v>335.43</v>
       </c>
       <c r="L41" t="n">
-        <v>236.98</v>
+        <v>348.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-358.64</v>
+        <v>-401.89</v>
       </c>
       <c r="K42" t="n">
-        <v>-140.72</v>
+        <v>-157.68</v>
       </c>
       <c r="L42" t="n">
-        <v>385.26</v>
+        <v>431.71</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>130.4</v>
+        <v>171.05</v>
       </c>
       <c r="K43" t="n">
-        <v>168.15</v>
+        <v>220.57</v>
       </c>
       <c r="L43" t="n">
-        <v>212.78</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-77.56</v>
+        <v>-72.53</v>
       </c>
       <c r="K44" t="n">
-        <v>-78.63</v>
+        <v>-73.53</v>
       </c>
       <c r="L44" t="n">
-        <v>110.44</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>89.23</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-45.98</v>
+        <v>-38.51</v>
       </c>
       <c r="L45" t="n">
-        <v>100.38</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.39</v>
+        <v>-30.92</v>
       </c>
       <c r="K46" t="n">
-        <v>163.33</v>
+        <v>125.03</v>
       </c>
       <c r="L46" t="n">
-        <v>168.25</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>98.16</v>
+        <v>87.52</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.97</v>
+        <v>-66.84</v>
       </c>
       <c r="L47" t="n">
-        <v>123.51</v>
+        <v>110.12</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>35.15</v>
+        <v>33.52</v>
       </c>
       <c r="K48" t="n">
-        <v>-153.81</v>
+        <v>-146.65</v>
       </c>
       <c r="L48" t="n">
-        <v>157.78</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-167</v>
+        <v>-123.41</v>
       </c>
       <c r="K49" t="n">
-        <v>137.03</v>
+        <v>101.26</v>
       </c>
       <c r="L49" t="n">
-        <v>216.02</v>
+        <v>159.63</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.92</v>
+        <v>-26.67</v>
       </c>
       <c r="K50" t="n">
-        <v>50.85</v>
+        <v>85.2</v>
       </c>
       <c r="L50" t="n">
-        <v>53.28</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-41.23</v>
+        <v>-34.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-388.43</v>
+        <v>-321.84</v>
       </c>
       <c r="L51" t="n">
-        <v>390.62</v>
+        <v>323.65</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-165.9</v>
+        <v>-151.68</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.95</v>
+        <v>-1.78</v>
       </c>
       <c r="L52" t="n">
-        <v>165.91</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>14.28</v>
+        <v>17.16</v>
       </c>
       <c r="K53" t="n">
-        <v>234.37</v>
+        <v>281.6</v>
       </c>
       <c r="L53" t="n">
-        <v>234.81</v>
+        <v>282.12</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-272.52</v>
+        <v>-296.25</v>
       </c>
       <c r="K54" t="n">
-        <v>-164.99</v>
+        <v>-179.36</v>
       </c>
       <c r="L54" t="n">
-        <v>318.58</v>
+        <v>346.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-243.9</v>
+        <v>-247.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-87.48</v>
+        <v>-88.84</v>
       </c>
       <c r="L55" t="n">
-        <v>259.12</v>
+        <v>263.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>20.91</v>
+        <v>21.91</v>
       </c>
       <c r="K56" t="n">
-        <v>733.87</v>
+        <v>769.04</v>
       </c>
       <c r="L56" t="n">
-        <v>734.17</v>
+        <v>769.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>221.95</v>
+        <v>216.87</v>
       </c>
       <c r="K57" t="n">
-        <v>547.23</v>
+        <v>534.7</v>
       </c>
       <c r="L57" t="n">
-        <v>590.53</v>
+        <v>577.01</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>229.93</v>
+        <v>223.72</v>
       </c>
       <c r="K58" t="n">
-        <v>669.08</v>
+        <v>650.99</v>
       </c>
       <c r="L58" t="n">
-        <v>707.48</v>
+        <v>688.36</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>32.81</v>
+        <v>23.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-168.94</v>
+        <v>-119.19</v>
       </c>
       <c r="L59" t="n">
-        <v>172.09</v>
+        <v>121.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-44.44</v>
+        <v>-37.28</v>
       </c>
       <c r="K60" t="n">
-        <v>62.34</v>
+        <v>52.29</v>
       </c>
       <c r="L60" t="n">
-        <v>76.56</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>90.69</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>40.13</v>
+        <v>31.12</v>
       </c>
       <c r="L61" t="n">
-        <v>99.17</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-97.27</v>
+        <v>-94.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-54.69</v>
+        <v>-53.09</v>
       </c>
       <c r="L62" t="n">
-        <v>111.59</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-101.86</v>
+        <v>-93.89</v>
       </c>
       <c r="K63" t="n">
-        <v>-101.45</v>
+        <v>-93.51000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>143.77</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.31</v>
+        <v>-34</v>
       </c>
       <c r="K64" t="n">
-        <v>142.77</v>
+        <v>141.48</v>
       </c>
       <c r="L64" t="n">
-        <v>146.83</v>
+        <v>145.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>349.46</v>
+        <v>307.26</v>
       </c>
       <c r="K65" t="n">
-        <v>-135.04</v>
+        <v>-118.73</v>
       </c>
       <c r="L65" t="n">
-        <v>374.65</v>
+        <v>329.4</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>11.25</v>
+        <v>11.71</v>
       </c>
       <c r="K66" t="n">
-        <v>-321.84</v>
+        <v>-334.83</v>
       </c>
       <c r="L66" t="n">
-        <v>322.04</v>
+        <v>335.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>125.91</v>
+        <v>119.66</v>
       </c>
       <c r="K67" t="n">
-        <v>-181.81</v>
+        <v>-172.79</v>
       </c>
       <c r="L67" t="n">
-        <v>221.15</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-145.8</v>
+        <v>-143.2</v>
       </c>
       <c r="K68" t="n">
-        <v>385.02</v>
+        <v>378.14</v>
       </c>
       <c r="L68" t="n">
-        <v>411.7</v>
+        <v>404.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>172.03</v>
+        <v>171.19</v>
       </c>
       <c r="K69" t="n">
-        <v>212.38</v>
+        <v>211.35</v>
       </c>
       <c r="L69" t="n">
-        <v>273.31</v>
+        <v>271.98</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>70.81</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>267.21</v>
+        <v>285.6</v>
       </c>
       <c r="L70" t="n">
-        <v>276.44</v>
+        <v>295.46</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-406.17</v>
+        <v>-540.83</v>
       </c>
       <c r="K71" t="n">
-        <v>142.39</v>
+        <v>189.6</v>
       </c>
       <c r="L71" t="n">
-        <v>430.4</v>
+        <v>573.1</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>192.94</v>
+        <v>272.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-246.63</v>
+        <v>-348.48</v>
       </c>
       <c r="L72" t="n">
-        <v>313.13</v>
+        <v>442.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>414.77</v>
+        <v>428.07</v>
       </c>
       <c r="K73" t="n">
-        <v>332.21</v>
+        <v>342.87</v>
       </c>
       <c r="L73" t="n">
-        <v>531.42</v>
+        <v>548.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.21</v>
+        <v>-59.97</v>
       </c>
       <c r="K74" t="n">
-        <v>45.26</v>
+        <v>58.75</v>
       </c>
       <c r="L74" t="n">
-        <v>64.68000000000001</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.72</v>
+        <v>-17.04</v>
       </c>
       <c r="K75" t="n">
-        <v>-72.98999999999999</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>74.27</v>
+        <v>92.23</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>54.13</v>
+        <v>52.71</v>
       </c>
       <c r="K76" t="n">
-        <v>54.17</v>
+        <v>52.75</v>
       </c>
       <c r="L76" t="n">
-        <v>76.58</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>130.57</v>
+        <v>123.58</v>
       </c>
       <c r="K77" t="n">
-        <v>83.48</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>154.98</v>
+        <v>146.68</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>81.86</v>
+        <v>88.36</v>
       </c>
       <c r="K78" t="n">
-        <v>49.53</v>
+        <v>53.46</v>
       </c>
       <c r="L78" t="n">
-        <v>95.68000000000001</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-78.39</v>
+        <v>-80.13</v>
       </c>
       <c r="K79" t="n">
-        <v>-39.75</v>
+        <v>-40.63</v>
       </c>
       <c r="L79" t="n">
-        <v>87.89</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>177.43</v>
+        <v>162.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-204.59</v>
+        <v>-186.87</v>
       </c>
       <c r="L80" t="n">
-        <v>270.81</v>
+        <v>247.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>96.95</v>
+        <v>130.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-65.69</v>
+        <v>-88.20999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>117.11</v>
+        <v>157.26</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>135.85</v>
+        <v>140.46</v>
       </c>
       <c r="K82" t="n">
-        <v>-176.62</v>
+        <v>-182.6</v>
       </c>
       <c r="L82" t="n">
-        <v>222.82</v>
+        <v>230.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>45.03</v>
+        <v>47.06</v>
       </c>
       <c r="K83" t="n">
-        <v>-383.65</v>
+        <v>-401</v>
       </c>
       <c r="L83" t="n">
-        <v>386.28</v>
+        <v>403.75</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-82.84</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>392.37</v>
+        <v>429.79</v>
       </c>
       <c r="L84" t="n">
-        <v>401.02</v>
+        <v>439.26</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-209.87</v>
+        <v>-200.7</v>
       </c>
       <c r="K85" t="n">
-        <v>222.69</v>
+        <v>212.96</v>
       </c>
       <c r="L85" t="n">
-        <v>306.01</v>
+        <v>292.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-346.78</v>
+        <v>-352.61</v>
       </c>
       <c r="K86" t="n">
-        <v>253.99</v>
+        <v>258.25</v>
       </c>
       <c r="L86" t="n">
-        <v>429.85</v>
+        <v>437.07</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-150.53</v>
+        <v>-152.24</v>
       </c>
       <c r="K87" t="n">
-        <v>489.8</v>
+        <v>495.37</v>
       </c>
       <c r="L87" t="n">
-        <v>512.41</v>
+        <v>518.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-133.75</v>
+        <v>-205.5</v>
       </c>
       <c r="K88" t="n">
-        <v>158.88</v>
+        <v>244.1</v>
       </c>
       <c r="L88" t="n">
-        <v>207.68</v>
+        <v>319.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.56</v>
+        <v>-14.66</v>
       </c>
       <c r="K14" t="n">
-        <v>58.68</v>
+        <v>48.98</v>
       </c>
       <c r="L14" t="n">
-        <v>61.25</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>100.84</v>
+        <v>86.13</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.92</v>
+        <v>-26.41</v>
       </c>
       <c r="L15" t="n">
-        <v>105.47</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>-64.16</v>
+        <v>-56.46</v>
       </c>
       <c r="L16" t="n">
-        <v>64.16</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-127.75</v>
+        <v>-106.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-37.41</v>
+        <v>-31.13</v>
       </c>
       <c r="L17" t="n">
-        <v>133.12</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>128.86</v>
+        <v>107.64</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.2</v>
+        <v>-33.58</v>
       </c>
       <c r="L18" t="n">
-        <v>134.98</v>
+        <v>112.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>143.67</v>
+        <v>107.81</v>
       </c>
       <c r="K19" t="n">
-        <v>-24.53</v>
+        <v>-18.41</v>
       </c>
       <c r="L19" t="n">
-        <v>145.75</v>
+        <v>109.37</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>184.64</v>
+        <v>130.25</v>
       </c>
       <c r="K20" t="n">
-        <v>-259.61</v>
+        <v>-183.14</v>
       </c>
       <c r="L20" t="n">
-        <v>318.57</v>
+        <v>224.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>46.63</v>
+        <v>33.36</v>
       </c>
       <c r="K21" t="n">
-        <v>95.59</v>
+        <v>68.39</v>
       </c>
       <c r="L21" t="n">
-        <v>106.36</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-26.75</v>
+        <v>-22.21</v>
       </c>
       <c r="K22" t="n">
-        <v>87</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>91.02</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-87.56</v>
+        <v>-49.94</v>
       </c>
       <c r="K23" t="n">
-        <v>82.40000000000001</v>
+        <v>47</v>
       </c>
       <c r="L23" t="n">
-        <v>120.23</v>
+        <v>68.58</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-290.02</v>
+        <v>-198.78</v>
       </c>
       <c r="K24" t="n">
-        <v>37.81</v>
+        <v>25.92</v>
       </c>
       <c r="L24" t="n">
-        <v>292.48</v>
+        <v>200.46</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-191.46</v>
+        <v>-129.03</v>
       </c>
       <c r="K25" t="n">
-        <v>271.03</v>
+        <v>182.65</v>
       </c>
       <c r="L25" t="n">
-        <v>331.84</v>
+        <v>223.63</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>373.22</v>
+        <v>240.36</v>
       </c>
       <c r="K26" t="n">
-        <v>-202.4</v>
+        <v>-130.35</v>
       </c>
       <c r="L26" t="n">
-        <v>424.57</v>
+        <v>273.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-23.45</v>
+        <v>-12.3</v>
       </c>
       <c r="K27" t="n">
-        <v>393.26</v>
+        <v>206.27</v>
       </c>
       <c r="L27" t="n">
-        <v>393.96</v>
+        <v>206.64</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>293</v>
+        <v>146.4</v>
       </c>
       <c r="K28" t="n">
-        <v>461.7</v>
+        <v>230.69</v>
       </c>
       <c r="L28" t="n">
-        <v>546.83</v>
+        <v>273.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-101.52</v>
+        <v>-98.84999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>98.87</v>
+        <v>96.28</v>
       </c>
       <c r="L29" t="n">
-        <v>141.71</v>
+        <v>137.99</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-22.53</v>
+        <v>-21.98</v>
       </c>
       <c r="K30" t="n">
-        <v>145.33</v>
+        <v>141.75</v>
       </c>
       <c r="L30" t="n">
-        <v>147.07</v>
+        <v>143.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>95.44</v>
+        <v>80.91</v>
       </c>
       <c r="K31" t="n">
-        <v>33.99</v>
+        <v>28.81</v>
       </c>
       <c r="L31" t="n">
-        <v>101.31</v>
+        <v>85.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.32</v>
+        <v>-8.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-98.88</v>
+        <v>-81.45</v>
       </c>
       <c r="L32" t="n">
-        <v>99.42</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-88.15000000000001</v>
+        <v>-69.23</v>
       </c>
       <c r="K33" t="n">
-        <v>-36.32</v>
+        <v>-28.52</v>
       </c>
       <c r="L33" t="n">
-        <v>95.34</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-161.72</v>
+        <v>-140.12</v>
       </c>
       <c r="K34" t="n">
-        <v>24.95</v>
+        <v>21.62</v>
       </c>
       <c r="L34" t="n">
-        <v>163.64</v>
+        <v>141.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-200.57</v>
+        <v>-133.89</v>
       </c>
       <c r="K35" t="n">
-        <v>113.07</v>
+        <v>75.48</v>
       </c>
       <c r="L35" t="n">
-        <v>230.24</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>67.86</v>
+        <v>44.51</v>
       </c>
       <c r="K36" t="n">
-        <v>-96.78</v>
+        <v>-63.48</v>
       </c>
       <c r="L36" t="n">
-        <v>118.2</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-189.24</v>
+        <v>-133.7</v>
       </c>
       <c r="K37" t="n">
-        <v>105.92</v>
+        <v>74.84</v>
       </c>
       <c r="L37" t="n">
-        <v>216.86</v>
+        <v>153.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>247.47</v>
+        <v>161.96</v>
       </c>
       <c r="K38" t="n">
-        <v>123.49</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>276.57</v>
+        <v>181.01</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.56</v>
+        <v>-9.31</v>
       </c>
       <c r="K39" t="n">
-        <v>324.86</v>
+        <v>207.71</v>
       </c>
       <c r="L39" t="n">
-        <v>325.19</v>
+        <v>207.92</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-246.15</v>
+        <v>-145.32</v>
       </c>
       <c r="K40" t="n">
-        <v>-463.66</v>
+        <v>-273.73</v>
       </c>
       <c r="L40" t="n">
-        <v>524.95</v>
+        <v>309.91</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>95.36</v>
+        <v>52.97</v>
       </c>
       <c r="K41" t="n">
-        <v>335.43</v>
+        <v>186.34</v>
       </c>
       <c r="L41" t="n">
-        <v>348.72</v>
+        <v>193.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-401.89</v>
+        <v>-218.17</v>
       </c>
       <c r="K42" t="n">
-        <v>-157.68</v>
+        <v>-85.59999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>431.71</v>
+        <v>234.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>171.05</v>
+        <v>105.39</v>
       </c>
       <c r="K43" t="n">
-        <v>220.57</v>
+        <v>135.89</v>
       </c>
       <c r="L43" t="n">
-        <v>279.12</v>
+        <v>171.97</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.53</v>
+        <v>-61.49</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.53</v>
+        <v>-62.34</v>
       </c>
       <c r="L44" t="n">
-        <v>103.28</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>74.73999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.51</v>
+        <v>-32.87</v>
       </c>
       <c r="L45" t="n">
-        <v>84.06999999999999</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.92</v>
+        <v>-25.97</v>
       </c>
       <c r="K46" t="n">
-        <v>125.03</v>
+        <v>105.02</v>
       </c>
       <c r="L46" t="n">
-        <v>128.8</v>
+        <v>108.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>87.52</v>
+        <v>76.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-66.84</v>
+        <v>-58.72</v>
       </c>
       <c r="L47" t="n">
-        <v>110.12</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>33.52</v>
+        <v>25.42</v>
       </c>
       <c r="K48" t="n">
-        <v>-146.65</v>
+        <v>-111.2</v>
       </c>
       <c r="L48" t="n">
-        <v>150.44</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-123.41</v>
+        <v>-109.3</v>
       </c>
       <c r="K49" t="n">
-        <v>101.26</v>
+        <v>89.69</v>
       </c>
       <c r="L49" t="n">
-        <v>159.63</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-26.67</v>
+        <v>-21.44</v>
       </c>
       <c r="K50" t="n">
-        <v>85.2</v>
+        <v>68.47</v>
       </c>
       <c r="L50" t="n">
-        <v>89.28</v>
+        <v>71.73999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-34.16</v>
+        <v>-26.04</v>
       </c>
       <c r="K51" t="n">
-        <v>-321.84</v>
+        <v>-245.29</v>
       </c>
       <c r="L51" t="n">
-        <v>323.65</v>
+        <v>246.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-151.68</v>
+        <v>-113.53</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.78</v>
+        <v>-1.33</v>
       </c>
       <c r="L52" t="n">
-        <v>151.69</v>
+        <v>113.54</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>17.16</v>
+        <v>10.23</v>
       </c>
       <c r="K53" t="n">
-        <v>281.6</v>
+        <v>167.86</v>
       </c>
       <c r="L53" t="n">
-        <v>282.12</v>
+        <v>168.17</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-296.25</v>
+        <v>-172.5</v>
       </c>
       <c r="K54" t="n">
-        <v>-179.36</v>
+        <v>-104.44</v>
       </c>
       <c r="L54" t="n">
-        <v>346.31</v>
+        <v>201.66</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-247.7</v>
+        <v>-166.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-88.84</v>
+        <v>-59.61</v>
       </c>
       <c r="L55" t="n">
-        <v>263.15</v>
+        <v>176.57</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>21.91</v>
+        <v>11.39</v>
       </c>
       <c r="K56" t="n">
-        <v>769.04</v>
+        <v>399.73</v>
       </c>
       <c r="L56" t="n">
-        <v>769.35</v>
+        <v>399.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>216.87</v>
+        <v>126.46</v>
       </c>
       <c r="K57" t="n">
-        <v>534.7</v>
+        <v>311.8</v>
       </c>
       <c r="L57" t="n">
-        <v>577.01</v>
+        <v>336.47</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>223.72</v>
+        <v>120.42</v>
       </c>
       <c r="K58" t="n">
-        <v>650.99</v>
+        <v>350.4</v>
       </c>
       <c r="L58" t="n">
-        <v>688.36</v>
+        <v>370.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>23.15</v>
+        <v>21.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-119.19</v>
+        <v>-112.66</v>
       </c>
       <c r="L59" t="n">
-        <v>121.42</v>
+        <v>114.76</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-37.28</v>
+        <v>-36.74</v>
       </c>
       <c r="K60" t="n">
-        <v>52.29</v>
+        <v>51.54</v>
       </c>
       <c r="L60" t="n">
-        <v>64.22</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>70.34999999999999</v>
+        <v>67.17</v>
       </c>
       <c r="K61" t="n">
-        <v>31.12</v>
+        <v>29.72</v>
       </c>
       <c r="L61" t="n">
-        <v>76.92</v>
+        <v>73.45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-94.42</v>
+        <v>-81.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.09</v>
+        <v>-45.9</v>
       </c>
       <c r="L62" t="n">
-        <v>108.32</v>
+        <v>93.66</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-93.89</v>
+        <v>-77.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-93.51000000000001</v>
+        <v>-77.64</v>
       </c>
       <c r="L63" t="n">
-        <v>132.52</v>
+        <v>110.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-34</v>
+        <v>-25.67</v>
       </c>
       <c r="K64" t="n">
-        <v>141.48</v>
+        <v>106.83</v>
       </c>
       <c r="L64" t="n">
-        <v>145.51</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>307.26</v>
+        <v>213.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-118.73</v>
+        <v>-82.36</v>
       </c>
       <c r="L65" t="n">
-        <v>329.4</v>
+        <v>228.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>11.71</v>
+        <v>7.25</v>
       </c>
       <c r="K66" t="n">
-        <v>-334.83</v>
+        <v>-207.52</v>
       </c>
       <c r="L66" t="n">
-        <v>335.04</v>
+        <v>207.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>119.66</v>
+        <v>83.77</v>
       </c>
       <c r="K67" t="n">
-        <v>-172.79</v>
+        <v>-120.96</v>
       </c>
       <c r="L67" t="n">
-        <v>210.18</v>
+        <v>147.13</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-143.2</v>
+        <v>-84.33</v>
       </c>
       <c r="K68" t="n">
-        <v>378.14</v>
+        <v>222.7</v>
       </c>
       <c r="L68" t="n">
-        <v>404.35</v>
+        <v>238.13</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>171.19</v>
+        <v>112.31</v>
       </c>
       <c r="K69" t="n">
-        <v>211.35</v>
+        <v>138.66</v>
       </c>
       <c r="L69" t="n">
-        <v>271.98</v>
+        <v>178.44</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>75.68000000000001</v>
+        <v>48.24</v>
       </c>
       <c r="K70" t="n">
-        <v>285.6</v>
+        <v>182.05</v>
       </c>
       <c r="L70" t="n">
-        <v>295.46</v>
+        <v>188.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-540.83</v>
+        <v>-273.05</v>
       </c>
       <c r="K71" t="n">
-        <v>189.6</v>
+        <v>95.72</v>
       </c>
       <c r="L71" t="n">
-        <v>573.1</v>
+        <v>289.34</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>272.62</v>
+        <v>140.6</v>
       </c>
       <c r="K72" t="n">
-        <v>-348.48</v>
+        <v>-179.73</v>
       </c>
       <c r="L72" t="n">
-        <v>442.45</v>
+        <v>228.19</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>428.07</v>
+        <v>253.43</v>
       </c>
       <c r="K73" t="n">
-        <v>342.87</v>
+        <v>202.99</v>
       </c>
       <c r="L73" t="n">
-        <v>548.46</v>
+        <v>324.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-59.97</v>
+        <v>-48.49</v>
       </c>
       <c r="K74" t="n">
-        <v>58.75</v>
+        <v>47.5</v>
       </c>
       <c r="L74" t="n">
-        <v>83.95</v>
+        <v>67.88</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-17.04</v>
+        <v>-13.66</v>
       </c>
       <c r="K75" t="n">
-        <v>-90.65000000000001</v>
+        <v>-72.67</v>
       </c>
       <c r="L75" t="n">
-        <v>92.23</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>52.71</v>
+        <v>47.85</v>
       </c>
       <c r="K76" t="n">
-        <v>52.75</v>
+        <v>47.89</v>
       </c>
       <c r="L76" t="n">
-        <v>74.58</v>
+        <v>67.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>123.58</v>
+        <v>100.65</v>
       </c>
       <c r="K77" t="n">
-        <v>79.01000000000001</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>146.68</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>88.36</v>
+        <v>77.47</v>
       </c>
       <c r="K78" t="n">
-        <v>53.46</v>
+        <v>46.88</v>
       </c>
       <c r="L78" t="n">
-        <v>103.28</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.13</v>
+        <v>-70.56</v>
       </c>
       <c r="K79" t="n">
-        <v>-40.63</v>
+        <v>-35.78</v>
       </c>
       <c r="L79" t="n">
-        <v>89.84999999999999</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>162.06</v>
+        <v>112.35</v>
       </c>
       <c r="K80" t="n">
-        <v>-186.87</v>
+        <v>-129.55</v>
       </c>
       <c r="L80" t="n">
-        <v>247.36</v>
+        <v>171.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>130.2</v>
+        <v>90.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-88.20999999999999</v>
+        <v>-61.19</v>
       </c>
       <c r="L81" t="n">
-        <v>157.26</v>
+        <v>109.08</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>140.46</v>
+        <v>99.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-182.6</v>
+        <v>-129.13</v>
       </c>
       <c r="L82" t="n">
-        <v>230.37</v>
+        <v>162.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>47.06</v>
+        <v>29.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-401</v>
+        <v>-247.84</v>
       </c>
       <c r="L83" t="n">
-        <v>403.75</v>
+        <v>249.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-90.73999999999999</v>
+        <v>-56.45</v>
       </c>
       <c r="K84" t="n">
-        <v>429.79</v>
+        <v>267.35</v>
       </c>
       <c r="L84" t="n">
-        <v>439.26</v>
+        <v>273.24</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-200.7</v>
+        <v>-135.11</v>
       </c>
       <c r="K85" t="n">
-        <v>212.96</v>
+        <v>143.36</v>
       </c>
       <c r="L85" t="n">
-        <v>292.62</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-352.61</v>
+        <v>-220.9</v>
       </c>
       <c r="K86" t="n">
-        <v>258.25</v>
+        <v>161.79</v>
       </c>
       <c r="L86" t="n">
-        <v>437.07</v>
+        <v>273.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-152.24</v>
+        <v>-93.70999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>495.37</v>
+        <v>304.91</v>
       </c>
       <c r="L87" t="n">
-        <v>518.23</v>
+        <v>318.98</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-205.5</v>
+        <v>-114.58</v>
       </c>
       <c r="K88" t="n">
-        <v>244.1</v>
+        <v>136.11</v>
       </c>
       <c r="L88" t="n">
-        <v>319.09</v>
+        <v>177.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.66</v>
+        <v>-14.5</v>
       </c>
       <c r="K14" t="n">
-        <v>48.98</v>
+        <v>48.45</v>
       </c>
       <c r="L14" t="n">
-        <v>51.13</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>86.13</v>
+        <v>85.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.41</v>
+        <v>-26.1</v>
       </c>
       <c r="L15" t="n">
-        <v>90.09</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="K16" t="n">
-        <v>-56.46</v>
+        <v>-55.25</v>
       </c>
       <c r="L16" t="n">
-        <v>56.46</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-106.3</v>
+        <v>-107.67</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.13</v>
+        <v>-31.53</v>
       </c>
       <c r="L17" t="n">
-        <v>110.76</v>
+        <v>112.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>107.64</v>
+        <v>108.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.58</v>
+        <v>-33.85</v>
       </c>
       <c r="L18" t="n">
-        <v>112.76</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>107.81</v>
+        <v>111.59</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.41</v>
+        <v>-19.06</v>
       </c>
       <c r="L19" t="n">
-        <v>109.37</v>
+        <v>113.21</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>130.25</v>
+        <v>136.21</v>
       </c>
       <c r="K20" t="n">
-        <v>-183.14</v>
+        <v>-191.51</v>
       </c>
       <c r="L20" t="n">
-        <v>224.73</v>
+        <v>235.01</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>33.36</v>
+        <v>35.1</v>
       </c>
       <c r="K21" t="n">
-        <v>68.39</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>76.09</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.21</v>
+        <v>-22.91</v>
       </c>
       <c r="K22" t="n">
-        <v>72.20999999999999</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>75.55</v>
+        <v>77.93000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-49.94</v>
+        <v>-54.89</v>
       </c>
       <c r="K23" t="n">
-        <v>47</v>
+        <v>51.65</v>
       </c>
       <c r="L23" t="n">
-        <v>68.58</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-198.78</v>
+        <v>-214.71</v>
       </c>
       <c r="K24" t="n">
-        <v>25.92</v>
+        <v>27.99</v>
       </c>
       <c r="L24" t="n">
-        <v>200.46</v>
+        <v>216.52</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-129.03</v>
+        <v>-139.48</v>
       </c>
       <c r="K25" t="n">
-        <v>182.65</v>
+        <v>197.44</v>
       </c>
       <c r="L25" t="n">
-        <v>223.63</v>
+        <v>241.74</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>240.36</v>
+        <v>259.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-130.35</v>
+        <v>-140.64</v>
       </c>
       <c r="L26" t="n">
-        <v>273.43</v>
+        <v>295.01</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-12.3</v>
+        <v>-13.68</v>
       </c>
       <c r="K27" t="n">
-        <v>206.27</v>
+        <v>229.45</v>
       </c>
       <c r="L27" t="n">
-        <v>206.64</v>
+        <v>229.86</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>146.4</v>
+        <v>161</v>
       </c>
       <c r="K28" t="n">
-        <v>230.69</v>
+        <v>253.69</v>
       </c>
       <c r="L28" t="n">
-        <v>273.22</v>
+        <v>300.47</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-98.84999999999999</v>
+        <v>-95.03</v>
       </c>
       <c r="K29" t="n">
-        <v>96.28</v>
+        <v>92.56</v>
       </c>
       <c r="L29" t="n">
-        <v>137.99</v>
+        <v>132.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-21.98</v>
+        <v>-21.3</v>
       </c>
       <c r="K30" t="n">
-        <v>141.75</v>
+        <v>137.42</v>
       </c>
       <c r="L30" t="n">
-        <v>143.45</v>
+        <v>139.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>80.91</v>
+        <v>79.2</v>
       </c>
       <c r="K31" t="n">
-        <v>28.81</v>
+        <v>28.2</v>
       </c>
       <c r="L31" t="n">
-        <v>85.89</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-81.45</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>81.90000000000001</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-69.23</v>
+        <v>-70.31</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.52</v>
+        <v>-28.97</v>
       </c>
       <c r="L33" t="n">
-        <v>74.88</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-140.12</v>
+        <v>-140.11</v>
       </c>
       <c r="K34" t="n">
         <v>21.62</v>
       </c>
       <c r="L34" t="n">
-        <v>141.78</v>
+        <v>141.77</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-133.89</v>
+        <v>-142.86</v>
       </c>
       <c r="K35" t="n">
-        <v>75.48</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>153.7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>44.51</v>
+        <v>46.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-63.48</v>
+        <v>-67</v>
       </c>
       <c r="L36" t="n">
-        <v>77.53</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-133.7</v>
+        <v>-142.22</v>
       </c>
       <c r="K37" t="n">
-        <v>74.84</v>
+        <v>79.61</v>
       </c>
       <c r="L37" t="n">
-        <v>153.22</v>
+        <v>162.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>161.96</v>
+        <v>174.92</v>
       </c>
       <c r="K38" t="n">
-        <v>80.81999999999999</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>181.01</v>
+        <v>195.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.31</v>
+        <v>-9.98</v>
       </c>
       <c r="K39" t="n">
-        <v>207.71</v>
+        <v>222.75</v>
       </c>
       <c r="L39" t="n">
-        <v>207.92</v>
+        <v>222.97</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-145.32</v>
+        <v>-157.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-273.73</v>
+        <v>-296.62</v>
       </c>
       <c r="L40" t="n">
-        <v>309.91</v>
+        <v>335.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>52.97</v>
+        <v>57.62</v>
       </c>
       <c r="K41" t="n">
-        <v>186.34</v>
+        <v>202.66</v>
       </c>
       <c r="L41" t="n">
-        <v>193.72</v>
+        <v>210.7</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-218.17</v>
+        <v>-240.06</v>
       </c>
       <c r="K42" t="n">
-        <v>-85.59999999999999</v>
+        <v>-94.19</v>
       </c>
       <c r="L42" t="n">
-        <v>234.36</v>
+        <v>257.88</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>105.39</v>
+        <v>115.12</v>
       </c>
       <c r="K43" t="n">
-        <v>135.89</v>
+        <v>148.45</v>
       </c>
       <c r="L43" t="n">
-        <v>171.97</v>
+        <v>187.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-61.49</v>
+        <v>-60.42</v>
       </c>
       <c r="K44" t="n">
-        <v>-62.34</v>
+        <v>-61.25</v>
       </c>
       <c r="L44" t="n">
-        <v>87.56</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>63.8</v>
+        <v>63.08</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.87</v>
+        <v>-32.5</v>
       </c>
       <c r="L45" t="n">
-        <v>71.77</v>
+        <v>70.95999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.97</v>
+        <v>-25.85</v>
       </c>
       <c r="K46" t="n">
-        <v>105.02</v>
+        <v>104.54</v>
       </c>
       <c r="L46" t="n">
-        <v>108.19</v>
+        <v>107.69</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>76.89</v>
+        <v>77.97</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.72</v>
+        <v>-59.55</v>
       </c>
       <c r="L47" t="n">
-        <v>96.75</v>
+        <v>98.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>25.42</v>
+        <v>25.94</v>
       </c>
       <c r="K48" t="n">
-        <v>-111.2</v>
+        <v>-113.52</v>
       </c>
       <c r="L48" t="n">
-        <v>114.07</v>
+        <v>116.45</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-109.3</v>
+        <v>-110.23</v>
       </c>
       <c r="K49" t="n">
-        <v>89.69</v>
+        <v>90.45</v>
       </c>
       <c r="L49" t="n">
-        <v>141.39</v>
+        <v>142.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.44</v>
+        <v>-22.45</v>
       </c>
       <c r="K50" t="n">
-        <v>68.47</v>
+        <v>71.72</v>
       </c>
       <c r="L50" t="n">
-        <v>71.73999999999999</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.04</v>
+        <v>-27.2</v>
       </c>
       <c r="K51" t="n">
-        <v>-245.29</v>
+        <v>-256.25</v>
       </c>
       <c r="L51" t="n">
-        <v>246.67</v>
+        <v>257.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-113.53</v>
+        <v>-119.45</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.33</v>
+        <v>-1.4</v>
       </c>
       <c r="L52" t="n">
-        <v>113.54</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>10.23</v>
+        <v>11.02</v>
       </c>
       <c r="K53" t="n">
-        <v>167.86</v>
+        <v>180.78</v>
       </c>
       <c r="L53" t="n">
-        <v>168.17</v>
+        <v>181.11</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-172.5</v>
+        <v>-187.92</v>
       </c>
       <c r="K54" t="n">
-        <v>-104.44</v>
+        <v>-113.77</v>
       </c>
       <c r="L54" t="n">
-        <v>201.66</v>
+        <v>219.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-166.2</v>
+        <v>-177.96</v>
       </c>
       <c r="K55" t="n">
-        <v>-59.61</v>
+        <v>-63.83</v>
       </c>
       <c r="L55" t="n">
-        <v>176.57</v>
+        <v>189.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>11.39</v>
+        <v>12.6</v>
       </c>
       <c r="K56" t="n">
-        <v>399.73</v>
+        <v>442.15</v>
       </c>
       <c r="L56" t="n">
-        <v>399.89</v>
+        <v>442.33</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>126.46</v>
+        <v>139.69</v>
       </c>
       <c r="K57" t="n">
-        <v>311.8</v>
+        <v>344.4</v>
       </c>
       <c r="L57" t="n">
-        <v>336.47</v>
+        <v>371.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>120.42</v>
+        <v>133.27</v>
       </c>
       <c r="K58" t="n">
-        <v>350.4</v>
+        <v>387.79</v>
       </c>
       <c r="L58" t="n">
-        <v>370.51</v>
+        <v>410.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>21.88</v>
+        <v>21.33</v>
       </c>
       <c r="K59" t="n">
-        <v>-112.66</v>
+        <v>-109.81</v>
       </c>
       <c r="L59" t="n">
-        <v>114.76</v>
+        <v>111.87</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-36.74</v>
+        <v>-35.7</v>
       </c>
       <c r="K60" t="n">
-        <v>51.54</v>
+        <v>50.08</v>
       </c>
       <c r="L60" t="n">
-        <v>63.3</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>67.17</v>
+        <v>65.42</v>
       </c>
       <c r="K61" t="n">
-        <v>29.72</v>
+        <v>28.95</v>
       </c>
       <c r="L61" t="n">
-        <v>73.45</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-81.64</v>
+        <v>-81.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-45.9</v>
+        <v>-45.95</v>
       </c>
       <c r="L62" t="n">
-        <v>93.66</v>
+        <v>93.76000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-77.95</v>
+        <v>-79.06999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-77.64</v>
+        <v>-78.75</v>
       </c>
       <c r="L63" t="n">
-        <v>110.02</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.67</v>
+        <v>-26.15</v>
       </c>
       <c r="K64" t="n">
-        <v>106.83</v>
+        <v>108.82</v>
       </c>
       <c r="L64" t="n">
-        <v>109.87</v>
+        <v>111.92</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>213.12</v>
+        <v>224.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-82.36</v>
+        <v>-86.69</v>
       </c>
       <c r="L65" t="n">
-        <v>228.48</v>
+        <v>240.51</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>7.25</v>
+        <v>7.69</v>
       </c>
       <c r="K66" t="n">
-        <v>-207.52</v>
+        <v>-220</v>
       </c>
       <c r="L66" t="n">
-        <v>207.64</v>
+        <v>220.13</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>83.77</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-120.96</v>
+        <v>-127.38</v>
       </c>
       <c r="L67" t="n">
-        <v>147.13</v>
+        <v>154.94</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-84.33</v>
+        <v>-92.79000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>222.7</v>
+        <v>245.02</v>
       </c>
       <c r="L68" t="n">
-        <v>238.13</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>112.31</v>
+        <v>122.55</v>
       </c>
       <c r="K69" t="n">
-        <v>138.66</v>
+        <v>151.3</v>
       </c>
       <c r="L69" t="n">
-        <v>178.44</v>
+        <v>194.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>48.24</v>
+        <v>52.1</v>
       </c>
       <c r="K70" t="n">
-        <v>182.05</v>
+        <v>196.62</v>
       </c>
       <c r="L70" t="n">
-        <v>188.34</v>
+        <v>203.4</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-273.05</v>
+        <v>-301.74</v>
       </c>
       <c r="K71" t="n">
-        <v>95.72</v>
+        <v>105.78</v>
       </c>
       <c r="L71" t="n">
-        <v>289.34</v>
+        <v>319.75</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>140.6</v>
+        <v>155.65</v>
       </c>
       <c r="K72" t="n">
-        <v>-179.73</v>
+        <v>-198.96</v>
       </c>
       <c r="L72" t="n">
-        <v>228.19</v>
+        <v>252.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>253.43</v>
+        <v>274.12</v>
       </c>
       <c r="K73" t="n">
-        <v>202.99</v>
+        <v>219.56</v>
       </c>
       <c r="L73" t="n">
-        <v>324.7</v>
+        <v>351.21</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.49</v>
+        <v>-47.68</v>
       </c>
       <c r="K74" t="n">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
       <c r="L74" t="n">
-        <v>67.88</v>
+        <v>66.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.66</v>
+        <v>-13.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-72.67</v>
+        <v>-71.64</v>
       </c>
       <c r="L75" t="n">
-        <v>73.95</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>47.85</v>
+        <v>46.56</v>
       </c>
       <c r="K76" t="n">
-        <v>47.89</v>
+        <v>46.6</v>
       </c>
       <c r="L76" t="n">
-        <v>67.69</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>100.65</v>
+        <v>101.61</v>
       </c>
       <c r="K77" t="n">
-        <v>64.34999999999999</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>119.46</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>77.47</v>
+        <v>78.17</v>
       </c>
       <c r="K78" t="n">
-        <v>46.88</v>
+        <v>47.3</v>
       </c>
       <c r="L78" t="n">
-        <v>90.55</v>
+        <v>91.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-70.56</v>
+        <v>-70.98999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-35.78</v>
+        <v>-36</v>
       </c>
       <c r="L79" t="n">
-        <v>79.11</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>112.35</v>
+        <v>118.5</v>
       </c>
       <c r="K80" t="n">
-        <v>-129.55</v>
+        <v>-136.64</v>
       </c>
       <c r="L80" t="n">
-        <v>171.49</v>
+        <v>180.87</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>90.31</v>
+        <v>94.92</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.19</v>
+        <v>-64.31</v>
       </c>
       <c r="L81" t="n">
-        <v>109.08</v>
+        <v>114.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>99.33</v>
+        <v>104.8</v>
       </c>
       <c r="K82" t="n">
-        <v>-129.13</v>
+        <v>-136.25</v>
       </c>
       <c r="L82" t="n">
-        <v>162.91</v>
+        <v>171.89</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>29.09</v>
+        <v>31.38</v>
       </c>
       <c r="K83" t="n">
-        <v>-247.84</v>
+        <v>-267.39</v>
       </c>
       <c r="L83" t="n">
-        <v>249.54</v>
+        <v>269.23</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-56.45</v>
+        <v>-59.86</v>
       </c>
       <c r="K84" t="n">
-        <v>267.35</v>
+        <v>283.52</v>
       </c>
       <c r="L84" t="n">
-        <v>273.24</v>
+        <v>289.77</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-135.11</v>
+        <v>-145.25</v>
       </c>
       <c r="K85" t="n">
-        <v>143.36</v>
+        <v>154.12</v>
       </c>
       <c r="L85" t="n">
-        <v>197</v>
+        <v>211.78</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-220.9</v>
+        <v>-238.36</v>
       </c>
       <c r="K86" t="n">
-        <v>161.79</v>
+        <v>174.58</v>
       </c>
       <c r="L86" t="n">
-        <v>273.81</v>
+        <v>295.45</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-93.70999999999999</v>
+        <v>-99.95</v>
       </c>
       <c r="K87" t="n">
-        <v>304.91</v>
+        <v>325.23</v>
       </c>
       <c r="L87" t="n">
-        <v>318.98</v>
+        <v>340.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-114.58</v>
+        <v>-125.51</v>
       </c>
       <c r="K88" t="n">
-        <v>136.11</v>
+        <v>149.09</v>
       </c>
       <c r="L88" t="n">
-        <v>177.92</v>
+        <v>194.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.5</v>
+        <v>-10.34</v>
       </c>
       <c r="K14" t="n">
-        <v>48.45</v>
+        <v>34.53</v>
       </c>
       <c r="L14" t="n">
-        <v>50.57</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>85.12</v>
+        <v>58.74</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.1</v>
+        <v>-18.01</v>
       </c>
       <c r="L15" t="n">
-        <v>89.03</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.59</v>
+        <v>-0.38</v>
       </c>
       <c r="K16" t="n">
-        <v>-55.25</v>
+        <v>-35.85</v>
       </c>
       <c r="L16" t="n">
-        <v>55.26</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-107.67</v>
+        <v>-70.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.53</v>
+        <v>-20.62</v>
       </c>
       <c r="L17" t="n">
-        <v>112.19</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>108.52</v>
+        <v>71.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-33.85</v>
+        <v>-22.31</v>
       </c>
       <c r="L18" t="n">
-        <v>113.68</v>
+        <v>74.92</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>111.59</v>
+        <v>71.89</v>
       </c>
       <c r="K19" t="n">
-        <v>-19.06</v>
+        <v>-12.28</v>
       </c>
       <c r="L19" t="n">
-        <v>113.21</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>136.21</v>
+        <v>82.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-191.51</v>
+        <v>-116.38</v>
       </c>
       <c r="L20" t="n">
-        <v>235.01</v>
+        <v>142.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>35.1</v>
+        <v>25.2</v>
       </c>
       <c r="K21" t="n">
-        <v>71.95999999999999</v>
+        <v>51.67</v>
       </c>
       <c r="L21" t="n">
-        <v>80.06</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.91</v>
+        <v>-15.84</v>
       </c>
       <c r="K22" t="n">
-        <v>74.48999999999999</v>
+        <v>51.52</v>
       </c>
       <c r="L22" t="n">
-        <v>77.93000000000001</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-54.89</v>
+        <v>-14.75</v>
       </c>
       <c r="K23" t="n">
-        <v>51.65</v>
+        <v>13.88</v>
       </c>
       <c r="L23" t="n">
-        <v>75.37</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-214.71</v>
+        <v>-144.34</v>
       </c>
       <c r="K24" t="n">
-        <v>27.99</v>
+        <v>18.82</v>
       </c>
       <c r="L24" t="n">
-        <v>216.52</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-139.48</v>
+        <v>-96.95</v>
       </c>
       <c r="K25" t="n">
-        <v>197.44</v>
+        <v>137.24</v>
       </c>
       <c r="L25" t="n">
-        <v>241.74</v>
+        <v>168.03</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>259.34</v>
+        <v>178.91</v>
       </c>
       <c r="K26" t="n">
-        <v>-140.64</v>
+        <v>-97.02</v>
       </c>
       <c r="L26" t="n">
-        <v>295.01</v>
+        <v>203.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.68</v>
+        <v>-8.92</v>
       </c>
       <c r="K27" t="n">
-        <v>229.45</v>
+        <v>149.58</v>
       </c>
       <c r="L27" t="n">
-        <v>229.86</v>
+        <v>149.84</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>161</v>
+        <v>91.45</v>
       </c>
       <c r="K28" t="n">
-        <v>253.69</v>
+        <v>144.1</v>
       </c>
       <c r="L28" t="n">
-        <v>300.47</v>
+        <v>170.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-95.03</v>
+        <v>-58.07</v>
       </c>
       <c r="K29" t="n">
-        <v>92.56</v>
+        <v>56.56</v>
       </c>
       <c r="L29" t="n">
-        <v>132.66</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-21.3</v>
+        <v>-13.05</v>
       </c>
       <c r="K30" t="n">
-        <v>137.42</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>139.06</v>
+        <v>85.15000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>79.2</v>
+        <v>49.13</v>
       </c>
       <c r="K31" t="n">
-        <v>28.2</v>
+        <v>17.49</v>
       </c>
       <c r="L31" t="n">
-        <v>84.08</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-8.6</v>
+        <v>-5.52</v>
       </c>
       <c r="K32" t="n">
-        <v>-82.40000000000001</v>
+        <v>-52.82</v>
       </c>
       <c r="L32" t="n">
-        <v>82.84999999999999</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-70.31</v>
+        <v>-46.71</v>
       </c>
       <c r="K33" t="n">
-        <v>-28.97</v>
+        <v>-19.24</v>
       </c>
       <c r="L33" t="n">
-        <v>76.05</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-140.11</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>21.62</v>
+        <v>13.17</v>
       </c>
       <c r="L34" t="n">
-        <v>141.77</v>
+        <v>86.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-142.86</v>
+        <v>-99.47</v>
       </c>
       <c r="K35" t="n">
-        <v>80.54000000000001</v>
+        <v>56.08</v>
       </c>
       <c r="L35" t="n">
-        <v>164</v>
+        <v>114.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>46.98</v>
+        <v>11.12</v>
       </c>
       <c r="K36" t="n">
-        <v>-67</v>
+        <v>-15.86</v>
       </c>
       <c r="L36" t="n">
-        <v>81.83</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-142.22</v>
+        <v>-79.73</v>
       </c>
       <c r="K37" t="n">
-        <v>79.61</v>
+        <v>44.63</v>
       </c>
       <c r="L37" t="n">
-        <v>162.98</v>
+        <v>91.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>174.92</v>
+        <v>116.2</v>
       </c>
       <c r="K38" t="n">
-        <v>87.29000000000001</v>
+        <v>57.99</v>
       </c>
       <c r="L38" t="n">
-        <v>195.49</v>
+        <v>129.87</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.98</v>
+        <v>-6.38</v>
       </c>
       <c r="K39" t="n">
-        <v>222.75</v>
+        <v>142.34</v>
       </c>
       <c r="L39" t="n">
-        <v>222.97</v>
+        <v>142.48</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-157.47</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-296.62</v>
+        <v>-155.13</v>
       </c>
       <c r="L40" t="n">
-        <v>335.83</v>
+        <v>175.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>57.62</v>
+        <v>36.75</v>
       </c>
       <c r="K41" t="n">
-        <v>202.66</v>
+        <v>129.27</v>
       </c>
       <c r="L41" t="n">
-        <v>210.7</v>
+        <v>134.39</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-240.06</v>
+        <v>-174.09</v>
       </c>
       <c r="K42" t="n">
-        <v>-94.19</v>
+        <v>-68.31</v>
       </c>
       <c r="L42" t="n">
-        <v>257.88</v>
+        <v>187.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>115.12</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>148.45</v>
+        <v>101.75</v>
       </c>
       <c r="L43" t="n">
-        <v>187.85</v>
+        <v>128.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-60.42</v>
+        <v>-37.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.25</v>
+        <v>-37.99</v>
       </c>
       <c r="L44" t="n">
-        <v>86.03</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>63.08</v>
+        <v>42.39</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.5</v>
+        <v>-21.84</v>
       </c>
       <c r="L45" t="n">
-        <v>70.95999999999999</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.85</v>
+        <v>-16.49</v>
       </c>
       <c r="K46" t="n">
-        <v>104.54</v>
+        <v>66.66</v>
       </c>
       <c r="L46" t="n">
-        <v>107.69</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>77.97</v>
+        <v>48.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-59.55</v>
+        <v>-37.36</v>
       </c>
       <c r="L47" t="n">
-        <v>98.11</v>
+        <v>61.55</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>25.94</v>
+        <v>16.05</v>
       </c>
       <c r="K48" t="n">
-        <v>-113.52</v>
+        <v>-70.23999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>116.45</v>
+        <v>72.05</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-110.23</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>90.45</v>
+        <v>57.7</v>
       </c>
       <c r="L49" t="n">
-        <v>142.59</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-22.45</v>
+        <v>-13.64</v>
       </c>
       <c r="K50" t="n">
-        <v>71.72</v>
+        <v>43.56</v>
       </c>
       <c r="L50" t="n">
-        <v>75.15000000000001</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-27.2</v>
+        <v>-15.08</v>
       </c>
       <c r="K51" t="n">
-        <v>-256.25</v>
+        <v>-142.05</v>
       </c>
       <c r="L51" t="n">
-        <v>257.69</v>
+        <v>142.85</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-119.45</v>
+        <v>-84.88</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.4</v>
+        <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>119.46</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>11.02</v>
+        <v>7.04</v>
       </c>
       <c r="K53" t="n">
-        <v>180.78</v>
+        <v>115.52</v>
       </c>
       <c r="L53" t="n">
-        <v>181.11</v>
+        <v>115.74</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-187.92</v>
+        <v>-121.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.77</v>
+        <v>-73.75</v>
       </c>
       <c r="L54" t="n">
-        <v>219.68</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-177.96</v>
+        <v>-115.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-63.83</v>
+        <v>-41.45</v>
       </c>
       <c r="L55" t="n">
-        <v>189.06</v>
+        <v>122.78</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>12.6</v>
+        <v>8.02</v>
       </c>
       <c r="K56" t="n">
-        <v>442.15</v>
+        <v>281.47</v>
       </c>
       <c r="L56" t="n">
-        <v>442.33</v>
+        <v>281.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>139.69</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>344.4</v>
+        <v>226.8</v>
       </c>
       <c r="L57" t="n">
-        <v>371.65</v>
+        <v>244.75</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>133.27</v>
+        <v>92.55</v>
       </c>
       <c r="K58" t="n">
-        <v>387.79</v>
+        <v>269.3</v>
       </c>
       <c r="L58" t="n">
-        <v>410.05</v>
+        <v>284.76</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>21.33</v>
+        <v>13.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-109.81</v>
+        <v>-68.12</v>
       </c>
       <c r="L59" t="n">
-        <v>111.87</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-35.7</v>
+        <v>-23.28</v>
       </c>
       <c r="K60" t="n">
-        <v>50.08</v>
+        <v>32.66</v>
       </c>
       <c r="L60" t="n">
-        <v>61.5</v>
+        <v>40.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>65.42</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>28.95</v>
+        <v>19.03</v>
       </c>
       <c r="L61" t="n">
-        <v>71.54000000000001</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-81.73</v>
+        <v>-49.57</v>
       </c>
       <c r="K62" t="n">
-        <v>-45.95</v>
+        <v>-27.87</v>
       </c>
       <c r="L62" t="n">
-        <v>93.76000000000001</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-79.06999999999999</v>
+        <v>-47.75</v>
       </c>
       <c r="K63" t="n">
-        <v>-78.75</v>
+        <v>-47.55</v>
       </c>
       <c r="L63" t="n">
-        <v>111.59</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.15</v>
+        <v>-16.04</v>
       </c>
       <c r="K64" t="n">
-        <v>108.82</v>
+        <v>66.73</v>
       </c>
       <c r="L64" t="n">
-        <v>111.92</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>224.34</v>
+        <v>131.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-86.69</v>
+        <v>-50.71</v>
       </c>
       <c r="L65" t="n">
-        <v>240.51</v>
+        <v>140.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>7.69</v>
+        <v>4.32</v>
       </c>
       <c r="K66" t="n">
-        <v>-220</v>
+        <v>-123.61</v>
       </c>
       <c r="L66" t="n">
-        <v>220.13</v>
+        <v>123.69</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>88.20999999999999</v>
+        <v>56.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-127.38</v>
+        <v>-81.81</v>
       </c>
       <c r="L67" t="n">
-        <v>154.94</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-92.79000000000001</v>
+        <v>-61.28</v>
       </c>
       <c r="K68" t="n">
-        <v>245.02</v>
+        <v>161.83</v>
       </c>
       <c r="L68" t="n">
-        <v>262</v>
+        <v>173.05</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>122.55</v>
+        <v>81.73</v>
       </c>
       <c r="K69" t="n">
-        <v>151.3</v>
+        <v>100.9</v>
       </c>
       <c r="L69" t="n">
-        <v>194.7</v>
+        <v>129.85</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>52.1</v>
+        <v>33.12</v>
       </c>
       <c r="K70" t="n">
-        <v>196.62</v>
+        <v>124.99</v>
       </c>
       <c r="L70" t="n">
-        <v>203.4</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-301.74</v>
+        <v>-176.93</v>
       </c>
       <c r="K71" t="n">
-        <v>105.78</v>
+        <v>62.03</v>
       </c>
       <c r="L71" t="n">
-        <v>319.75</v>
+        <v>187.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>155.65</v>
+        <v>97.02</v>
       </c>
       <c r="K72" t="n">
-        <v>-198.96</v>
+        <v>-124.02</v>
       </c>
       <c r="L72" t="n">
-        <v>252.61</v>
+        <v>157.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>274.12</v>
+        <v>169.59</v>
       </c>
       <c r="K73" t="n">
-        <v>219.56</v>
+        <v>135.84</v>
       </c>
       <c r="L73" t="n">
-        <v>351.21</v>
+        <v>217.29</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-47.68</v>
+        <v>-27.78</v>
       </c>
       <c r="K74" t="n">
-        <v>46.7</v>
+        <v>27.21</v>
       </c>
       <c r="L74" t="n">
-        <v>66.73999999999999</v>
+        <v>38.88</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.46</v>
+        <v>-7.75</v>
       </c>
       <c r="K75" t="n">
-        <v>-71.64</v>
+        <v>-41.24</v>
       </c>
       <c r="L75" t="n">
-        <v>72.89</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>46.56</v>
+        <v>28.82</v>
       </c>
       <c r="K76" t="n">
-        <v>46.6</v>
+        <v>28.84</v>
       </c>
       <c r="L76" t="n">
-        <v>65.87</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>101.61</v>
+        <v>58.77</v>
       </c>
       <c r="K77" t="n">
-        <v>64.95999999999999</v>
+        <v>37.57</v>
       </c>
       <c r="L77" t="n">
-        <v>120.6</v>
+        <v>69.75</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>78.17</v>
+        <v>44.52</v>
       </c>
       <c r="K78" t="n">
-        <v>47.3</v>
+        <v>26.94</v>
       </c>
       <c r="L78" t="n">
-        <v>91.37</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-70.98999999999999</v>
+        <v>-44.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-36</v>
+        <v>-22.69</v>
       </c>
       <c r="L79" t="n">
-        <v>79.59</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>118.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-136.64</v>
+        <v>-86.02</v>
       </c>
       <c r="L80" t="n">
-        <v>180.87</v>
+        <v>113.86</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>94.92</v>
+        <v>55.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-64.31</v>
+        <v>-37.62</v>
       </c>
       <c r="L81" t="n">
-        <v>114.65</v>
+        <v>67.06</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>104.8</v>
+        <v>58.88</v>
       </c>
       <c r="K82" t="n">
-        <v>-136.25</v>
+        <v>-76.55</v>
       </c>
       <c r="L82" t="n">
-        <v>171.89</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>31.38</v>
+        <v>18.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-267.39</v>
+        <v>-160.69</v>
       </c>
       <c r="L83" t="n">
-        <v>269.23</v>
+        <v>161.79</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-59.86</v>
+        <v>-33.01</v>
       </c>
       <c r="K84" t="n">
-        <v>283.52</v>
+        <v>156.36</v>
       </c>
       <c r="L84" t="n">
-        <v>289.77</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-145.25</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>154.12</v>
+        <v>100.65</v>
       </c>
       <c r="L85" t="n">
-        <v>211.78</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-238.36</v>
+        <v>-153.54</v>
       </c>
       <c r="K86" t="n">
-        <v>174.58</v>
+        <v>112.45</v>
       </c>
       <c r="L86" t="n">
-        <v>295.45</v>
+        <v>190.31</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-99.95</v>
+        <v>-61.38</v>
       </c>
       <c r="K87" t="n">
-        <v>325.23</v>
+        <v>199.73</v>
       </c>
       <c r="L87" t="n">
-        <v>340.24</v>
+        <v>208.95</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-125.51</v>
+        <v>-80.84</v>
       </c>
       <c r="K88" t="n">
-        <v>149.09</v>
+        <v>96.03</v>
       </c>
       <c r="L88" t="n">
-        <v>194.88</v>
+        <v>125.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.34</v>
+        <v>-10.77</v>
       </c>
       <c r="K14" t="n">
-        <v>34.53</v>
+        <v>35.97</v>
       </c>
       <c r="L14" t="n">
-        <v>36.05</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>58.74</v>
+        <v>57.45</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.01</v>
+        <v>-17.62</v>
       </c>
       <c r="L15" t="n">
-        <v>61.44</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>-35.85</v>
+        <v>-37.81</v>
       </c>
       <c r="L16" t="n">
-        <v>35.85</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-70.42</v>
+        <v>-69.67</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.62</v>
+        <v>-20.4</v>
       </c>
       <c r="L17" t="n">
-        <v>73.37</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>71.52</v>
+        <v>70.53</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.31</v>
+        <v>-22</v>
       </c>
       <c r="L18" t="n">
-        <v>74.92</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>71.89</v>
+        <v>71.78</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.28</v>
+        <v>-12.26</v>
       </c>
       <c r="L19" t="n">
-        <v>72.93000000000001</v>
+        <v>72.81999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>82.77</v>
+        <v>79.44</v>
       </c>
       <c r="K20" t="n">
-        <v>-116.38</v>
+        <v>-111.7</v>
       </c>
       <c r="L20" t="n">
-        <v>142.81</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>25.2</v>
+        <v>27.01</v>
       </c>
       <c r="K21" t="n">
-        <v>51.67</v>
+        <v>55.38</v>
       </c>
       <c r="L21" t="n">
-        <v>57.49</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-15.84</v>
+        <v>-17.01</v>
       </c>
       <c r="K22" t="n">
-        <v>51.52</v>
+        <v>55.33</v>
       </c>
       <c r="L22" t="n">
-        <v>53.9</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-14.75</v>
+        <v>-14.48</v>
       </c>
       <c r="K23" t="n">
-        <v>13.88</v>
+        <v>13.63</v>
       </c>
       <c r="L23" t="n">
-        <v>20.26</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-144.34</v>
+        <v>-141.51</v>
       </c>
       <c r="K24" t="n">
-        <v>18.82</v>
+        <v>18.45</v>
       </c>
       <c r="L24" t="n">
-        <v>145.56</v>
+        <v>142.71</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-96.95</v>
+        <v>-93.59</v>
       </c>
       <c r="K25" t="n">
-        <v>137.24</v>
+        <v>132.48</v>
       </c>
       <c r="L25" t="n">
-        <v>168.03</v>
+        <v>162.21</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>178.91</v>
+        <v>175.23</v>
       </c>
       <c r="K26" t="n">
-        <v>-97.02</v>
+        <v>-95.02</v>
       </c>
       <c r="L26" t="n">
-        <v>203.53</v>
+        <v>199.33</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.92</v>
+        <v>-9.23</v>
       </c>
       <c r="K27" t="n">
-        <v>149.58</v>
+        <v>154.81</v>
       </c>
       <c r="L27" t="n">
-        <v>149.84</v>
+        <v>155.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>91.45</v>
+        <v>93.5</v>
       </c>
       <c r="K28" t="n">
-        <v>144.1</v>
+        <v>147.33</v>
       </c>
       <c r="L28" t="n">
-        <v>170.66</v>
+        <v>174.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-58.07</v>
+        <v>-55.47</v>
       </c>
       <c r="K29" t="n">
-        <v>56.56</v>
+        <v>54.02</v>
       </c>
       <c r="L29" t="n">
-        <v>81.06</v>
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.05</v>
+        <v>-12.42</v>
       </c>
       <c r="K30" t="n">
-        <v>84.15000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>85.15000000000001</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>49.13</v>
+        <v>49.42</v>
       </c>
       <c r="K31" t="n">
-        <v>17.49</v>
+        <v>17.6</v>
       </c>
       <c r="L31" t="n">
-        <v>52.15</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.52</v>
+        <v>-5.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-52.82</v>
+        <v>-54.61</v>
       </c>
       <c r="L32" t="n">
-        <v>53.11</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.71</v>
+        <v>-48.79</v>
       </c>
       <c r="K33" t="n">
-        <v>-19.24</v>
+        <v>-20.1</v>
       </c>
       <c r="L33" t="n">
-        <v>50.51</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.34999999999999</v>
+        <v>-82.94</v>
       </c>
       <c r="K34" t="n">
-        <v>13.17</v>
+        <v>12.8</v>
       </c>
       <c r="L34" t="n">
-        <v>86.36</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-99.47</v>
+        <v>-97.70999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>56.08</v>
+        <v>55.09</v>
       </c>
       <c r="L35" t="n">
-        <v>114.19</v>
+        <v>112.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>11.12</v>
+        <v>10.91</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.86</v>
+        <v>-15.56</v>
       </c>
       <c r="L36" t="n">
-        <v>19.37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-79.73</v>
+        <v>-80.63</v>
       </c>
       <c r="K37" t="n">
-        <v>44.63</v>
+        <v>45.13</v>
       </c>
       <c r="L37" t="n">
-        <v>91.37</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>116.2</v>
+        <v>115.77</v>
       </c>
       <c r="K38" t="n">
-        <v>57.99</v>
+        <v>57.77</v>
       </c>
       <c r="L38" t="n">
-        <v>129.87</v>
+        <v>129.38</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.38</v>
+        <v>-6.31</v>
       </c>
       <c r="K39" t="n">
-        <v>142.34</v>
+        <v>140.79</v>
       </c>
       <c r="L39" t="n">
-        <v>142.48</v>
+        <v>140.93</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-82.34999999999999</v>
+        <v>-81.20999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-155.13</v>
+        <v>-152.97</v>
       </c>
       <c r="L40" t="n">
-        <v>175.63</v>
+        <v>173.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>36.75</v>
+        <v>38.44</v>
       </c>
       <c r="K41" t="n">
-        <v>129.27</v>
+        <v>135.22</v>
       </c>
       <c r="L41" t="n">
-        <v>134.39</v>
+        <v>140.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-174.09</v>
+        <v>-173.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-68.31</v>
+        <v>-68.02</v>
       </c>
       <c r="L42" t="n">
-        <v>187.01</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>78.90000000000001</v>
+        <v>82.38</v>
       </c>
       <c r="K43" t="n">
-        <v>101.75</v>
+        <v>106.23</v>
       </c>
       <c r="L43" t="n">
-        <v>128.76</v>
+        <v>134.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-37.48</v>
+        <v>-31.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.99</v>
+        <v>-32.36</v>
       </c>
       <c r="L44" t="n">
-        <v>53.37</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>42.39</v>
+        <v>42.6</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.84</v>
+        <v>-21.95</v>
       </c>
       <c r="L45" t="n">
-        <v>47.69</v>
+        <v>47.93</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.49</v>
+        <v>-16</v>
       </c>
       <c r="K46" t="n">
-        <v>66.66</v>
+        <v>64.69</v>
       </c>
       <c r="L46" t="n">
-        <v>68.67</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>48.92</v>
+        <v>49.11</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.36</v>
+        <v>-37.51</v>
       </c>
       <c r="L47" t="n">
-        <v>61.55</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>16.05</v>
+        <v>15.95</v>
       </c>
       <c r="K48" t="n">
-        <v>-70.23999999999999</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>72.05</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-70.31999999999999</v>
+        <v>-67.63</v>
       </c>
       <c r="K49" t="n">
-        <v>57.7</v>
+        <v>55.49</v>
       </c>
       <c r="L49" t="n">
-        <v>90.95999999999999</v>
+        <v>87.48</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.64</v>
+        <v>-13.3</v>
       </c>
       <c r="K50" t="n">
-        <v>43.56</v>
+        <v>42.49</v>
       </c>
       <c r="L50" t="n">
-        <v>45.64</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.08</v>
+        <v>-14.41</v>
       </c>
       <c r="K51" t="n">
-        <v>-142.05</v>
+        <v>-135.74</v>
       </c>
       <c r="L51" t="n">
-        <v>142.85</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-84.88</v>
+        <v>-85.03</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>84.89</v>
+        <v>85.04000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>7.04</v>
+        <v>7.13</v>
       </c>
       <c r="K53" t="n">
-        <v>115.52</v>
+        <v>117.06</v>
       </c>
       <c r="L53" t="n">
-        <v>115.74</v>
+        <v>117.28</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-121.82</v>
+        <v>-120.5</v>
       </c>
       <c r="K54" t="n">
-        <v>-73.75</v>
+        <v>-72.95</v>
       </c>
       <c r="L54" t="n">
-        <v>142.41</v>
+        <v>140.86</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-115.57</v>
+        <v>-115.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-41.45</v>
+        <v>-41.33</v>
       </c>
       <c r="L55" t="n">
-        <v>122.78</v>
+        <v>122.43</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>8.02</v>
+        <v>7.68</v>
       </c>
       <c r="K56" t="n">
-        <v>281.47</v>
+        <v>269.6</v>
       </c>
       <c r="L56" t="n">
-        <v>281.58</v>
+        <v>269.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>91.98999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="K57" t="n">
-        <v>226.8</v>
+        <v>218.78</v>
       </c>
       <c r="L57" t="n">
-        <v>244.75</v>
+        <v>236.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>92.55</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>269.3</v>
+        <v>257</v>
       </c>
       <c r="L58" t="n">
-        <v>284.76</v>
+        <v>271.75</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>13.23</v>
+        <v>12.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-68.12</v>
+        <v>-65.84</v>
       </c>
       <c r="L59" t="n">
-        <v>69.39</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.28</v>
+        <v>-23.81</v>
       </c>
       <c r="K60" t="n">
-        <v>32.66</v>
+        <v>33.4</v>
       </c>
       <c r="L60" t="n">
-        <v>40.11</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>43</v>
+        <v>43.11</v>
       </c>
       <c r="K61" t="n">
-        <v>19.03</v>
+        <v>19.07</v>
       </c>
       <c r="L61" t="n">
-        <v>47.03</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-49.57</v>
+        <v>-50.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-27.87</v>
+        <v>-28.35</v>
       </c>
       <c r="L62" t="n">
-        <v>56.87</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.75</v>
+        <v>-47.69</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.55</v>
+        <v>-47.5</v>
       </c>
       <c r="L63" t="n">
-        <v>67.39</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.04</v>
+        <v>-16.06</v>
       </c>
       <c r="K64" t="n">
-        <v>66.73</v>
+        <v>66.84</v>
       </c>
       <c r="L64" t="n">
-        <v>68.63</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>131.23</v>
+        <v>126.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-50.71</v>
+        <v>-48.71</v>
       </c>
       <c r="L65" t="n">
-        <v>140.69</v>
+        <v>135.14</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>4.32</v>
+        <v>4.23</v>
       </c>
       <c r="K66" t="n">
-        <v>-123.61</v>
+        <v>-120.98</v>
       </c>
       <c r="L66" t="n">
-        <v>123.69</v>
+        <v>121.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>56.65</v>
+        <v>56.23</v>
       </c>
       <c r="K67" t="n">
-        <v>-81.81</v>
+        <v>-81.2</v>
       </c>
       <c r="L67" t="n">
-        <v>99.51000000000001</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-61.28</v>
+        <v>-59.45</v>
       </c>
       <c r="K68" t="n">
-        <v>161.83</v>
+        <v>156.98</v>
       </c>
       <c r="L68" t="n">
-        <v>173.05</v>
+        <v>167.86</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>81.73</v>
+        <v>81.2</v>
       </c>
       <c r="K69" t="n">
-        <v>100.9</v>
+        <v>100.24</v>
       </c>
       <c r="L69" t="n">
-        <v>129.85</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>33.12</v>
+        <v>33.06</v>
       </c>
       <c r="K70" t="n">
-        <v>124.99</v>
+        <v>124.78</v>
       </c>
       <c r="L70" t="n">
-        <v>129.3</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-176.93</v>
+        <v>-177.73</v>
       </c>
       <c r="K71" t="n">
-        <v>62.03</v>
+        <v>62.31</v>
       </c>
       <c r="L71" t="n">
-        <v>187.49</v>
+        <v>188.34</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>97.02</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-124.02</v>
+        <v>-127.13</v>
       </c>
       <c r="L72" t="n">
-        <v>157.46</v>
+        <v>161.42</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>169.59</v>
+        <v>165.55</v>
       </c>
       <c r="K73" t="n">
-        <v>135.84</v>
+        <v>132.6</v>
       </c>
       <c r="L73" t="n">
-        <v>217.29</v>
+        <v>212.1</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.78</v>
+        <v>-29.46</v>
       </c>
       <c r="K74" t="n">
-        <v>27.21</v>
+        <v>28.85</v>
       </c>
       <c r="L74" t="n">
-        <v>38.88</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.75</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.24</v>
+        <v>-43.32</v>
       </c>
       <c r="L75" t="n">
-        <v>41.96</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.82</v>
+        <v>29.75</v>
       </c>
       <c r="K76" t="n">
-        <v>28.84</v>
+        <v>29.77</v>
       </c>
       <c r="L76" t="n">
-        <v>40.77</v>
+        <v>42.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>58.77</v>
+        <v>58.61</v>
       </c>
       <c r="K77" t="n">
-        <v>37.57</v>
+        <v>37.47</v>
       </c>
       <c r="L77" t="n">
-        <v>69.75</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>44.52</v>
+        <v>46.07</v>
       </c>
       <c r="K78" t="n">
-        <v>26.94</v>
+        <v>27.87</v>
       </c>
       <c r="L78" t="n">
-        <v>52.04</v>
+        <v>53.84</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-44.75</v>
+        <v>-46.26</v>
       </c>
       <c r="K79" t="n">
-        <v>-22.69</v>
+        <v>-23.46</v>
       </c>
       <c r="L79" t="n">
-        <v>50.17</v>
+        <v>51.87</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>74.59999999999999</v>
+        <v>73.05</v>
       </c>
       <c r="K80" t="n">
-        <v>-86.02</v>
+        <v>-84.23</v>
       </c>
       <c r="L80" t="n">
-        <v>113.86</v>
+        <v>111.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.52</v>
+        <v>58.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.62</v>
+        <v>-39.58</v>
       </c>
       <c r="L81" t="n">
-        <v>67.06</v>
+        <v>70.56999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>58.88</v>
+        <v>58.86</v>
       </c>
       <c r="K82" t="n">
-        <v>-76.55</v>
+        <v>-76.52</v>
       </c>
       <c r="L82" t="n">
-        <v>96.58</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>18.86</v>
+        <v>18.49</v>
       </c>
       <c r="K83" t="n">
-        <v>-160.69</v>
+        <v>-157.51</v>
       </c>
       <c r="L83" t="n">
-        <v>161.79</v>
+        <v>158.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-33.01</v>
+        <v>-32.54</v>
       </c>
       <c r="K84" t="n">
-        <v>156.36</v>
+        <v>154.13</v>
       </c>
       <c r="L84" t="n">
-        <v>159.8</v>
+        <v>157.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-94.84999999999999</v>
+        <v>-93.48</v>
       </c>
       <c r="K85" t="n">
-        <v>100.65</v>
+        <v>99.19</v>
       </c>
       <c r="L85" t="n">
-        <v>138.3</v>
+        <v>136.3</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-153.54</v>
+        <v>-151.48</v>
       </c>
       <c r="K86" t="n">
-        <v>112.45</v>
+        <v>110.95</v>
       </c>
       <c r="L86" t="n">
-        <v>190.31</v>
+        <v>187.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-61.38</v>
+        <v>-60.01</v>
       </c>
       <c r="K87" t="n">
-        <v>199.73</v>
+        <v>195.27</v>
       </c>
       <c r="L87" t="n">
-        <v>208.95</v>
+        <v>204.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-80.84</v>
+        <v>-85.17</v>
       </c>
       <c r="K88" t="n">
-        <v>96.03</v>
+        <v>101.18</v>
       </c>
       <c r="L88" t="n">
-        <v>125.53</v>
+        <v>132.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.77</v>
+        <v>-11.26</v>
       </c>
       <c r="K14" t="n">
-        <v>35.97</v>
+        <v>37.62</v>
       </c>
       <c r="L14" t="n">
-        <v>37.55</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>57.45</v>
+        <v>55.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.62</v>
+        <v>-17.17</v>
       </c>
       <c r="L15" t="n">
-        <v>60.1</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4</v>
+        <v>-0.43</v>
       </c>
       <c r="K16" t="n">
-        <v>-37.81</v>
+        <v>-40.04</v>
       </c>
       <c r="L16" t="n">
-        <v>37.81</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-69.67</v>
+        <v>-68.81</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.4</v>
+        <v>-20.15</v>
       </c>
       <c r="L17" t="n">
-        <v>72.59</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>70.53</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-22</v>
+        <v>-21.65</v>
       </c>
       <c r="L18" t="n">
-        <v>73.89</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>71.78</v>
+        <v>71.66</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.26</v>
+        <v>-12.24</v>
       </c>
       <c r="L19" t="n">
-        <v>72.81999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>79.44</v>
+        <v>75.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-111.7</v>
+        <v>-106.35</v>
       </c>
       <c r="L20" t="n">
-        <v>137.07</v>
+        <v>130.51</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>27.01</v>
+        <v>29.08</v>
       </c>
       <c r="K21" t="n">
-        <v>55.38</v>
+        <v>59.61</v>
       </c>
       <c r="L21" t="n">
-        <v>61.61</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.01</v>
+        <v>-18.35</v>
       </c>
       <c r="K22" t="n">
-        <v>55.33</v>
+        <v>59.67</v>
       </c>
       <c r="L22" t="n">
-        <v>57.88</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-14.48</v>
+        <v>-15.55</v>
       </c>
       <c r="K23" t="n">
-        <v>13.63</v>
+        <v>14.63</v>
       </c>
       <c r="L23" t="n">
-        <v>19.88</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-141.51</v>
+        <v>-138.28</v>
       </c>
       <c r="K24" t="n">
-        <v>18.45</v>
+        <v>18.03</v>
       </c>
       <c r="L24" t="n">
-        <v>142.71</v>
+        <v>139.45</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-93.59</v>
+        <v>-89.75</v>
       </c>
       <c r="K25" t="n">
-        <v>132.48</v>
+        <v>127.05</v>
       </c>
       <c r="L25" t="n">
-        <v>162.21</v>
+        <v>155.55</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>175.23</v>
+        <v>171.01</v>
       </c>
       <c r="K26" t="n">
-        <v>-95.02</v>
+        <v>-92.73999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>199.33</v>
+        <v>194.54</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-9.23</v>
+        <v>-9.59</v>
       </c>
       <c r="K27" t="n">
-        <v>154.81</v>
+        <v>160.79</v>
       </c>
       <c r="L27" t="n">
-        <v>155.08</v>
+        <v>161.07</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>93.5</v>
+        <v>95.84</v>
       </c>
       <c r="K28" t="n">
-        <v>147.33</v>
+        <v>151.02</v>
       </c>
       <c r="L28" t="n">
-        <v>174.49</v>
+        <v>178.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-55.47</v>
+        <v>-52.5</v>
       </c>
       <c r="K29" t="n">
-        <v>54.02</v>
+        <v>51.13</v>
       </c>
       <c r="L29" t="n">
-        <v>77.43000000000001</v>
+        <v>73.28</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.42</v>
+        <v>-11.7</v>
       </c>
       <c r="K30" t="n">
-        <v>80.09999999999999</v>
+        <v>75.47</v>
       </c>
       <c r="L30" t="n">
-        <v>81.06</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>49.42</v>
+        <v>49.76</v>
       </c>
       <c r="K31" t="n">
-        <v>17.6</v>
+        <v>17.72</v>
       </c>
       <c r="L31" t="n">
-        <v>52.46</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.7</v>
+        <v>-5.91</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.61</v>
+        <v>-56.64</v>
       </c>
       <c r="L32" t="n">
-        <v>54.9</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-48.79</v>
+        <v>-51.18</v>
       </c>
       <c r="K33" t="n">
-        <v>-20.1</v>
+        <v>-21.09</v>
       </c>
       <c r="L33" t="n">
-        <v>52.77</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-82.94</v>
+        <v>-80.19</v>
       </c>
       <c r="K34" t="n">
-        <v>12.8</v>
+        <v>12.37</v>
       </c>
       <c r="L34" t="n">
-        <v>83.92</v>
+        <v>81.14</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-97.70999999999999</v>
+        <v>-95.7</v>
       </c>
       <c r="K35" t="n">
-        <v>55.09</v>
+        <v>53.95</v>
       </c>
       <c r="L35" t="n">
-        <v>112.17</v>
+        <v>109.85</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>10.91</v>
+        <v>11.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.56</v>
+        <v>-16.75</v>
       </c>
       <c r="L36" t="n">
-        <v>19</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-80.63</v>
+        <v>-81.67</v>
       </c>
       <c r="K37" t="n">
-        <v>45.13</v>
+        <v>45.71</v>
       </c>
       <c r="L37" t="n">
-        <v>92.41</v>
+        <v>93.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>115.77</v>
+        <v>115.26</v>
       </c>
       <c r="K38" t="n">
-        <v>57.77</v>
+        <v>57.52</v>
       </c>
       <c r="L38" t="n">
-        <v>129.38</v>
+        <v>128.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.31</v>
+        <v>-6.23</v>
       </c>
       <c r="K39" t="n">
-        <v>140.79</v>
+        <v>139.02</v>
       </c>
       <c r="L39" t="n">
-        <v>140.93</v>
+        <v>139.16</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-81.20999999999999</v>
+        <v>-79.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-152.97</v>
+        <v>-149.92</v>
       </c>
       <c r="L40" t="n">
-        <v>173.19</v>
+        <v>169.74</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>38.44</v>
+        <v>40.37</v>
       </c>
       <c r="K41" t="n">
-        <v>135.22</v>
+        <v>142.02</v>
       </c>
       <c r="L41" t="n">
-        <v>140.57</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-173.36</v>
+        <v>-172.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-68.02</v>
+        <v>-67.69</v>
       </c>
       <c r="L42" t="n">
-        <v>186.23</v>
+        <v>185.34</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>82.38</v>
+        <v>86.36</v>
       </c>
       <c r="K43" t="n">
-        <v>106.23</v>
+        <v>111.36</v>
       </c>
       <c r="L43" t="n">
-        <v>134.44</v>
+        <v>140.93</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-31.91</v>
+        <v>-32.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-32.36</v>
+        <v>-33.15</v>
       </c>
       <c r="L44" t="n">
-        <v>45.45</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>42.6</v>
+        <v>42.85</v>
       </c>
       <c r="K45" t="n">
-        <v>-21.95</v>
+        <v>-22.08</v>
       </c>
       <c r="L45" t="n">
-        <v>47.93</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-16</v>
+        <v>-15.44</v>
       </c>
       <c r="K46" t="n">
-        <v>64.69</v>
+        <v>62.44</v>
       </c>
       <c r="L46" t="n">
-        <v>66.64</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>49.11</v>
+        <v>49.32</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.51</v>
+        <v>-37.67</v>
       </c>
       <c r="L47" t="n">
-        <v>61.79</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>15.95</v>
+        <v>15.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.79000000000001</v>
+        <v>-69.28</v>
       </c>
       <c r="L48" t="n">
-        <v>71.59</v>
+        <v>71.06999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-67.63</v>
+        <v>-64.56</v>
       </c>
       <c r="K49" t="n">
-        <v>55.49</v>
+        <v>52.97</v>
       </c>
       <c r="L49" t="n">
-        <v>87.48</v>
+        <v>83.51000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.3</v>
+        <v>-14.62</v>
       </c>
       <c r="K50" t="n">
-        <v>42.49</v>
+        <v>46.7</v>
       </c>
       <c r="L50" t="n">
-        <v>44.52</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.41</v>
+        <v>-13.64</v>
       </c>
       <c r="K51" t="n">
-        <v>-135.74</v>
+        <v>-128.53</v>
       </c>
       <c r="L51" t="n">
-        <v>136.5</v>
+        <v>129.25</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-85.03</v>
+        <v>-85.20999999999999</v>
       </c>
       <c r="K52" t="n">
         <v>-1</v>
       </c>
       <c r="L52" t="n">
-        <v>85.04000000000001</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="K53" t="n">
-        <v>117.06</v>
+        <v>118.82</v>
       </c>
       <c r="L53" t="n">
-        <v>117.28</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.5</v>
+        <v>-118.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-72.95</v>
+        <v>-72.03</v>
       </c>
       <c r="L54" t="n">
-        <v>140.86</v>
+        <v>139.09</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-115.24</v>
+        <v>-114.87</v>
       </c>
       <c r="K55" t="n">
-        <v>-41.33</v>
+        <v>-41.2</v>
       </c>
       <c r="L55" t="n">
-        <v>122.43</v>
+        <v>122.03</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>7.68</v>
+        <v>7.29</v>
       </c>
       <c r="K56" t="n">
-        <v>269.6</v>
+        <v>256.04</v>
       </c>
       <c r="L56" t="n">
-        <v>269.71</v>
+        <v>256.14</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>88.73</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>218.78</v>
+        <v>209.6</v>
       </c>
       <c r="L57" t="n">
-        <v>236.09</v>
+        <v>226.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>88.31999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>257</v>
+        <v>242.94</v>
       </c>
       <c r="L58" t="n">
-        <v>271.75</v>
+        <v>256.89</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>12.79</v>
+        <v>12.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-65.84</v>
+        <v>-63.23</v>
       </c>
       <c r="L59" t="n">
-        <v>67.06999999999999</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-23.81</v>
+        <v>-24.41</v>
       </c>
       <c r="K60" t="n">
-        <v>33.4</v>
+        <v>34.24</v>
       </c>
       <c r="L60" t="n">
-        <v>41.02</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>43.11</v>
+        <v>43.22</v>
       </c>
       <c r="K61" t="n">
-        <v>19.07</v>
+        <v>19.12</v>
       </c>
       <c r="L61" t="n">
-        <v>47.14</v>
+        <v>47.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-50.42</v>
+        <v>-51.38</v>
       </c>
       <c r="K62" t="n">
-        <v>-28.35</v>
+        <v>-28.89</v>
       </c>
       <c r="L62" t="n">
-        <v>57.84</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.69</v>
+        <v>-47.63</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.5</v>
+        <v>-47.44</v>
       </c>
       <c r="L63" t="n">
-        <v>67.31</v>
+        <v>67.23</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.06</v>
+        <v>-16.1</v>
       </c>
       <c r="K64" t="n">
-        <v>66.84</v>
+        <v>66.97</v>
       </c>
       <c r="L64" t="n">
-        <v>68.75</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>126.05</v>
+        <v>120.13</v>
       </c>
       <c r="K65" t="n">
-        <v>-48.71</v>
+        <v>-46.42</v>
       </c>
       <c r="L65" t="n">
-        <v>135.14</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>4.23</v>
+        <v>4.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-120.98</v>
+        <v>-117.98</v>
       </c>
       <c r="L66" t="n">
-        <v>121.06</v>
+        <v>118.05</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>56.23</v>
+        <v>55.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-81.2</v>
+        <v>-80.5</v>
       </c>
       <c r="L67" t="n">
-        <v>98.77</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-59.45</v>
+        <v>-57.35</v>
       </c>
       <c r="K68" t="n">
-        <v>156.98</v>
+        <v>151.44</v>
       </c>
       <c r="L68" t="n">
-        <v>167.86</v>
+        <v>161.93</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>81.2</v>
+        <v>80.58</v>
       </c>
       <c r="K69" t="n">
-        <v>100.24</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>129</v>
+        <v>128.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>33.06</v>
+        <v>33</v>
       </c>
       <c r="K70" t="n">
-        <v>124.78</v>
+        <v>124.54</v>
       </c>
       <c r="L70" t="n">
-        <v>129.08</v>
+        <v>128.84</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-177.73</v>
+        <v>-178.64</v>
       </c>
       <c r="K71" t="n">
-        <v>62.31</v>
+        <v>62.63</v>
       </c>
       <c r="L71" t="n">
-        <v>188.34</v>
+        <v>189.3</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>99.45999999999999</v>
+        <v>102.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-127.13</v>
+        <v>-130.7</v>
       </c>
       <c r="L72" t="n">
-        <v>161.42</v>
+        <v>165.94</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>165.55</v>
+        <v>160.92</v>
       </c>
       <c r="K73" t="n">
-        <v>132.6</v>
+        <v>128.89</v>
       </c>
       <c r="L73" t="n">
-        <v>212.1</v>
+        <v>206.18</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-29.46</v>
+        <v>-31.38</v>
       </c>
       <c r="K74" t="n">
-        <v>28.85</v>
+        <v>30.73</v>
       </c>
       <c r="L74" t="n">
-        <v>41.23</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="K75" t="n">
-        <v>-43.32</v>
+        <v>-45.69</v>
       </c>
       <c r="L75" t="n">
-        <v>44.07</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>29.75</v>
+        <v>30.81</v>
       </c>
       <c r="K76" t="n">
-        <v>29.77</v>
+        <v>30.83</v>
       </c>
       <c r="L76" t="n">
-        <v>42.08</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>58.61</v>
+        <v>58.43</v>
       </c>
       <c r="K77" t="n">
-        <v>37.47</v>
+        <v>37.36</v>
       </c>
       <c r="L77" t="n">
-        <v>69.56</v>
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>46.07</v>
+        <v>47.83</v>
       </c>
       <c r="K78" t="n">
-        <v>27.87</v>
+        <v>28.94</v>
       </c>
       <c r="L78" t="n">
-        <v>53.84</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-46.26</v>
+        <v>-48</v>
       </c>
       <c r="K79" t="n">
-        <v>-23.46</v>
+        <v>-24.34</v>
       </c>
       <c r="L79" t="n">
-        <v>51.87</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>73.05</v>
+        <v>71.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-84.23</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>111.49</v>
+        <v>108.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>58.42</v>
+        <v>61.74</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.58</v>
+        <v>-41.83</v>
       </c>
       <c r="L81" t="n">
-        <v>70.56999999999999</v>
+        <v>74.56999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>58.86</v>
+        <v>58.82</v>
       </c>
       <c r="K82" t="n">
-        <v>-76.52</v>
+        <v>-76.47</v>
       </c>
       <c r="L82" t="n">
-        <v>96.53</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>18.49</v>
+        <v>18.06</v>
       </c>
       <c r="K83" t="n">
-        <v>-157.51</v>
+        <v>-153.87</v>
       </c>
       <c r="L83" t="n">
-        <v>158.59</v>
+        <v>154.93</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.54</v>
+        <v>-31.94</v>
       </c>
       <c r="K84" t="n">
-        <v>154.13</v>
+        <v>151.3</v>
       </c>
       <c r="L84" t="n">
-        <v>157.53</v>
+        <v>154.64</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-93.48</v>
+        <v>-91.92</v>
       </c>
       <c r="K85" t="n">
-        <v>99.19</v>
+        <v>97.53</v>
       </c>
       <c r="L85" t="n">
-        <v>136.3</v>
+        <v>134.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-151.48</v>
+        <v>-149.14</v>
       </c>
       <c r="K86" t="n">
-        <v>110.95</v>
+        <v>109.23</v>
       </c>
       <c r="L86" t="n">
-        <v>187.77</v>
+        <v>184.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-60.01</v>
+        <v>-58.45</v>
       </c>
       <c r="K87" t="n">
-        <v>195.27</v>
+        <v>190.18</v>
       </c>
       <c r="L87" t="n">
-        <v>204.28</v>
+        <v>198.95</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-85.17</v>
+        <v>-90.12</v>
       </c>
       <c r="K88" t="n">
-        <v>101.18</v>
+        <v>107.05</v>
       </c>
       <c r="L88" t="n">
-        <v>132.25</v>
+        <v>139.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="F14" t="n">
-        <v>8.08</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>82.8</v>
+        <v>72</v>
       </c>
       <c r="H14" t="n">
-        <v>45.9</v>
+        <v>44.6</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.26</v>
+        <v>-42.26</v>
       </c>
       <c r="K14" t="n">
-        <v>37.62</v>
+        <v>45.26</v>
       </c>
       <c r="L14" t="n">
-        <v>39.27</v>
+        <v>61.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:33:54</t>
+          <t>06:35:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="F15" t="n">
-        <v>8.18</v>
+        <v>4.57</v>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>86.8</v>
       </c>
       <c r="H15" t="n">
-        <v>42</v>
+        <v>45.3</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>55.98</v>
+        <v>10.99</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.17</v>
+        <v>82.28</v>
       </c>
       <c r="L15" t="n">
-        <v>58.56</v>
+        <v>83.01000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:36:44</t>
+          <t>06:37:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.31</v>
+        <v>1.99</v>
       </c>
       <c r="F16" t="n">
-        <v>8.109999999999999</v>
+        <v>5.97</v>
       </c>
       <c r="G16" t="n">
-        <v>58.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>41.7</v>
+        <v>51</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.43</v>
+        <v>-43.84</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.04</v>
+        <v>21.68</v>
       </c>
       <c r="L16" t="n">
-        <v>40.04</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:41:31</t>
+          <t>06:41:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="F17" t="n">
-        <v>7.32</v>
+        <v>6.63</v>
       </c>
       <c r="G17" t="n">
-        <v>65.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>47.7</v>
+        <v>43.1</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-68.81</v>
+        <v>-61.24</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.15</v>
+        <v>22.13</v>
       </c>
       <c r="L17" t="n">
-        <v>71.7</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:42:52</t>
+          <t>06:42:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="F18" t="n">
-        <v>7.34</v>
+        <v>6.15</v>
       </c>
       <c r="G18" t="n">
-        <v>73.5</v>
+        <v>79.2</v>
       </c>
       <c r="H18" t="n">
-        <v>44.8</v>
+        <v>43.3</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>69.40000000000001</v>
+        <v>-44.02</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.65</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>72.7</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:43:55</t>
+          <t>06:44:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="F19" t="n">
-        <v>6.89</v>
+        <v>8.74</v>
       </c>
       <c r="G19" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="H19" t="n">
-        <v>52.2</v>
+        <v>38.8</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>71.66</v>
+        <v>-14.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.24</v>
+        <v>87.86</v>
       </c>
       <c r="L19" t="n">
-        <v>72.7</v>
+        <v>89.06999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:48:26</t>
+          <t>06:49:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="F20" t="n">
-        <v>6.9</v>
+        <v>6.33</v>
       </c>
       <c r="G20" t="n">
-        <v>74.8</v>
+        <v>71.8</v>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>75.64</v>
+        <v>-120.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-106.35</v>
+        <v>-83.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>130.51</v>
+        <v>146.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:50:11</t>
+          <t>06:50:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="F21" t="n">
-        <v>7.98</v>
+        <v>5.18</v>
       </c>
       <c r="G21" t="n">
-        <v>84.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="H21" t="n">
-        <v>44.4</v>
+        <v>49.7</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>29.08</v>
+        <v>51.92</v>
       </c>
       <c r="K21" t="n">
-        <v>59.61</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>66.33</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:51:28</t>
+          <t>06:51:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="F22" t="n">
-        <v>8.07</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>80.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>41.5</v>
+        <v>50.6</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.35</v>
+        <v>34.67</v>
       </c>
       <c r="K22" t="n">
-        <v>59.67</v>
+        <v>-178.38</v>
       </c>
       <c r="L22" t="n">
-        <v>62.43</v>
+        <v>181.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:56:20</t>
+          <t>06:56:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6</v>
+        <v>2.37</v>
       </c>
       <c r="F23" t="n">
-        <v>7.57</v>
+        <v>6.77</v>
       </c>
       <c r="G23" t="n">
-        <v>79.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-15.55</v>
+        <v>98.39</v>
       </c>
       <c r="K23" t="n">
-        <v>14.63</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>21.35</v>
+        <v>123.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:57:25</t>
+          <t>06:59:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="F24" t="n">
-        <v>7.67</v>
+        <v>4.83</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H24" t="n">
-        <v>50.1</v>
+        <v>46.6</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>-138.28</v>
+        <v>79.84</v>
       </c>
       <c r="K24" t="n">
-        <v>18.03</v>
+        <v>-105.59</v>
       </c>
       <c r="L24" t="n">
-        <v>139.45</v>
+        <v>132.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:59:43</t>
+          <t>07:00:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="F25" t="n">
-        <v>7.09</v>
+        <v>6.14</v>
       </c>
       <c r="G25" t="n">
-        <v>88.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H25" t="n">
-        <v>45.2</v>
+        <v>40.8</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>-89.75</v>
+        <v>184.62</v>
       </c>
       <c r="K25" t="n">
-        <v>127.05</v>
+        <v>-34.52</v>
       </c>
       <c r="L25" t="n">
-        <v>155.55</v>
+        <v>187.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:04:45</t>
+          <t>07:05:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="F26" t="n">
-        <v>7.51</v>
+        <v>5.04</v>
       </c>
       <c r="G26" t="n">
-        <v>66.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>44.3</v>
+        <v>45</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>171.01</v>
+        <v>-112.93</v>
       </c>
       <c r="K26" t="n">
-        <v>-92.73999999999999</v>
+        <v>140.98</v>
       </c>
       <c r="L26" t="n">
-        <v>194.54</v>
+        <v>180.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:06:25</t>
+          <t>07:08:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="F27" t="n">
-        <v>8.02</v>
+        <v>8.09</v>
       </c>
       <c r="G27" t="n">
-        <v>83</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-9.59</v>
+        <v>213.83</v>
       </c>
       <c r="K27" t="n">
-        <v>160.79</v>
+        <v>102.04</v>
       </c>
       <c r="L27" t="n">
-        <v>161.07</v>
+        <v>236.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:09:08</t>
+          <t>07:10:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.24</v>
+        <v>2.24</v>
       </c>
       <c r="F28" t="n">
-        <v>7.12</v>
+        <v>6.77</v>
       </c>
       <c r="G28" t="n">
-        <v>82.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>46.4</v>
+        <v>50.2</v>
       </c>
       <c r="I28" t="n">
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>95.84</v>
+        <v>124.44</v>
       </c>
       <c r="K28" t="n">
-        <v>151.02</v>
+        <v>175.54</v>
       </c>
       <c r="L28" t="n">
-        <v>178.87</v>
+        <v>215.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:17:23</t>
+          <t>07:20:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="F29" t="n">
-        <v>7.38</v>
+        <v>4.65</v>
       </c>
       <c r="G29" t="n">
-        <v>80.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>43.8</v>
+        <v>49.5</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-52.5</v>
+        <v>-59.45</v>
       </c>
       <c r="K29" t="n">
-        <v>51.13</v>
+        <v>58.59</v>
       </c>
       <c r="L29" t="n">
-        <v>73.28</v>
+        <v>83.45999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:19:01</t>
+          <t>07:21:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="F30" t="n">
-        <v>7.5</v>
+        <v>8.74</v>
       </c>
       <c r="G30" t="n">
-        <v>78.3</v>
+        <v>71.7</v>
       </c>
       <c r="H30" t="n">
-        <v>49.8</v>
+        <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.7</v>
+        <v>-15</v>
       </c>
       <c r="K30" t="n">
-        <v>75.47</v>
+        <v>100.14</v>
       </c>
       <c r="L30" t="n">
-        <v>76.37</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:20:19</t>
+          <t>07:23:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="F31" t="n">
-        <v>7.34</v>
+        <v>8.27</v>
       </c>
       <c r="G31" t="n">
-        <v>85.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>41.9</v>
+        <v>51.9</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>49.76</v>
+        <v>66.52</v>
       </c>
       <c r="K31" t="n">
-        <v>17.72</v>
+        <v>24.08</v>
       </c>
       <c r="L31" t="n">
-        <v>52.82</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:25:09</t>
+          <t>07:27:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="F32" t="n">
-        <v>7.42</v>
+        <v>7.05</v>
       </c>
       <c r="G32" t="n">
-        <v>69.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>45.7</v>
+        <v>43.6</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.91</v>
+        <v>-5.05</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.64</v>
+        <v>-74.52</v>
       </c>
       <c r="L32" t="n">
-        <v>56.95</v>
+        <v>74.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:25:57</t>
+          <t>07:29:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1426,31 +1426,31 @@
         <v>2.26</v>
       </c>
       <c r="F33" t="n">
-        <v>7.5</v>
+        <v>7.95</v>
       </c>
       <c r="G33" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="H33" t="n">
-        <v>43.6</v>
+        <v>44.9</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-51.18</v>
+        <v>-16.06</v>
       </c>
       <c r="K33" t="n">
-        <v>-21.09</v>
+        <v>77.12</v>
       </c>
       <c r="L33" t="n">
-        <v>55.35</v>
+        <v>78.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:27:23</t>
+          <t>07:31:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="F34" t="n">
-        <v>7.64</v>
+        <v>6.2</v>
       </c>
       <c r="G34" t="n">
-        <v>66.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H34" t="n">
-        <v>42</v>
+        <v>46.3</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-80.19</v>
+        <v>22.15</v>
       </c>
       <c r="K34" t="n">
-        <v>12.37</v>
+        <v>-88.56</v>
       </c>
       <c r="L34" t="n">
-        <v>81.14</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:32:32</t>
+          <t>07:36:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="F35" t="n">
-        <v>7.6</v>
+        <v>5.95</v>
       </c>
       <c r="G35" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>44.2</v>
+        <v>45.9</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-95.7</v>
+        <v>89.62</v>
       </c>
       <c r="K35" t="n">
-        <v>53.95</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>109.85</v>
+        <v>119.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:33:43</t>
+          <t>07:36:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="F36" t="n">
-        <v>7.87</v>
+        <v>8.34</v>
       </c>
       <c r="G36" t="n">
-        <v>76.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="H36" t="n">
-        <v>39.7</v>
+        <v>48.6</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>11.74</v>
+        <v>2.43</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.75</v>
+        <v>155.05</v>
       </c>
       <c r="L36" t="n">
-        <v>20.46</v>
+        <v>155.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:34:23</t>
+          <t>07:38:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="F37" t="n">
-        <v>7.99</v>
+        <v>8.74</v>
       </c>
       <c r="G37" t="n">
-        <v>66.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="H37" t="n">
-        <v>55.9</v>
+        <v>49.8</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-81.67</v>
+        <v>104.54</v>
       </c>
       <c r="K37" t="n">
-        <v>45.71</v>
+        <v>-12.72</v>
       </c>
       <c r="L37" t="n">
-        <v>93.59</v>
+        <v>105.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:38:13</t>
+          <t>07:43:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="F38" t="n">
-        <v>7.63</v>
+        <v>8.74</v>
       </c>
       <c r="G38" t="n">
-        <v>83.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>115.26</v>
+        <v>130.94</v>
       </c>
       <c r="K38" t="n">
-        <v>57.52</v>
+        <v>127.44</v>
       </c>
       <c r="L38" t="n">
-        <v>128.82</v>
+        <v>182.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:40:15</t>
+          <t>07:45:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="F39" t="n">
-        <v>7.91</v>
+        <v>5.78</v>
       </c>
       <c r="G39" t="n">
-        <v>68.7</v>
+        <v>81.5</v>
       </c>
       <c r="H39" t="n">
-        <v>43.6</v>
+        <v>49</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.23</v>
+        <v>153.23</v>
       </c>
       <c r="K39" t="n">
-        <v>139.02</v>
+        <v>129.16</v>
       </c>
       <c r="L39" t="n">
-        <v>139.16</v>
+        <v>200.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:41:52</t>
+          <t>07:46:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>2.5</v>
       </c>
       <c r="F40" t="n">
-        <v>7.65</v>
+        <v>8.74</v>
       </c>
       <c r="G40" t="n">
-        <v>73.2</v>
+        <v>74.7</v>
       </c>
       <c r="H40" t="n">
-        <v>52.2</v>
+        <v>45.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-79.59</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-149.92</v>
+        <v>-174.64</v>
       </c>
       <c r="L40" t="n">
-        <v>169.74</v>
+        <v>191.95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:45:12</t>
+          <t>07:51:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="F41" t="n">
-        <v>7.8</v>
+        <v>8.74</v>
       </c>
       <c r="G41" t="n">
-        <v>63.6</v>
+        <v>77.8</v>
       </c>
       <c r="H41" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>40.37</v>
+        <v>123.26</v>
       </c>
       <c r="K41" t="n">
-        <v>142.02</v>
+        <v>179.69</v>
       </c>
       <c r="L41" t="n">
-        <v>147.64</v>
+        <v>217.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:47:34</t>
+          <t>07:52:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>7.65</v>
+        <v>4.07</v>
       </c>
       <c r="G42" t="n">
-        <v>58.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>41.6</v>
+        <v>38.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-172.53</v>
+        <v>-181.29</v>
       </c>
       <c r="K42" t="n">
-        <v>-67.69</v>
+        <v>-80.38</v>
       </c>
       <c r="L42" t="n">
-        <v>185.34</v>
+        <v>198.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:48:13</t>
+          <t>07:54:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="F43" t="n">
-        <v>8.06</v>
+        <v>7.36</v>
       </c>
       <c r="G43" t="n">
-        <v>79.7</v>
+        <v>82.8</v>
       </c>
       <c r="H43" t="n">
-        <v>49.5</v>
+        <v>48.9</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>86.36</v>
+        <v>170.4</v>
       </c>
       <c r="K43" t="n">
-        <v>111.36</v>
+        <v>147.17</v>
       </c>
       <c r="L43" t="n">
-        <v>140.93</v>
+        <v>225.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:59:51</t>
+          <t>08:05:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="F44" t="n">
-        <v>7.77</v>
+        <v>7.07</v>
       </c>
       <c r="G44" t="n">
-        <v>67.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>44.6</v>
+        <v>42.6</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-32.7</v>
+        <v>-43.88</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.15</v>
+        <v>-45.51</v>
       </c>
       <c r="L44" t="n">
-        <v>46.56</v>
+        <v>63.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:01:58</t>
+          <t>08:07:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="F45" t="n">
-        <v>7.38</v>
+        <v>6.83</v>
       </c>
       <c r="G45" t="n">
-        <v>80.2</v>
+        <v>69.2</v>
       </c>
       <c r="H45" t="n">
-        <v>42.4</v>
+        <v>49.1</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>42.85</v>
+        <v>53.81</v>
       </c>
       <c r="K45" t="n">
-        <v>-22.08</v>
+        <v>-27.07</v>
       </c>
       <c r="L45" t="n">
-        <v>48.2</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:03:03</t>
+          <t>08:07:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="F46" t="n">
-        <v>7.12</v>
+        <v>8.74</v>
       </c>
       <c r="G46" t="n">
-        <v>73.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.44</v>
+        <v>-20.34</v>
       </c>
       <c r="K46" t="n">
-        <v>62.44</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>64.31999999999999</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:07:10</t>
+          <t>08:10:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="F47" t="n">
-        <v>8.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>86.3</v>
+        <v>88.3</v>
       </c>
       <c r="H47" t="n">
-        <v>53.7</v>
+        <v>52.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>49.32</v>
+        <v>70.87</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.67</v>
+        <v>-52.36</v>
       </c>
       <c r="L47" t="n">
-        <v>62.06</v>
+        <v>88.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:08:17</t>
+          <t>08:12:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="F48" t="n">
-        <v>7.96</v>
+        <v>6.66</v>
       </c>
       <c r="G48" t="n">
-        <v>68.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>15.83</v>
+        <v>23.33</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.28</v>
+        <v>-91.98</v>
       </c>
       <c r="L48" t="n">
-        <v>71.06999999999999</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:10:02</t>
+          <t>08:13:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="F49" t="n">
-        <v>7.3</v>
+        <v>8.74</v>
       </c>
       <c r="G49" t="n">
-        <v>82.2</v>
+        <v>67.7</v>
       </c>
       <c r="H49" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-64.56</v>
+        <v>-88.97</v>
       </c>
       <c r="K49" t="n">
-        <v>52.97</v>
+        <v>75.13</v>
       </c>
       <c r="L49" t="n">
-        <v>83.51000000000001</v>
+        <v>116.45</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:14:04</t>
+          <t>08:18:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="F50" t="n">
-        <v>7.61</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>83.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>52.5</v>
+        <v>51</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.62</v>
+        <v>3.92</v>
       </c>
       <c r="K50" t="n">
-        <v>46.7</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>48.93</v>
+        <v>95.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:16:26</t>
+          <t>08:20:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F51" t="n">
-        <v>7.9</v>
+        <v>8.74</v>
       </c>
       <c r="G51" t="n">
-        <v>64.3</v>
+        <v>79.7</v>
       </c>
       <c r="H51" t="n">
-        <v>50.6</v>
+        <v>41.2</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.64</v>
+        <v>-10.49</v>
       </c>
       <c r="K51" t="n">
-        <v>-128.53</v>
+        <v>-171.49</v>
       </c>
       <c r="L51" t="n">
-        <v>129.25</v>
+        <v>171.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:17:58</t>
+          <t>08:22:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="F52" t="n">
-        <v>7.67</v>
+        <v>7.17</v>
       </c>
       <c r="G52" t="n">
-        <v>74.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="H52" t="n">
-        <v>48</v>
+        <v>46.4</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-85.20999999999999</v>
+        <v>-115.01</v>
       </c>
       <c r="K52" t="n">
-        <v>-1</v>
+        <v>0.42</v>
       </c>
       <c r="L52" t="n">
-        <v>85.20999999999999</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:23:06</t>
+          <t>08:26:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="F53" t="n">
-        <v>7.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>85</v>
+        <v>68.2</v>
       </c>
       <c r="H53" t="n">
-        <v>39.5</v>
+        <v>51.5</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>7.24</v>
+        <v>33.33</v>
       </c>
       <c r="K53" t="n">
-        <v>118.82</v>
+        <v>170.94</v>
       </c>
       <c r="L53" t="n">
-        <v>119.04</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:25:03</t>
+          <t>08:28:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="F54" t="n">
-        <v>7.73</v>
+        <v>6.76</v>
       </c>
       <c r="G54" t="n">
-        <v>74.7</v>
+        <v>76.2</v>
       </c>
       <c r="H54" t="n">
-        <v>43.6</v>
+        <v>46.4</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-118.98</v>
+        <v>-145.98</v>
       </c>
       <c r="K54" t="n">
-        <v>-72.03</v>
+        <v>-96.73999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>139.09</v>
+        <v>175.12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:27:12</t>
+          <t>08:30:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2350,31 +2350,31 @@
         <v>2.51</v>
       </c>
       <c r="F55" t="n">
-        <v>7.52</v>
+        <v>8.74</v>
       </c>
       <c r="G55" t="n">
-        <v>86.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>45.5</v>
+        <v>52.1</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-114.87</v>
+        <v>-169.59</v>
       </c>
       <c r="K55" t="n">
-        <v>-41.2</v>
+        <v>-57.98</v>
       </c>
       <c r="L55" t="n">
-        <v>122.03</v>
+        <v>179.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:32:13</t>
+          <t>08:34:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="F56" t="n">
-        <v>7.86</v>
+        <v>8.51</v>
       </c>
       <c r="G56" t="n">
-        <v>84.8</v>
+        <v>78.8</v>
       </c>
       <c r="H56" t="n">
-        <v>46.8</v>
+        <v>51.4</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>7.29</v>
+        <v>42.54</v>
       </c>
       <c r="K56" t="n">
-        <v>256.04</v>
+        <v>319.11</v>
       </c>
       <c r="L56" t="n">
-        <v>256.14</v>
+        <v>321.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:32:48</t>
+          <t>08:36:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="F57" t="n">
-        <v>7.47</v>
+        <v>5.37</v>
       </c>
       <c r="G57" t="n">
-        <v>80.3</v>
+        <v>71</v>
       </c>
       <c r="H57" t="n">
-        <v>55.2</v>
+        <v>49.2</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>85.01000000000001</v>
+        <v>136.21</v>
       </c>
       <c r="K57" t="n">
-        <v>209.6</v>
+        <v>274</v>
       </c>
       <c r="L57" t="n">
-        <v>226.19</v>
+        <v>305.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:34:42</t>
+          <t>08:38:02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="F58" t="n">
-        <v>8.02</v>
+        <v>5.97</v>
       </c>
       <c r="G58" t="n">
-        <v>57.9</v>
+        <v>82.2</v>
       </c>
       <c r="H58" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>83.48999999999999</v>
+        <v>124.96</v>
       </c>
       <c r="K58" t="n">
-        <v>242.94</v>
+        <v>281.25</v>
       </c>
       <c r="L58" t="n">
-        <v>256.89</v>
+        <v>307.76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:47:07</t>
+          <t>08:49:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2518,31 +2518,31 @@
         <v>2.5</v>
       </c>
       <c r="F59" t="n">
-        <v>7.35</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="H59" t="n">
-        <v>49.8</v>
+        <v>43.6</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>12.28</v>
+        <v>17.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-63.23</v>
+        <v>-85.09</v>
       </c>
       <c r="L59" t="n">
-        <v>64.42</v>
+        <v>86.79000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:48:45</t>
+          <t>08:50:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="F60" t="n">
-        <v>7.53</v>
+        <v>7.95</v>
       </c>
       <c r="G60" t="n">
-        <v>67.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H60" t="n">
-        <v>47.5</v>
+        <v>42.9</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.41</v>
+        <v>-35.11</v>
       </c>
       <c r="K60" t="n">
-        <v>34.24</v>
+        <v>50.62</v>
       </c>
       <c r="L60" t="n">
-        <v>42.05</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:49:54</t>
+          <t>08:52:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="F61" t="n">
-        <v>7.11</v>
+        <v>7.63</v>
       </c>
       <c r="G61" t="n">
-        <v>78.3</v>
+        <v>63.9</v>
       </c>
       <c r="H61" t="n">
-        <v>45.5</v>
+        <v>48.2</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>43.22</v>
+        <v>61.57</v>
       </c>
       <c r="K61" t="n">
-        <v>19.12</v>
+        <v>27.52</v>
       </c>
       <c r="L61" t="n">
-        <v>47.27</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:54:57</t>
+          <t>08:58:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>2.64</v>
       </c>
       <c r="F62" t="n">
-        <v>8.1</v>
+        <v>6.79</v>
       </c>
       <c r="G62" t="n">
-        <v>73.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="H62" t="n">
-        <v>42.6</v>
+        <v>45.6</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.38</v>
+        <v>-66.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-28.89</v>
+        <v>-38.96</v>
       </c>
       <c r="L62" t="n">
-        <v>58.95</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:57:18</t>
+          <t>09:00:26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2686,31 +2686,31 @@
         <v>2.66</v>
       </c>
       <c r="F63" t="n">
-        <v>8.17</v>
+        <v>8.74</v>
       </c>
       <c r="G63" t="n">
-        <v>80.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>48</v>
+        <v>49.5</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.63</v>
+        <v>-60.33</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.44</v>
+        <v>-62.41</v>
       </c>
       <c r="L63" t="n">
-        <v>67.23</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:59:25</t>
+          <t>09:03:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="F64" t="n">
-        <v>7.41</v>
+        <v>6.13</v>
       </c>
       <c r="G64" t="n">
-        <v>70.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>41.3</v>
+        <v>44.1</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.1</v>
+        <v>-17.52</v>
       </c>
       <c r="K64" t="n">
-        <v>66.97</v>
+        <v>82.56</v>
       </c>
       <c r="L64" t="n">
-        <v>68.88</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:05:02</t>
+          <t>09:07:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="F65" t="n">
-        <v>7.7</v>
+        <v>8.74</v>
       </c>
       <c r="G65" t="n">
-        <v>73.7</v>
+        <v>75.8</v>
       </c>
       <c r="H65" t="n">
-        <v>44.7</v>
+        <v>45.9</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>120.13</v>
+        <v>170.31</v>
       </c>
       <c r="K65" t="n">
-        <v>-46.42</v>
+        <v>-61.29</v>
       </c>
       <c r="L65" t="n">
-        <v>128.79</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:06:46</t>
+          <t>09:08:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2812,31 +2812,31 @@
         <v>2.84</v>
       </c>
       <c r="F66" t="n">
-        <v>8.109999999999999</v>
+        <v>6.12</v>
       </c>
       <c r="G66" t="n">
-        <v>79.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="H66" t="n">
-        <v>39.6</v>
+        <v>49</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>4.12</v>
+        <v>12.53</v>
       </c>
       <c r="K66" t="n">
-        <v>-117.98</v>
+        <v>-129.68</v>
       </c>
       <c r="L66" t="n">
-        <v>118.05</v>
+        <v>130.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:08:02</t>
+          <t>09:09:54</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="F67" t="n">
-        <v>7.39</v>
+        <v>6.53</v>
       </c>
       <c r="G67" t="n">
-        <v>75.5</v>
+        <v>69.5</v>
       </c>
       <c r="H67" t="n">
-        <v>41.5</v>
+        <v>46.8</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>55.75</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-80.5</v>
+        <v>-98.34</v>
       </c>
       <c r="L67" t="n">
-        <v>97.92</v>
+        <v>125.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:12:19</t>
+          <t>09:15:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="F68" t="n">
-        <v>7.33</v>
+        <v>8.74</v>
       </c>
       <c r="G68" t="n">
-        <v>83.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>49.8</v>
+        <v>50.9</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-57.35</v>
+        <v>-59.56</v>
       </c>
       <c r="K68" t="n">
-        <v>151.44</v>
+        <v>208.4</v>
       </c>
       <c r="L68" t="n">
-        <v>161.93</v>
+        <v>216.74</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:14:01</t>
+          <t>09:17:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2938,31 +2938,31 @@
         <v>2.37</v>
       </c>
       <c r="F69" t="n">
-        <v>7.19</v>
+        <v>6.34</v>
       </c>
       <c r="G69" t="n">
-        <v>78.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>54</v>
+        <v>48.3</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>80.58</v>
+        <v>117.22</v>
       </c>
       <c r="K69" t="n">
-        <v>99.48999999999999</v>
+        <v>134.53</v>
       </c>
       <c r="L69" t="n">
-        <v>128.03</v>
+        <v>178.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:15:32</t>
+          <t>09:18:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2980,31 +2980,31 @@
         <v>2.63</v>
       </c>
       <c r="F70" t="n">
-        <v>7.08</v>
+        <v>8.74</v>
       </c>
       <c r="G70" t="n">
-        <v>74.8</v>
+        <v>63.4</v>
       </c>
       <c r="H70" t="n">
-        <v>48.9</v>
+        <v>46.4</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>33</v>
+        <v>61.01</v>
       </c>
       <c r="K70" t="n">
-        <v>124.54</v>
+        <v>170</v>
       </c>
       <c r="L70" t="n">
-        <v>128.84</v>
+        <v>180.62</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:20:14</t>
+          <t>09:22:56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3022,31 +3022,31 @@
         <v>3.05</v>
       </c>
       <c r="F71" t="n">
-        <v>7.54</v>
+        <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>68.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H71" t="n">
-        <v>48.9</v>
+        <v>43.2</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-178.64</v>
+        <v>-192.56</v>
       </c>
       <c r="K71" t="n">
-        <v>62.63</v>
+        <v>100.76</v>
       </c>
       <c r="L71" t="n">
-        <v>189.3</v>
+        <v>217.33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:22:33</t>
+          <t>09:24:47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3064,31 +3064,31 @@
         <v>2.71</v>
       </c>
       <c r="F72" t="n">
-        <v>7.82</v>
+        <v>8.74</v>
       </c>
       <c r="G72" t="n">
-        <v>75.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="H72" t="n">
-        <v>48.1</v>
+        <v>46.9</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>102.24</v>
+        <v>181.29</v>
       </c>
       <c r="K72" t="n">
-        <v>-130.7</v>
+        <v>-145.21</v>
       </c>
       <c r="L72" t="n">
-        <v>165.94</v>
+        <v>232.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:24:23</t>
+          <t>09:26:06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="F73" t="n">
-        <v>7.39</v>
+        <v>7.6</v>
       </c>
       <c r="G73" t="n">
-        <v>68.7</v>
+        <v>69.5</v>
       </c>
       <c r="H73" t="n">
-        <v>46.1</v>
+        <v>43.4</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>160.92</v>
+        <v>244.94</v>
       </c>
       <c r="K73" t="n">
-        <v>128.89</v>
+        <v>180.03</v>
       </c>
       <c r="L73" t="n">
-        <v>206.18</v>
+        <v>303.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:36:10</t>
+          <t>09:38:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>2.82</v>
       </c>
       <c r="F74" t="n">
-        <v>7.51</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>98</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>45.1</v>
+        <v>58</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-31.38</v>
+        <v>-44.46</v>
       </c>
       <c r="K74" t="n">
-        <v>30.73</v>
+        <v>46.95</v>
       </c>
       <c r="L74" t="n">
-        <v>43.92</v>
+        <v>64.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:38:08</t>
+          <t>09:40:27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="F75" t="n">
-        <v>7.24</v>
+        <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>75.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.59</v>
+        <v>-10.8</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.69</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>46.49</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:40:25</t>
+          <t>09:42:48</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3232,31 +3232,31 @@
         <v>2.51</v>
       </c>
       <c r="F76" t="n">
-        <v>7.32</v>
+        <v>7.61</v>
       </c>
       <c r="G76" t="n">
-        <v>62</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>44.8</v>
+        <v>40.1</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>30.81</v>
+        <v>45.66</v>
       </c>
       <c r="K76" t="n">
-        <v>30.83</v>
+        <v>44.89</v>
       </c>
       <c r="L76" t="n">
-        <v>43.58</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:46:06</t>
+          <t>09:48:04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3274,31 +3274,31 @@
         <v>2.87</v>
       </c>
       <c r="F77" t="n">
-        <v>7.23</v>
+        <v>8.74</v>
       </c>
       <c r="G77" t="n">
-        <v>68.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>42.4</v>
+        <v>43.4</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>58.43</v>
+        <v>76.38</v>
       </c>
       <c r="K77" t="n">
-        <v>37.36</v>
+        <v>48.49</v>
       </c>
       <c r="L77" t="n">
-        <v>69.34999999999999</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:48:27</t>
+          <t>09:49:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3316,31 +3316,31 @@
         <v>2.95</v>
       </c>
       <c r="F78" t="n">
-        <v>7.95</v>
+        <v>8.74</v>
       </c>
       <c r="G78" t="n">
-        <v>59.6</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>49</v>
+        <v>38.9</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>47.83</v>
+        <v>70.41</v>
       </c>
       <c r="K78" t="n">
-        <v>28.94</v>
+        <v>39.44</v>
       </c>
       <c r="L78" t="n">
-        <v>55.9</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:50:05</t>
+          <t>09:51:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3358,31 +3358,31 @@
         <v>2.47</v>
       </c>
       <c r="F79" t="n">
-        <v>7.05</v>
+        <v>6.69</v>
       </c>
       <c r="G79" t="n">
-        <v>79.2</v>
+        <v>62.8</v>
       </c>
       <c r="H79" t="n">
-        <v>48.2</v>
+        <v>48.7</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-48</v>
+        <v>-68.66</v>
       </c>
       <c r="K79" t="n">
-        <v>-24.34</v>
+        <v>-33.81</v>
       </c>
       <c r="L79" t="n">
-        <v>53.82</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:55:07</t>
+          <t>09:55:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3400,31 +3400,31 @@
         <v>2.39</v>
       </c>
       <c r="F80" t="n">
-        <v>7.13</v>
+        <v>6.24</v>
       </c>
       <c r="G80" t="n">
-        <v>74.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H80" t="n">
-        <v>42.6</v>
+        <v>46.2</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>71.27</v>
+        <v>94.75</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.18000000000001</v>
+        <v>-98.48</v>
       </c>
       <c r="L80" t="n">
-        <v>108.78</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:56:32</t>
+          <t>09:57:11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3442,31 +3442,31 @@
         <v>2.67</v>
       </c>
       <c r="F81" t="n">
-        <v>7.48</v>
+        <v>7.89</v>
       </c>
       <c r="G81" t="n">
-        <v>83</v>
+        <v>71.3</v>
       </c>
       <c r="H81" t="n">
-        <v>43.6</v>
+        <v>50.6</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>61.74</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.83</v>
+        <v>-46.95</v>
       </c>
       <c r="L81" t="n">
-        <v>74.56999999999999</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:58:28</t>
+          <t>09:59:09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3484,31 +3484,31 @@
         <v>2.84</v>
       </c>
       <c r="F82" t="n">
-        <v>7.62</v>
+        <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>69.3</v>
+        <v>74</v>
       </c>
       <c r="H82" t="n">
-        <v>50</v>
+        <v>43.7</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>58.82</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-76.47</v>
+        <v>-95.48999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>96.48</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:02:49</t>
+          <t>10:04:09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>2.98</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>7.28</v>
       </c>
       <c r="G83" t="n">
-        <v>91.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="H83" t="n">
-        <v>50.7</v>
+        <v>54.8</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>18.06</v>
+        <v>45.09</v>
       </c>
       <c r="K83" t="n">
-        <v>-153.87</v>
+        <v>-185.59</v>
       </c>
       <c r="L83" t="n">
-        <v>154.93</v>
+        <v>190.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:04:27</t>
+          <t>10:05:37</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>3.46</v>
       </c>
       <c r="F84" t="n">
-        <v>7.85</v>
+        <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>73.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>42.2</v>
+        <v>45.6</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-31.94</v>
+        <v>-12.1</v>
       </c>
       <c r="K84" t="n">
-        <v>151.3</v>
+        <v>200.73</v>
       </c>
       <c r="L84" t="n">
-        <v>154.64</v>
+        <v>201.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:05:56</t>
+          <t>10:07:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,31 +3610,31 @@
         <v>2.48</v>
       </c>
       <c r="F85" t="n">
-        <v>7.9</v>
+        <v>7.19</v>
       </c>
       <c r="G85" t="n">
-        <v>82.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-91.92</v>
+        <v>-109.71</v>
       </c>
       <c r="K85" t="n">
-        <v>97.53</v>
+        <v>141.87</v>
       </c>
       <c r="L85" t="n">
-        <v>134.02</v>
+        <v>179.34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:10:46</t>
+          <t>10:12:03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3652,31 +3652,31 @@
         <v>2.54</v>
       </c>
       <c r="F86" t="n">
-        <v>7.73</v>
+        <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>77.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>46.9</v>
+        <v>47.8</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-149.14</v>
+        <v>-184.42</v>
       </c>
       <c r="K86" t="n">
-        <v>109.23</v>
+        <v>181.98</v>
       </c>
       <c r="L86" t="n">
-        <v>184.86</v>
+        <v>259.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:12:32</t>
+          <t>10:13:54</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="F87" t="n">
-        <v>7.45</v>
+        <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>81.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="H87" t="n">
-        <v>40.3</v>
+        <v>49.8</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-58.45</v>
+        <v>-42.58</v>
       </c>
       <c r="K87" t="n">
-        <v>190.18</v>
+        <v>280.2</v>
       </c>
       <c r="L87" t="n">
-        <v>198.95</v>
+        <v>283.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:14:23</t>
+          <t>10:16:19</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,25 +3736,25 @@
         <v>2.54</v>
       </c>
       <c r="F88" t="n">
-        <v>7.73</v>
+        <v>8.5</v>
       </c>
       <c r="G88" t="n">
-        <v>65</v>
+        <v>76.3</v>
       </c>
       <c r="H88" t="n">
-        <v>46.3</v>
+        <v>41.5</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-90.12</v>
+        <v>-46.28</v>
       </c>
       <c r="K88" t="n">
-        <v>107.05</v>
+        <v>193.1</v>
       </c>
       <c r="L88" t="n">
-        <v>139.94</v>
+        <v>198.57</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>-42.26</v>
+        <v>-46.79</v>
       </c>
       <c r="K14" t="n">
-        <v>45.26</v>
+        <v>50.11</v>
       </c>
       <c r="L14" t="n">
-        <v>61.92</v>
+        <v>68.56</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>10.99</v>
+        <v>12.34</v>
       </c>
       <c r="K15" t="n">
-        <v>82.28</v>
+        <v>92.38</v>
       </c>
       <c r="L15" t="n">
-        <v>83.01000000000001</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-43.84</v>
+        <v>-47.09</v>
       </c>
       <c r="K16" t="n">
-        <v>21.68</v>
+        <v>23.29</v>
       </c>
       <c r="L16" t="n">
-        <v>48.91</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>-61.24</v>
+        <v>-67.8</v>
       </c>
       <c r="K17" t="n">
-        <v>22.13</v>
+        <v>24.5</v>
       </c>
       <c r="L17" t="n">
-        <v>65.11</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-44.02</v>
+        <v>-48.02</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>57.82</v>
       </c>
       <c r="L18" t="n">
-        <v>68.90000000000001</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>-14.62</v>
+        <v>-16.42</v>
       </c>
       <c r="K19" t="n">
-        <v>87.86</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>89.06999999999999</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-120.75</v>
+        <v>-127.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-83.73999999999999</v>
+        <v>-88.48</v>
       </c>
       <c r="L20" t="n">
-        <v>146.94</v>
+        <v>155.26</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>51.92</v>
+        <v>52.94</v>
       </c>
       <c r="K21" t="n">
-        <v>-84.18000000000001</v>
+        <v>-85.83</v>
       </c>
       <c r="L21" t="n">
-        <v>98.90000000000001</v>
+        <v>100.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>34.67</v>
+        <v>35.35</v>
       </c>
       <c r="K22" t="n">
-        <v>-178.38</v>
+        <v>-181.88</v>
       </c>
       <c r="L22" t="n">
-        <v>181.72</v>
+        <v>185.28</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>98.39</v>
+        <v>108.93</v>
       </c>
       <c r="K23" t="n">
-        <v>74.76000000000001</v>
+        <v>82.77</v>
       </c>
       <c r="L23" t="n">
-        <v>123.57</v>
+        <v>136.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>79.84</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-105.59</v>
+        <v>-118.55</v>
       </c>
       <c r="L24" t="n">
-        <v>132.37</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>184.62</v>
+        <v>198.29</v>
       </c>
       <c r="K25" t="n">
-        <v>-34.52</v>
+        <v>-37.08</v>
       </c>
       <c r="L25" t="n">
-        <v>187.82</v>
+        <v>201.73</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-112.93</v>
+        <v>-117.27</v>
       </c>
       <c r="K26" t="n">
-        <v>140.98</v>
+        <v>146.4</v>
       </c>
       <c r="L26" t="n">
-        <v>180.63</v>
+        <v>187.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>213.83</v>
+        <v>225.93</v>
       </c>
       <c r="K27" t="n">
-        <v>102.04</v>
+        <v>107.81</v>
       </c>
       <c r="L27" t="n">
-        <v>236.93</v>
+        <v>250.34</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>124.44</v>
+        <v>129.23</v>
       </c>
       <c r="K28" t="n">
-        <v>175.54</v>
+        <v>182.3</v>
       </c>
       <c r="L28" t="n">
-        <v>215.18</v>
+        <v>223.45</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>-59.45</v>
+        <v>-60.61</v>
       </c>
       <c r="K29" t="n">
-        <v>58.59</v>
+        <v>59.73</v>
       </c>
       <c r="L29" t="n">
-        <v>83.45999999999999</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-15</v>
+        <v>-15.58</v>
       </c>
       <c r="K30" t="n">
-        <v>100.14</v>
+        <v>103.99</v>
       </c>
       <c r="L30" t="n">
-        <v>101.26</v>
+        <v>105.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>66.52</v>
+        <v>71.45</v>
       </c>
       <c r="K31" t="n">
-        <v>24.08</v>
+        <v>25.86</v>
       </c>
       <c r="L31" t="n">
-        <v>70.75</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.05</v>
+        <v>-5.43</v>
       </c>
       <c r="K32" t="n">
-        <v>-74.52</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>74.69</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.06</v>
+        <v>-16.37</v>
       </c>
       <c r="K33" t="n">
-        <v>77.12</v>
+        <v>78.63</v>
       </c>
       <c r="L33" t="n">
-        <v>78.77</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>22.15</v>
+        <v>24.17</v>
       </c>
       <c r="K34" t="n">
-        <v>-88.56</v>
+        <v>-96.61</v>
       </c>
       <c r="L34" t="n">
-        <v>91.29000000000001</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>89.62</v>
+        <v>97.77</v>
       </c>
       <c r="K35" t="n">
-        <v>78.98999999999999</v>
+        <v>86.17</v>
       </c>
       <c r="L35" t="n">
-        <v>119.46</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="K36" t="n">
-        <v>155.05</v>
+        <v>166.54</v>
       </c>
       <c r="L36" t="n">
-        <v>155.07</v>
+        <v>166.56</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>104.54</v>
+        <v>108.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-12.72</v>
+        <v>-13.21</v>
       </c>
       <c r="L37" t="n">
-        <v>105.32</v>
+        <v>109.37</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>130.94</v>
+        <v>147.02</v>
       </c>
       <c r="K38" t="n">
-        <v>127.44</v>
+        <v>143.09</v>
       </c>
       <c r="L38" t="n">
-        <v>182.72</v>
+        <v>205.16</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>153.23</v>
+        <v>164.58</v>
       </c>
       <c r="K39" t="n">
-        <v>129.16</v>
+        <v>138.73</v>
       </c>
       <c r="L39" t="n">
-        <v>200.4</v>
+        <v>215.25</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-79.65000000000001</v>
+        <v>-85.55</v>
       </c>
       <c r="K40" t="n">
-        <v>-174.64</v>
+        <v>-187.58</v>
       </c>
       <c r="L40" t="n">
-        <v>191.95</v>
+        <v>206.17</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>123.26</v>
+        <v>134.47</v>
       </c>
       <c r="K41" t="n">
-        <v>179.69</v>
+        <v>196.03</v>
       </c>
       <c r="L41" t="n">
-        <v>217.91</v>
+        <v>237.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-181.29</v>
+        <v>-191.55</v>
       </c>
       <c r="K42" t="n">
-        <v>-80.38</v>
+        <v>-84.93000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>198.31</v>
+        <v>209.54</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>170.4</v>
+        <v>191.33</v>
       </c>
       <c r="K43" t="n">
-        <v>147.17</v>
+        <v>165.25</v>
       </c>
       <c r="L43" t="n">
-        <v>225.16</v>
+        <v>252.81</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-43.88</v>
+        <v>-47.87</v>
       </c>
       <c r="K44" t="n">
-        <v>-45.51</v>
+        <v>-49.65</v>
       </c>
       <c r="L44" t="n">
-        <v>63.22</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>53.81</v>
+        <v>54.86</v>
       </c>
       <c r="K45" t="n">
-        <v>-27.07</v>
+        <v>-27.6</v>
       </c>
       <c r="L45" t="n">
-        <v>60.23</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.34</v>
+        <v>-21.85</v>
       </c>
       <c r="K46" t="n">
-        <v>84.56999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="L46" t="n">
-        <v>86.98</v>
+        <v>93.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>70.87</v>
+        <v>73.59</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.36</v>
+        <v>-54.38</v>
       </c>
       <c r="L47" t="n">
-        <v>88.11</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>17</v>
       </c>
       <c r="J48" t="n">
-        <v>23.33</v>
+        <v>26.2</v>
       </c>
       <c r="K48" t="n">
-        <v>-91.98</v>
+        <v>-103.28</v>
       </c>
       <c r="L48" t="n">
-        <v>94.90000000000001</v>
+        <v>106.55</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-88.97</v>
+        <v>-92.39</v>
       </c>
       <c r="K49" t="n">
-        <v>75.13</v>
+        <v>78.02</v>
       </c>
       <c r="L49" t="n">
-        <v>116.45</v>
+        <v>120.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>3.92</v>
+        <v>4.4</v>
       </c>
       <c r="K50" t="n">
-        <v>95.76000000000001</v>
+        <v>107.52</v>
       </c>
       <c r="L50" t="n">
-        <v>95.84</v>
+        <v>107.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.49</v>
+        <v>-10.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-171.49</v>
+        <v>-178.09</v>
       </c>
       <c r="L51" t="n">
-        <v>171.81</v>
+        <v>178.42</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-115.01</v>
+        <v>-117.27</v>
       </c>
       <c r="K52" t="n">
         <v>0.42</v>
       </c>
       <c r="L52" t="n">
-        <v>115.01</v>
+        <v>117.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="K53" t="n">
-        <v>170.94</v>
+        <v>186.48</v>
       </c>
       <c r="L53" t="n">
-        <v>174.16</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-145.98</v>
+        <v>-161.62</v>
       </c>
       <c r="K54" t="n">
-        <v>-96.73999999999999</v>
+        <v>-107.11</v>
       </c>
       <c r="L54" t="n">
-        <v>175.12</v>
+        <v>193.89</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-169.59</v>
+        <v>-187.76</v>
       </c>
       <c r="K55" t="n">
-        <v>-57.98</v>
+        <v>-64.2</v>
       </c>
       <c r="L55" t="n">
-        <v>179.23</v>
+        <v>198.43</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>42.54</v>
+        <v>43.38</v>
       </c>
       <c r="K56" t="n">
-        <v>319.11</v>
+        <v>325.36</v>
       </c>
       <c r="L56" t="n">
-        <v>321.93</v>
+        <v>328.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>136.21</v>
+        <v>150.81</v>
       </c>
       <c r="K57" t="n">
-        <v>274</v>
+        <v>303.36</v>
       </c>
       <c r="L57" t="n">
-        <v>305.99</v>
+        <v>338.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>124.96</v>
+        <v>129.76</v>
       </c>
       <c r="K58" t="n">
-        <v>281.25</v>
+        <v>292.07</v>
       </c>
       <c r="L58" t="n">
-        <v>307.76</v>
+        <v>319.6</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>17.1</v>
+        <v>18.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-85.09</v>
+        <v>-91.39</v>
       </c>
       <c r="L59" t="n">
-        <v>86.79000000000001</v>
+        <v>93.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-35.11</v>
+        <v>-38.3</v>
       </c>
       <c r="K60" t="n">
-        <v>50.62</v>
+        <v>55.23</v>
       </c>
       <c r="L60" t="n">
-        <v>61.61</v>
+        <v>67.20999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>61.57</v>
+        <v>67.16</v>
       </c>
       <c r="K61" t="n">
-        <v>27.52</v>
+        <v>30.02</v>
       </c>
       <c r="L61" t="n">
-        <v>67.44</v>
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.19</v>
+        <v>-69.93000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-38.96</v>
+        <v>-41.16</v>
       </c>
       <c r="L62" t="n">
-        <v>76.8</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-60.33</v>
+        <v>-61.52</v>
       </c>
       <c r="K63" t="n">
-        <v>-62.41</v>
+        <v>-63.63</v>
       </c>
       <c r="L63" t="n">
-        <v>86.8</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-17.52</v>
+        <v>-19.11</v>
       </c>
       <c r="K64" t="n">
-        <v>82.56</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>84.40000000000001</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>170.31</v>
+        <v>191.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-61.29</v>
+        <v>-68.81</v>
       </c>
       <c r="L65" t="n">
-        <v>181</v>
+        <v>203.23</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>12.53</v>
+        <v>13.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-129.68</v>
+        <v>-134.67</v>
       </c>
       <c r="L66" t="n">
-        <v>130.29</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>77.29000000000001</v>
+        <v>83.02</v>
       </c>
       <c r="K67" t="n">
-        <v>-98.34</v>
+        <v>-105.62</v>
       </c>
       <c r="L67" t="n">
-        <v>125.08</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>-59.56</v>
+        <v>-64.98</v>
       </c>
       <c r="K68" t="n">
-        <v>208.4</v>
+        <v>227.34</v>
       </c>
       <c r="L68" t="n">
-        <v>216.74</v>
+        <v>236.45</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>117.22</v>
+        <v>129.78</v>
       </c>
       <c r="K69" t="n">
-        <v>134.53</v>
+        <v>148.94</v>
       </c>
       <c r="L69" t="n">
-        <v>178.43</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>61.01</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>170</v>
+        <v>179.63</v>
       </c>
       <c r="L70" t="n">
-        <v>180.62</v>
+        <v>190.84</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-192.56</v>
+        <v>-203.45</v>
       </c>
       <c r="K71" t="n">
-        <v>100.76</v>
+        <v>106.47</v>
       </c>
       <c r="L71" t="n">
-        <v>217.33</v>
+        <v>229.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>181.29</v>
+        <v>197.77</v>
       </c>
       <c r="K72" t="n">
-        <v>-145.21</v>
+        <v>-158.41</v>
       </c>
       <c r="L72" t="n">
-        <v>232.27</v>
+        <v>253.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>244.94</v>
+        <v>275.02</v>
       </c>
       <c r="K73" t="n">
-        <v>180.03</v>
+        <v>202.14</v>
       </c>
       <c r="L73" t="n">
-        <v>303.98</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.46</v>
+        <v>-49.92</v>
       </c>
       <c r="K74" t="n">
-        <v>46.95</v>
+        <v>52.71</v>
       </c>
       <c r="L74" t="n">
-        <v>64.66</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.8</v>
+        <v>-11.96</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.20999999999999</v>
+        <v>-71.08</v>
       </c>
       <c r="L75" t="n">
-        <v>65.11</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>17</v>
       </c>
       <c r="J76" t="n">
-        <v>45.66</v>
+        <v>51.27</v>
       </c>
       <c r="K76" t="n">
-        <v>44.89</v>
+        <v>50.4</v>
       </c>
       <c r="L76" t="n">
-        <v>64.03</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>76.38</v>
+        <v>77.87</v>
       </c>
       <c r="K77" t="n">
-        <v>48.49</v>
+        <v>49.44</v>
       </c>
       <c r="L77" t="n">
-        <v>90.47</v>
+        <v>92.23999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>70.41</v>
+        <v>75.62</v>
       </c>
       <c r="K78" t="n">
-        <v>39.44</v>
+        <v>42.37</v>
       </c>
       <c r="L78" t="n">
-        <v>80.70999999999999</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-68.66</v>
+        <v>-76.02</v>
       </c>
       <c r="K79" t="n">
-        <v>-33.81</v>
+        <v>-37.43</v>
       </c>
       <c r="L79" t="n">
-        <v>76.54000000000001</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>94.75</v>
+        <v>101.77</v>
       </c>
       <c r="K80" t="n">
-        <v>-98.48</v>
+        <v>-105.78</v>
       </c>
       <c r="L80" t="n">
-        <v>136.66</v>
+        <v>146.78</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>94.59999999999999</v>
+        <v>101.6</v>
       </c>
       <c r="K81" t="n">
-        <v>-46.95</v>
+        <v>-50.43</v>
       </c>
       <c r="L81" t="n">
-        <v>105.61</v>
+        <v>113.43</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>85.23999999999999</v>
+        <v>88.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-95.48999999999999</v>
+        <v>-99.16</v>
       </c>
       <c r="L82" t="n">
-        <v>128</v>
+        <v>132.93</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>45.09</v>
+        <v>46.82</v>
       </c>
       <c r="K83" t="n">
-        <v>-185.59</v>
+        <v>-192.73</v>
       </c>
       <c r="L83" t="n">
-        <v>190.99</v>
+        <v>198.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.1</v>
+        <v>-12.79</v>
       </c>
       <c r="K84" t="n">
-        <v>200.73</v>
+        <v>212.15</v>
       </c>
       <c r="L84" t="n">
-        <v>201.09</v>
+        <v>212.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-109.71</v>
+        <v>-117.83</v>
       </c>
       <c r="K85" t="n">
-        <v>141.87</v>
+        <v>152.37</v>
       </c>
       <c r="L85" t="n">
-        <v>179.34</v>
+        <v>192.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-184.42</v>
+        <v>-198.08</v>
       </c>
       <c r="K86" t="n">
-        <v>181.98</v>
+        <v>195.46</v>
       </c>
       <c r="L86" t="n">
-        <v>259.09</v>
+        <v>278.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-42.58</v>
+        <v>-44.99</v>
       </c>
       <c r="K87" t="n">
-        <v>280.2</v>
+        <v>296.06</v>
       </c>
       <c r="L87" t="n">
-        <v>283.42</v>
+        <v>299.46</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-46.28</v>
+        <v>-51.23</v>
       </c>
       <c r="K88" t="n">
-        <v>193.1</v>
+        <v>213.79</v>
       </c>
       <c r="L88" t="n">
-        <v>198.57</v>
+        <v>219.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="F14" t="n">
-        <v>8.550000000000001</v>
+        <v>5.92</v>
       </c>
       <c r="G14" t="n">
-        <v>72</v>
+        <v>58.6</v>
       </c>
       <c r="H14" t="n">
-        <v>44.6</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-46.79</v>
+        <v>26.74</v>
       </c>
       <c r="K14" t="n">
-        <v>50.11</v>
+        <v>21.39</v>
       </c>
       <c r="L14" t="n">
-        <v>68.56</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:35:50</t>
+          <t>06:34:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="F15" t="n">
-        <v>4.57</v>
+        <v>6.63</v>
       </c>
       <c r="G15" t="n">
-        <v>86.8</v>
+        <v>62</v>
       </c>
       <c r="H15" t="n">
-        <v>45.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>12.34</v>
+        <v>21.31</v>
       </c>
       <c r="K15" t="n">
-        <v>92.38</v>
+        <v>-27.05</v>
       </c>
       <c r="L15" t="n">
-        <v>93.2</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:37:24</t>
+          <t>06:36:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="F16" t="n">
-        <v>5.97</v>
+        <v>5.22</v>
       </c>
       <c r="G16" t="n">
-        <v>67.09999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="H16" t="n">
-        <v>51</v>
+        <v>42.1</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>-47.09</v>
+        <v>-7.34</v>
       </c>
       <c r="K16" t="n">
-        <v>23.29</v>
+        <v>-24.46</v>
       </c>
       <c r="L16" t="n">
-        <v>52.53</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:41:35</t>
+          <t>06:41:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.03</v>
+        <v>3.14</v>
       </c>
       <c r="F17" t="n">
-        <v>6.63</v>
+        <v>8.74</v>
       </c>
       <c r="G17" t="n">
-        <v>70.90000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="H17" t="n">
-        <v>43.1</v>
+        <v>58.7</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-67.8</v>
+        <v>-0.02</v>
       </c>
       <c r="K17" t="n">
-        <v>24.5</v>
+        <v>-81.92</v>
       </c>
       <c r="L17" t="n">
-        <v>72.09</v>
+        <v>81.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:42:38</t>
+          <t>06:42:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>6.15</v>
+        <v>5.43</v>
       </c>
       <c r="G18" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
       <c r="H18" t="n">
-        <v>43.3</v>
+        <v>36.8</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.02</v>
+        <v>49.36</v>
       </c>
       <c r="K18" t="n">
-        <v>57.82</v>
+        <v>12.39</v>
       </c>
       <c r="L18" t="n">
-        <v>75.16</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:44:50</t>
+          <t>06:44:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="F19" t="n">
-        <v>8.74</v>
+        <v>7.62</v>
       </c>
       <c r="G19" t="n">
-        <v>77.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>38.8</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.42</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>98.65000000000001</v>
+        <v>59.28</v>
       </c>
       <c r="L19" t="n">
-        <v>100.01</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:49:10</t>
+          <t>06:48:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="F20" t="n">
-        <v>6.33</v>
+        <v>2.53</v>
       </c>
       <c r="G20" t="n">
-        <v>71.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-127.58</v>
+        <v>-60.38</v>
       </c>
       <c r="K20" t="n">
-        <v>-88.48</v>
+        <v>-76.39</v>
       </c>
       <c r="L20" t="n">
-        <v>155.26</v>
+        <v>97.37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:50:27</t>
+          <t>06:49:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.03</v>
+        <v>2.69</v>
       </c>
       <c r="F21" t="n">
-        <v>5.18</v>
+        <v>7.67</v>
       </c>
       <c r="G21" t="n">
-        <v>77.7</v>
+        <v>74.7</v>
       </c>
       <c r="H21" t="n">
-        <v>49.7</v>
+        <v>8.5</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>52.94</v>
+        <v>38.9</v>
       </c>
       <c r="K21" t="n">
-        <v>-85.83</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>100.84</v>
+        <v>99.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:51:56</t>
+          <t>06:50:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.49</v>
+        <v>3.48</v>
       </c>
       <c r="F22" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="G22" t="n">
-        <v>75.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H22" t="n">
-        <v>50.6</v>
+        <v>29.4</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>35.35</v>
+        <v>-129.18</v>
       </c>
       <c r="K22" t="n">
-        <v>-181.88</v>
+        <v>-12.45</v>
       </c>
       <c r="L22" t="n">
-        <v>185.28</v>
+        <v>129.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:56:44</t>
+          <t>06:54:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="F23" t="n">
-        <v>6.77</v>
+        <v>7.83</v>
       </c>
       <c r="G23" t="n">
-        <v>64.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H23" t="n">
-        <v>45.6</v>
+        <v>59.5</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>108.93</v>
+        <v>178.93</v>
       </c>
       <c r="K23" t="n">
-        <v>82.77</v>
+        <v>24.54</v>
       </c>
       <c r="L23" t="n">
-        <v>136.8</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:59:01</t>
+          <t>06:57:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="F24" t="n">
-        <v>4.83</v>
+        <v>5.8</v>
       </c>
       <c r="G24" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="H24" t="n">
-        <v>46.6</v>
+        <v>40.5</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>89.65000000000001</v>
+        <v>-127.23</v>
       </c>
       <c r="K24" t="n">
-        <v>-118.55</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>148.63</v>
+        <v>148.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:00:48</t>
+          <t>06:59:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="F25" t="n">
-        <v>6.14</v>
+        <v>8.74</v>
       </c>
       <c r="G25" t="n">
-        <v>64.3</v>
+        <v>66.2</v>
       </c>
       <c r="H25" t="n">
-        <v>40.8</v>
+        <v>53.7</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>198.29</v>
+        <v>91.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-37.08</v>
+        <v>116.87</v>
       </c>
       <c r="L25" t="n">
-        <v>201.73</v>
+        <v>148.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:05:47</t>
+          <t>07:03:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="F26" t="n">
-        <v>5.04</v>
+        <v>8.74</v>
       </c>
       <c r="G26" t="n">
-        <v>93.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>45</v>
+        <v>11.1</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-117.27</v>
+        <v>123.69</v>
       </c>
       <c r="K26" t="n">
-        <v>146.4</v>
+        <v>117.17</v>
       </c>
       <c r="L26" t="n">
-        <v>187.58</v>
+        <v>170.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:08:30</t>
+          <t>07:05:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="F27" t="n">
-        <v>8.09</v>
+        <v>6.8</v>
       </c>
       <c r="G27" t="n">
-        <v>69.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="H27" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>225.93</v>
+        <v>-122.05</v>
       </c>
       <c r="K27" t="n">
-        <v>107.81</v>
+        <v>-176.51</v>
       </c>
       <c r="L27" t="n">
-        <v>250.34</v>
+        <v>214.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:10:32</t>
+          <t>07:07:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="F28" t="n">
-        <v>6.77</v>
+        <v>6.55</v>
       </c>
       <c r="G28" t="n">
-        <v>64.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>50.2</v>
+        <v>24.7</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>129.23</v>
+        <v>115.2</v>
       </c>
       <c r="K28" t="n">
-        <v>182.3</v>
+        <v>181.9</v>
       </c>
       <c r="L28" t="n">
-        <v>223.45</v>
+        <v>215.31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:20:08</t>
+          <t>07:16:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="F29" t="n">
-        <v>4.65</v>
+        <v>6.32</v>
       </c>
       <c r="G29" t="n">
-        <v>69.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="H29" t="n">
-        <v>49.5</v>
+        <v>61.7</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-60.61</v>
+        <v>15.69</v>
       </c>
       <c r="K29" t="n">
-        <v>59.73</v>
+        <v>33.65</v>
       </c>
       <c r="L29" t="n">
-        <v>85.09999999999999</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:21:26</t>
+          <t>07:19:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="F30" t="n">
-        <v>8.74</v>
+        <v>6.19</v>
       </c>
       <c r="G30" t="n">
-        <v>71.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>48.2</v>
+        <v>70.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.58</v>
+        <v>21.6</v>
       </c>
       <c r="K30" t="n">
-        <v>103.99</v>
+        <v>-33.24</v>
       </c>
       <c r="L30" t="n">
-        <v>105.15</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:23:13</t>
+          <t>07:20:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="F31" t="n">
-        <v>8.27</v>
+        <v>4.12</v>
       </c>
       <c r="G31" t="n">
-        <v>68.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="H31" t="n">
-        <v>51.9</v>
+        <v>80.3</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>71.45</v>
+        <v>-8.31</v>
       </c>
       <c r="K31" t="n">
-        <v>25.86</v>
+        <v>37.37</v>
       </c>
       <c r="L31" t="n">
-        <v>75.98999999999999</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:27:59</t>
+          <t>07:23:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="F32" t="n">
-        <v>7.05</v>
+        <v>4.83</v>
       </c>
       <c r="G32" t="n">
-        <v>70.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="H32" t="n">
-        <v>43.6</v>
+        <v>67.7</v>
       </c>
       <c r="I32" t="n">
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.43</v>
+        <v>30.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-80.04000000000001</v>
+        <v>-58.2</v>
       </c>
       <c r="L32" t="n">
-        <v>80.23</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:29:25</t>
+          <t>07:24:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="F33" t="n">
-        <v>7.95</v>
+        <v>8.74</v>
       </c>
       <c r="G33" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="H33" t="n">
-        <v>44.9</v>
+        <v>33.8</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.37</v>
+        <v>67.58</v>
       </c>
       <c r="K33" t="n">
-        <v>78.63</v>
+        <v>-79.8</v>
       </c>
       <c r="L33" t="n">
-        <v>80.31999999999999</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:31:08</t>
+          <t>07:26:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1468,31 +1468,31 @@
         <v>2.61</v>
       </c>
       <c r="F34" t="n">
-        <v>6.2</v>
+        <v>7.35</v>
       </c>
       <c r="G34" t="n">
-        <v>87.5</v>
+        <v>78.3</v>
       </c>
       <c r="H34" t="n">
-        <v>46.3</v>
+        <v>57.2</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>24.17</v>
+        <v>27.18</v>
       </c>
       <c r="K34" t="n">
-        <v>-96.61</v>
+        <v>-63.02</v>
       </c>
       <c r="L34" t="n">
-        <v>99.59</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:36:08</t>
+          <t>07:31:03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="F35" t="n">
-        <v>5.95</v>
+        <v>8.74</v>
       </c>
       <c r="G35" t="n">
-        <v>69.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>45.9</v>
+        <v>25.2</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>97.77</v>
+        <v>101.28</v>
       </c>
       <c r="K35" t="n">
-        <v>86.17</v>
+        <v>-14.6</v>
       </c>
       <c r="L35" t="n">
-        <v>130.32</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:36:48</t>
+          <t>07:32:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="F36" t="n">
-        <v>8.34</v>
+        <v>7.32</v>
       </c>
       <c r="G36" t="n">
-        <v>65.5</v>
+        <v>78.2</v>
       </c>
       <c r="H36" t="n">
-        <v>48.6</v>
+        <v>52.7</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>2.61</v>
+        <v>116.14</v>
       </c>
       <c r="K36" t="n">
-        <v>166.54</v>
+        <v>-10.29</v>
       </c>
       <c r="L36" t="n">
-        <v>166.56</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:38:17</t>
+          <t>07:33:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="F37" t="n">
         <v>8.74</v>
       </c>
       <c r="G37" t="n">
-        <v>81.5</v>
+        <v>73.3</v>
       </c>
       <c r="H37" t="n">
-        <v>49.8</v>
+        <v>38</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>108.57</v>
+        <v>102.05</v>
       </c>
       <c r="K37" t="n">
-        <v>-13.21</v>
+        <v>43.6</v>
       </c>
       <c r="L37" t="n">
-        <v>109.37</v>
+        <v>110.97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:43:52</t>
+          <t>07:39:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="F38" t="n">
         <v>8.74</v>
       </c>
       <c r="G38" t="n">
-        <v>72.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="H38" t="n">
-        <v>46.2</v>
+        <v>68.3</v>
       </c>
       <c r="I38" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>147.02</v>
+        <v>131.72</v>
       </c>
       <c r="K38" t="n">
-        <v>143.09</v>
+        <v>4.72</v>
       </c>
       <c r="L38" t="n">
-        <v>205.16</v>
+        <v>131.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:45:29</t>
+          <t>07:40:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.27</v>
+        <v>2.61</v>
       </c>
       <c r="F39" t="n">
-        <v>5.78</v>
+        <v>8.74</v>
       </c>
       <c r="G39" t="n">
-        <v>81.5</v>
+        <v>70</v>
       </c>
       <c r="H39" t="n">
-        <v>49</v>
+        <v>37.4</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>164.58</v>
+        <v>-21.67</v>
       </c>
       <c r="K39" t="n">
-        <v>138.73</v>
+        <v>98.42</v>
       </c>
       <c r="L39" t="n">
-        <v>215.25</v>
+        <v>100.78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:46:42</t>
+          <t>07:41:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="F40" t="n">
-        <v>8.74</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>74.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>45.7</v>
+        <v>36.4</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-85.55</v>
+        <v>-19.78</v>
       </c>
       <c r="K40" t="n">
-        <v>-187.58</v>
+        <v>-176.13</v>
       </c>
       <c r="L40" t="n">
-        <v>206.17</v>
+        <v>177.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:51:29</t>
+          <t>07:46:03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="F41" t="n">
         <v>8.74</v>
       </c>
       <c r="G41" t="n">
-        <v>77.8</v>
+        <v>72.3</v>
       </c>
       <c r="H41" t="n">
-        <v>40.9</v>
+        <v>46.4</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>134.47</v>
+        <v>214.5</v>
       </c>
       <c r="K41" t="n">
-        <v>196.03</v>
+        <v>-54.42</v>
       </c>
       <c r="L41" t="n">
-        <v>237.72</v>
+        <v>221.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:52:08</t>
+          <t>07:47:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="F42" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="G42" t="n">
-        <v>74.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>38.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-191.55</v>
+        <v>-183.68</v>
       </c>
       <c r="K42" t="n">
-        <v>-84.93000000000001</v>
+        <v>106.37</v>
       </c>
       <c r="L42" t="n">
-        <v>209.54</v>
+        <v>212.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:54:21</t>
+          <t>07:49:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="F43" t="n">
-        <v>7.36</v>
+        <v>7.38</v>
       </c>
       <c r="G43" t="n">
-        <v>82.8</v>
+        <v>73.7</v>
       </c>
       <c r="H43" t="n">
-        <v>48.9</v>
+        <v>30.8</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>191.33</v>
+        <v>153.76</v>
       </c>
       <c r="K43" t="n">
-        <v>165.25</v>
+        <v>78.12</v>
       </c>
       <c r="L43" t="n">
-        <v>252.81</v>
+        <v>172.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:56</t>
+          <t>07:58:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="F44" t="n">
-        <v>7.07</v>
+        <v>4.31</v>
       </c>
       <c r="G44" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>42.6</v>
+        <v>51.7</v>
       </c>
       <c r="I44" t="n">
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-47.87</v>
+        <v>15.52</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.65</v>
+        <v>22.78</v>
       </c>
       <c r="L44" t="n">
-        <v>68.97</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:07:00</t>
+          <t>08:00:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="F45" t="n">
-        <v>6.83</v>
+        <v>8.1</v>
       </c>
       <c r="G45" t="n">
-        <v>69.2</v>
+        <v>74.8</v>
       </c>
       <c r="H45" t="n">
-        <v>49.1</v>
+        <v>60.2</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>54.86</v>
+        <v>-36.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-27.6</v>
+        <v>21.93</v>
       </c>
       <c r="L45" t="n">
-        <v>61.42</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:07:50</t>
+          <t>08:01:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="F46" t="n">
-        <v>8.74</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>64.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="H46" t="n">
-        <v>46</v>
+        <v>10.2</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.85</v>
+        <v>28.15</v>
       </c>
       <c r="K46" t="n">
-        <v>90.83</v>
+        <v>-28.66</v>
       </c>
       <c r="L46" t="n">
-        <v>93.42</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:10:46</t>
+          <t>08:07:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="F47" t="n">
-        <v>8.300000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="G47" t="n">
-        <v>88.3</v>
+        <v>71.8</v>
       </c>
       <c r="H47" t="n">
-        <v>52.2</v>
+        <v>59.4</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>73.59</v>
+        <v>-26.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-54.38</v>
+        <v>55.48</v>
       </c>
       <c r="L47" t="n">
-        <v>91.5</v>
+        <v>61.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:12:31</t>
+          <t>08:09:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="F48" t="n">
-        <v>6.66</v>
+        <v>7.44</v>
       </c>
       <c r="G48" t="n">
-        <v>80.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="H48" t="n">
-        <v>43.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>26.2</v>
+        <v>-63.46</v>
       </c>
       <c r="K48" t="n">
-        <v>-103.28</v>
+        <v>-36.68</v>
       </c>
       <c r="L48" t="n">
-        <v>106.55</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:13:41</t>
+          <t>08:11:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="F49" t="n">
-        <v>8.74</v>
+        <v>8.01</v>
       </c>
       <c r="G49" t="n">
-        <v>67.7</v>
+        <v>75.7</v>
       </c>
       <c r="H49" t="n">
-        <v>50.1</v>
+        <v>54.6</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-92.39</v>
+        <v>-29.08</v>
       </c>
       <c r="K49" t="n">
-        <v>78.02</v>
+        <v>-85.05</v>
       </c>
       <c r="L49" t="n">
-        <v>120.93</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:18:56</t>
+          <t>08:17:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="F50" t="n">
-        <v>8.74</v>
+        <v>6.11</v>
       </c>
       <c r="G50" t="n">
-        <v>73.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="H50" t="n">
-        <v>51</v>
+        <v>39.5</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>4.4</v>
+        <v>-52.03</v>
       </c>
       <c r="K50" t="n">
-        <v>107.52</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>107.61</v>
+        <v>98.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:20:29</t>
+          <t>08:17:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F51" t="n">
         <v>8.74</v>
       </c>
       <c r="G51" t="n">
-        <v>79.7</v>
+        <v>72.3</v>
       </c>
       <c r="H51" t="n">
-        <v>41.2</v>
+        <v>36.3</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.89</v>
+        <v>30.55</v>
       </c>
       <c r="K51" t="n">
-        <v>-178.09</v>
+        <v>-85.20999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>178.42</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:18:54</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="F52" t="n">
-        <v>7.17</v>
+        <v>3.52</v>
       </c>
       <c r="G52" t="n">
-        <v>75.2</v>
+        <v>79.8</v>
       </c>
       <c r="H52" t="n">
-        <v>46.4</v>
+        <v>40.1</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>-117.27</v>
+        <v>13.89</v>
       </c>
       <c r="K52" t="n">
-        <v>0.42</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>117.27</v>
+        <v>85.15000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:26:00</t>
+          <t>08:23:53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="F53" t="n">
-        <v>8.109999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="G53" t="n">
-        <v>68.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>51.5</v>
+        <v>57.4</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>36.36</v>
+        <v>46.83</v>
       </c>
       <c r="K53" t="n">
-        <v>186.48</v>
+        <v>-113.85</v>
       </c>
       <c r="L53" t="n">
-        <v>190</v>
+        <v>123.11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:28:09</t>
+          <t>08:25:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="F54" t="n">
-        <v>6.76</v>
+        <v>6.39</v>
       </c>
       <c r="G54" t="n">
-        <v>76.2</v>
+        <v>88.3</v>
       </c>
       <c r="H54" t="n">
-        <v>46.4</v>
+        <v>76</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-161.62</v>
+        <v>-135.52</v>
       </c>
       <c r="K54" t="n">
-        <v>-107.11</v>
+        <v>25.22</v>
       </c>
       <c r="L54" t="n">
-        <v>193.89</v>
+        <v>137.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:30:08</t>
+          <t>08:26:31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.51</v>
+        <v>2.91</v>
       </c>
       <c r="F55" t="n">
         <v>8.74</v>
       </c>
       <c r="G55" t="n">
-        <v>72.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="H55" t="n">
-        <v>52.1</v>
+        <v>45.6</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>-187.76</v>
+        <v>144.33</v>
       </c>
       <c r="K55" t="n">
-        <v>-64.2</v>
+        <v>31.47</v>
       </c>
       <c r="L55" t="n">
-        <v>198.43</v>
+        <v>147.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:34:07</t>
+          <t>08:30:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="F56" t="n">
-        <v>8.51</v>
+        <v>3.31</v>
       </c>
       <c r="G56" t="n">
-        <v>78.8</v>
+        <v>75</v>
       </c>
       <c r="H56" t="n">
-        <v>51.4</v>
+        <v>32.3</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>43.38</v>
+        <v>-85.81999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>325.36</v>
+        <v>-167.64</v>
       </c>
       <c r="L56" t="n">
-        <v>328.24</v>
+        <v>188.33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:36:01</t>
+          <t>08:32:06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="F57" t="n">
-        <v>5.37</v>
+        <v>8.66</v>
       </c>
       <c r="G57" t="n">
-        <v>71</v>
+        <v>71.3</v>
       </c>
       <c r="H57" t="n">
-        <v>49.2</v>
+        <v>80.2</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>150.81</v>
+        <v>157.95</v>
       </c>
       <c r="K57" t="n">
-        <v>303.36</v>
+        <v>-102.25</v>
       </c>
       <c r="L57" t="n">
-        <v>338.78</v>
+        <v>188.15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:38:02</t>
+          <t>08:34:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.19</v>
+        <v>2.76</v>
       </c>
       <c r="F58" t="n">
-        <v>5.97</v>
+        <v>8.74</v>
       </c>
       <c r="G58" t="n">
-        <v>82.2</v>
+        <v>66</v>
       </c>
       <c r="H58" t="n">
-        <v>38</v>
+        <v>26.5</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>129.76</v>
+        <v>95.11</v>
       </c>
       <c r="K58" t="n">
-        <v>292.07</v>
+        <v>-135.16</v>
       </c>
       <c r="L58" t="n">
-        <v>319.6</v>
+        <v>165.27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:49:49</t>
+          <t>08:46:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="F59" t="n">
-        <v>8.050000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="G59" t="n">
-        <v>68.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>43.6</v>
+        <v>47.2</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>18.37</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-91.39</v>
+        <v>24.29</v>
       </c>
       <c r="L59" t="n">
-        <v>93.22</v>
+        <v>26.03</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:50:58</t>
+          <t>08:48:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="F60" t="n">
-        <v>7.95</v>
+        <v>6.13</v>
       </c>
       <c r="G60" t="n">
-        <v>72.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>42.9</v>
+        <v>21.9</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.3</v>
+        <v>-31.2</v>
       </c>
       <c r="K60" t="n">
-        <v>55.23</v>
+        <v>6.61</v>
       </c>
       <c r="L60" t="n">
-        <v>67.20999999999999</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:52:19</t>
+          <t>08:50:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="F61" t="n">
-        <v>7.63</v>
+        <v>5.04</v>
       </c>
       <c r="G61" t="n">
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="H61" t="n">
-        <v>48.2</v>
+        <v>14.7</v>
       </c>
       <c r="I61" t="n">
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>67.16</v>
+        <v>37.63</v>
       </c>
       <c r="K61" t="n">
-        <v>30.02</v>
+        <v>-11.87</v>
       </c>
       <c r="L61" t="n">
-        <v>73.56999999999999</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:58:20</t>
+          <t>08:53:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="F62" t="n">
-        <v>6.79</v>
+        <v>5.45</v>
       </c>
       <c r="G62" t="n">
-        <v>83.8</v>
+        <v>64.7</v>
       </c>
       <c r="H62" t="n">
-        <v>45.6</v>
+        <v>57</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-69.93000000000001</v>
+        <v>-10.76</v>
       </c>
       <c r="K62" t="n">
-        <v>-41.16</v>
+        <v>65.72</v>
       </c>
       <c r="L62" t="n">
-        <v>81.15000000000001</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:00:26</t>
+          <t>08:54:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="F63" t="n">
         <v>8.74</v>
       </c>
       <c r="G63" t="n">
-        <v>85.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>49.5</v>
+        <v>40.7</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.52</v>
+        <v>23.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-63.63</v>
+        <v>52.33</v>
       </c>
       <c r="L63" t="n">
-        <v>88.51000000000001</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:03:00</t>
+          <t>08:56:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="F64" t="n">
-        <v>6.13</v>
+        <v>8.74</v>
       </c>
       <c r="G64" t="n">
-        <v>69.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H64" t="n">
-        <v>44.1</v>
+        <v>36.2</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-19.11</v>
+        <v>43.71</v>
       </c>
       <c r="K64" t="n">
-        <v>90.06999999999999</v>
+        <v>12.16</v>
       </c>
       <c r="L64" t="n">
-        <v>92.06999999999999</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:07:32</t>
+          <t>09:00:48</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="F65" t="n">
-        <v>8.74</v>
+        <v>5.13</v>
       </c>
       <c r="G65" t="n">
-        <v>75.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>45.9</v>
+        <v>76</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>191.22</v>
+        <v>53.45</v>
       </c>
       <c r="K65" t="n">
-        <v>-68.81</v>
+        <v>-22.9</v>
       </c>
       <c r="L65" t="n">
-        <v>203.23</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:08:48</t>
+          <t>09:02:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.84</v>
+        <v>2.67</v>
       </c>
       <c r="F66" t="n">
-        <v>6.12</v>
+        <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>83.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>49</v>
+        <v>42.7</v>
       </c>
       <c r="I66" t="n">
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>13.01</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-134.67</v>
+        <v>65.08</v>
       </c>
       <c r="L66" t="n">
-        <v>135.3</v>
+        <v>110.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:09:54</t>
+          <t>09:04:05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="F67" t="n">
-        <v>6.53</v>
+        <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>69.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>46.8</v>
+        <v>71</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>83.02</v>
+        <v>50.61</v>
       </c>
       <c r="K67" t="n">
-        <v>-105.62</v>
+        <v>-85.13</v>
       </c>
       <c r="L67" t="n">
-        <v>134.34</v>
+        <v>99.04000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:15:29</t>
+          <t>09:09:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="F68" t="n">
-        <v>8.74</v>
+        <v>8.48</v>
       </c>
       <c r="G68" t="n">
-        <v>68.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>50.9</v>
+        <v>63</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-64.98</v>
+        <v>-37.2</v>
       </c>
       <c r="K68" t="n">
-        <v>227.34</v>
+        <v>-88.01000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>236.45</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:17:00</t>
+          <t>09:11:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.37</v>
+        <v>3.22</v>
       </c>
       <c r="F69" t="n">
-        <v>6.34</v>
+        <v>8.74</v>
       </c>
       <c r="G69" t="n">
-        <v>65.59999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="H69" t="n">
-        <v>48.3</v>
+        <v>68.7</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>129.78</v>
+        <v>134.32</v>
       </c>
       <c r="K69" t="n">
-        <v>148.94</v>
+        <v>-63.31</v>
       </c>
       <c r="L69" t="n">
-        <v>197.55</v>
+        <v>148.49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:18:22</t>
+          <t>09:12:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="F70" t="n">
-        <v>8.74</v>
+        <v>8.35</v>
       </c>
       <c r="G70" t="n">
-        <v>63.4</v>
+        <v>65.7</v>
       </c>
       <c r="H70" t="n">
-        <v>46.4</v>
+        <v>32.9</v>
       </c>
       <c r="I70" t="n">
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>64.45999999999999</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>179.63</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>190.84</v>
+        <v>122.19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:22:56</t>
+          <t>09:16:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="F71" t="n">
         <v>8.74</v>
       </c>
       <c r="G71" t="n">
-        <v>72.5</v>
+        <v>79.7</v>
       </c>
       <c r="H71" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-203.45</v>
+        <v>33.48</v>
       </c>
       <c r="K71" t="n">
-        <v>106.47</v>
+        <v>-44.09</v>
       </c>
       <c r="L71" t="n">
-        <v>229.63</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:24:47</t>
+          <t>09:17:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.71</v>
+        <v>2.32</v>
       </c>
       <c r="F72" t="n">
-        <v>8.74</v>
+        <v>6.25</v>
       </c>
       <c r="G72" t="n">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="H72" t="n">
-        <v>46.9</v>
+        <v>26.5</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>197.77</v>
+        <v>-153.6</v>
       </c>
       <c r="K72" t="n">
-        <v>-158.41</v>
+        <v>-95.88</v>
       </c>
       <c r="L72" t="n">
-        <v>253.39</v>
+        <v>181.07</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:26:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="F73" t="n">
-        <v>7.6</v>
+        <v>8.74</v>
       </c>
       <c r="G73" t="n">
-        <v>69.5</v>
+        <v>63.7</v>
       </c>
       <c r="H73" t="n">
-        <v>43.4</v>
+        <v>36</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>275.02</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>202.14</v>
+        <v>-178.45</v>
       </c>
       <c r="L73" t="n">
-        <v>341.32</v>
+        <v>198.83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:38:10</t>
+          <t>09:28:50</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="F74" t="n">
-        <v>8.720000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="G74" t="n">
-        <v>71.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>58</v>
+        <v>72.3</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.92</v>
+        <v>-50.14</v>
       </c>
       <c r="K74" t="n">
-        <v>52.71</v>
+        <v>7.44</v>
       </c>
       <c r="L74" t="n">
-        <v>72.59999999999999</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:40:27</t>
+          <t>09:30:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="F75" t="n">
         <v>8.74</v>
       </c>
       <c r="G75" t="n">
-        <v>66.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="H75" t="n">
-        <v>47</v>
+        <v>56.2</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.96</v>
+        <v>-30.5</v>
       </c>
       <c r="K75" t="n">
-        <v>-71.08</v>
+        <v>-25.91</v>
       </c>
       <c r="L75" t="n">
-        <v>72.08</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:42:48</t>
+          <t>09:32:06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="F76" t="n">
-        <v>7.61</v>
+        <v>7.91</v>
       </c>
       <c r="G76" t="n">
-        <v>68.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="H76" t="n">
-        <v>40.1</v>
+        <v>60.7</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>51.27</v>
+        <v>9.85</v>
       </c>
       <c r="K76" t="n">
-        <v>50.4</v>
+        <v>-56.34</v>
       </c>
       <c r="L76" t="n">
-        <v>71.89</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:48:04</t>
+          <t>09:36:09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.87</v>
+        <v>3.47</v>
       </c>
       <c r="F77" t="n">
-        <v>8.74</v>
+        <v>8.5</v>
       </c>
       <c r="G77" t="n">
-        <v>66.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>43.4</v>
+        <v>46</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>77.87</v>
+        <v>37.63</v>
       </c>
       <c r="K77" t="n">
-        <v>49.44</v>
+        <v>69.39</v>
       </c>
       <c r="L77" t="n">
-        <v>92.23999999999999</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:49:42</t>
+          <t>09:38:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,7 +3313,7 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="F78" t="n">
         <v>8.74</v>
@@ -3322,25 +3322,25 @@
         <v>80.59999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>38.9</v>
+        <v>56.5</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>75.62</v>
+        <v>-80.34</v>
       </c>
       <c r="K78" t="n">
-        <v>42.37</v>
+        <v>24.71</v>
       </c>
       <c r="L78" t="n">
-        <v>86.68000000000001</v>
+        <v>84.06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:51:16</t>
+          <t>09:40:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="F79" t="n">
-        <v>6.69</v>
+        <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>62.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-76.02</v>
+        <v>10.96</v>
       </c>
       <c r="K79" t="n">
-        <v>-37.43</v>
+        <v>-2.3</v>
       </c>
       <c r="L79" t="n">
-        <v>84.73999999999999</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:55:15</t>
+          <t>09:45:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="F80" t="n">
-        <v>6.24</v>
+        <v>8.33</v>
       </c>
       <c r="G80" t="n">
-        <v>64.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>101.77</v>
+        <v>-110.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-105.78</v>
+        <v>-49.11</v>
       </c>
       <c r="L80" t="n">
-        <v>146.78</v>
+        <v>120.89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:57:11</t>
+          <t>09:47:38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="F81" t="n">
-        <v>7.89</v>
+        <v>8.06</v>
       </c>
       <c r="G81" t="n">
-        <v>71.3</v>
+        <v>79.7</v>
       </c>
       <c r="H81" t="n">
-        <v>50.6</v>
+        <v>40.1</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>101.6</v>
+        <v>50.63</v>
       </c>
       <c r="K81" t="n">
-        <v>-50.43</v>
+        <v>-74.52</v>
       </c>
       <c r="L81" t="n">
-        <v>113.43</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:59:09</t>
+          <t>09:49:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="F82" t="n">
         <v>8.74</v>
       </c>
       <c r="G82" t="n">
-        <v>74</v>
+        <v>78.2</v>
       </c>
       <c r="H82" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>88.52</v>
+        <v>101.32</v>
       </c>
       <c r="K82" t="n">
-        <v>-99.16</v>
+        <v>76.69</v>
       </c>
       <c r="L82" t="n">
-        <v>132.93</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:04:09</t>
+          <t>09:56:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="F83" t="n">
-        <v>7.28</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>81.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>54.8</v>
+        <v>60.1</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>46.82</v>
+        <v>110.31</v>
       </c>
       <c r="K83" t="n">
-        <v>-192.73</v>
+        <v>-83.97</v>
       </c>
       <c r="L83" t="n">
-        <v>198.33</v>
+        <v>138.63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:05:37</t>
+          <t>09:57:28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="F84" t="n">
         <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>78.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>45.6</v>
+        <v>29</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.79</v>
+        <v>147</v>
       </c>
       <c r="K84" t="n">
-        <v>212.15</v>
+        <v>-22.54</v>
       </c>
       <c r="L84" t="n">
-        <v>212.53</v>
+        <v>148.72</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:07:20</t>
+          <t>09:59:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="F85" t="n">
-        <v>7.19</v>
+        <v>8.74</v>
       </c>
       <c r="G85" t="n">
-        <v>79.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>50.3</v>
+        <v>56</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-117.83</v>
+        <v>195.49</v>
       </c>
       <c r="K85" t="n">
-        <v>152.37</v>
+        <v>35.36</v>
       </c>
       <c r="L85" t="n">
-        <v>192.62</v>
+        <v>198.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:12:03</t>
+          <t>10:03:02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="F86" t="n">
-        <v>8.74</v>
+        <v>7.83</v>
       </c>
       <c r="G86" t="n">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="H86" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-198.08</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>195.46</v>
+        <v>126.19</v>
       </c>
       <c r="L86" t="n">
-        <v>278.28</v>
+        <v>126.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:13:54</t>
+          <t>10:05:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3697,28 +3697,28 @@
         <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>70.7</v>
+        <v>69.2</v>
       </c>
       <c r="H87" t="n">
-        <v>49.8</v>
+        <v>35.3</v>
       </c>
       <c r="I87" t="n">
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-44.99</v>
+        <v>206.99</v>
       </c>
       <c r="K87" t="n">
-        <v>296.06</v>
+        <v>63.61</v>
       </c>
       <c r="L87" t="n">
-        <v>299.46</v>
+        <v>216.55</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:16:19</t>
+          <t>10:06:13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="F88" t="n">
-        <v>8.5</v>
+        <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>76.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>41.5</v>
+        <v>55.1</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-51.23</v>
+        <v>-58.76</v>
       </c>
       <c r="K88" t="n">
-        <v>213.79</v>
+        <v>-195.68</v>
       </c>
       <c r="L88" t="n">
-        <v>219.84</v>
+        <v>204.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="F14" t="n">
-        <v>5.92</v>
+        <v>8.74</v>
       </c>
       <c r="G14" t="n">
-        <v>58.6</v>
+        <v>81.8</v>
       </c>
       <c r="H14" t="n">
-        <v>48.3</v>
+        <v>34.2</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>26.74</v>
+        <v>-19.54</v>
       </c>
       <c r="K14" t="n">
-        <v>21.39</v>
+        <v>26.94</v>
       </c>
       <c r="L14" t="n">
-        <v>34.25</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:34:22</t>
+          <t>06:35:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="F15" t="n">
-        <v>6.63</v>
+        <v>4.97</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>73.2</v>
       </c>
       <c r="H15" t="n">
-        <v>64.59999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>21.31</v>
+        <v>17.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-27.05</v>
+        <v>54.86</v>
       </c>
       <c r="L15" t="n">
-        <v>34.44</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:36:48</t>
+          <t>06:36:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="F16" t="n">
-        <v>5.22</v>
+        <v>8.74</v>
       </c>
       <c r="G16" t="n">
-        <v>52.1</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>42.1</v>
+        <v>59.3</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.34</v>
+        <v>-33.41</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.46</v>
+        <v>-0.47</v>
       </c>
       <c r="L16" t="n">
-        <v>25.54</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:41:06</t>
+          <t>06:41:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.14</v>
+        <v>2.29</v>
       </c>
       <c r="F17" t="n">
-        <v>8.74</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>63.4</v>
+        <v>82.8</v>
       </c>
       <c r="H17" t="n">
-        <v>58.7</v>
+        <v>35.6</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.02</v>
+        <v>-10.91</v>
       </c>
       <c r="K17" t="n">
-        <v>-81.92</v>
+        <v>-50.87</v>
       </c>
       <c r="L17" t="n">
-        <v>81.92</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:42:45</t>
+          <t>06:43:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="F18" t="n">
-        <v>5.43</v>
+        <v>6.8</v>
       </c>
       <c r="G18" t="n">
-        <v>78.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>36.8</v>
+        <v>35.5</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>49.36</v>
+        <v>-1.98</v>
       </c>
       <c r="K18" t="n">
-        <v>12.39</v>
+        <v>-39.83</v>
       </c>
       <c r="L18" t="n">
-        <v>50.89</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:44:49</t>
+          <t>06:44:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="F19" t="n">
-        <v>7.62</v>
+        <v>4.37</v>
       </c>
       <c r="G19" t="n">
-        <v>69.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>9.619999999999999</v>
+        <v>-21.92</v>
       </c>
       <c r="K19" t="n">
-        <v>59.28</v>
+        <v>35.27</v>
       </c>
       <c r="L19" t="n">
-        <v>60.06</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:48:37</t>
+          <t>06:47:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="F20" t="n">
-        <v>2.53</v>
+        <v>7.05</v>
       </c>
       <c r="G20" t="n">
-        <v>76.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="H20" t="n">
-        <v>39.1</v>
+        <v>57.4</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>-60.38</v>
+        <v>43.32</v>
       </c>
       <c r="K20" t="n">
-        <v>-76.39</v>
+        <v>-24.35</v>
       </c>
       <c r="L20" t="n">
-        <v>97.37</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:49:26</t>
+          <t>06:50:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="F21" t="n">
-        <v>7.67</v>
+        <v>5.75</v>
       </c>
       <c r="G21" t="n">
-        <v>74.7</v>
+        <v>66.3</v>
       </c>
       <c r="H21" t="n">
-        <v>8.5</v>
+        <v>53.3</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>38.9</v>
+        <v>64.89</v>
       </c>
       <c r="K21" t="n">
-        <v>91.98999999999999</v>
+        <v>-38.87</v>
       </c>
       <c r="L21" t="n">
-        <v>99.88</v>
+        <v>75.65000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:50:53</t>
+          <t>06:51:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.48</v>
+        <v>2.22</v>
       </c>
       <c r="F22" t="n">
-        <v>8.74</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>96.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>29.4</v>
+        <v>37.3</v>
       </c>
       <c r="I22" t="n">
         <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>-129.18</v>
+        <v>-75.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-12.45</v>
+        <v>-4.7</v>
       </c>
       <c r="L22" t="n">
-        <v>129.78</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:54:36</t>
+          <t>06:54:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="F23" t="n">
-        <v>7.83</v>
+        <v>5.63</v>
       </c>
       <c r="G23" t="n">
-        <v>68.5</v>
+        <v>73.5</v>
       </c>
       <c r="H23" t="n">
-        <v>59.5</v>
+        <v>57.5</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>178.93</v>
+        <v>47.94</v>
       </c>
       <c r="K23" t="n">
-        <v>24.54</v>
+        <v>106.8</v>
       </c>
       <c r="L23" t="n">
-        <v>180.6</v>
+        <v>117.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:57:03</t>
+          <t>06:56:29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="F24" t="n">
-        <v>5.8</v>
+        <v>7.01</v>
       </c>
       <c r="G24" t="n">
-        <v>81.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>40.5</v>
+        <v>30.9</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-127.23</v>
+        <v>29.72</v>
       </c>
       <c r="K24" t="n">
-        <v>77.09999999999999</v>
+        <v>-120.37</v>
       </c>
       <c r="L24" t="n">
-        <v>148.77</v>
+        <v>123.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:59:17</t>
+          <t>06:57:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.78</v>
+        <v>1.93</v>
       </c>
       <c r="F25" t="n">
-        <v>8.74</v>
+        <v>6.9</v>
       </c>
       <c r="G25" t="n">
-        <v>66.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>53.7</v>
+        <v>41.6</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>91.5</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>116.87</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>148.43</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:03:26</t>
+          <t>07:01:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="F26" t="n">
-        <v>8.74</v>
+        <v>4.78</v>
       </c>
       <c r="G26" t="n">
-        <v>85.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>11.1</v>
+        <v>50.3</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>123.69</v>
+        <v>189.41</v>
       </c>
       <c r="K26" t="n">
-        <v>117.17</v>
+        <v>51.82</v>
       </c>
       <c r="L26" t="n">
-        <v>170.37</v>
+        <v>196.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:05:52</t>
+          <t>07:03:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="F27" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="G27" t="n">
-        <v>69.7</v>
+        <v>88.7</v>
       </c>
       <c r="H27" t="n">
-        <v>49.3</v>
+        <v>59.5</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J27" t="n">
-        <v>-122.05</v>
+        <v>-180.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-176.51</v>
+        <v>-58.23</v>
       </c>
       <c r="L27" t="n">
-        <v>214.6</v>
+        <v>190.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:07:32</t>
+          <t>07:05:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="F28" t="n">
-        <v>6.55</v>
+        <v>7.33</v>
       </c>
       <c r="G28" t="n">
-        <v>66.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>24.7</v>
+        <v>43.3</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>115.2</v>
+        <v>56.96</v>
       </c>
       <c r="K28" t="n">
-        <v>181.9</v>
+        <v>161.33</v>
       </c>
       <c r="L28" t="n">
-        <v>215.31</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:16:59</t>
+          <t>07:13:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="F29" t="n">
-        <v>6.32</v>
+        <v>5.62</v>
       </c>
       <c r="G29" t="n">
-        <v>64.2</v>
+        <v>79.3</v>
       </c>
       <c r="H29" t="n">
-        <v>61.7</v>
+        <v>17.3</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>15.69</v>
+        <v>-11.94</v>
       </c>
       <c r="K29" t="n">
-        <v>33.65</v>
+        <v>33.41</v>
       </c>
       <c r="L29" t="n">
-        <v>37.13</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:19:11</t>
+          <t>07:15:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="F30" t="n">
-        <v>6.19</v>
+        <v>6.94</v>
       </c>
       <c r="G30" t="n">
-        <v>76.59999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="H30" t="n">
-        <v>70.5</v>
+        <v>20.7</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>21.6</v>
+        <v>38.39</v>
       </c>
       <c r="K30" t="n">
-        <v>-33.24</v>
+        <v>5.97</v>
       </c>
       <c r="L30" t="n">
-        <v>39.64</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:20:46</t>
+          <t>07:16:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="F31" t="n">
-        <v>4.12</v>
+        <v>7.04</v>
       </c>
       <c r="G31" t="n">
-        <v>76.8</v>
+        <v>63.2</v>
       </c>
       <c r="H31" t="n">
-        <v>80.3</v>
+        <v>60</v>
       </c>
       <c r="I31" t="n">
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.31</v>
+        <v>-2.06</v>
       </c>
       <c r="K31" t="n">
-        <v>37.37</v>
+        <v>-30.91</v>
       </c>
       <c r="L31" t="n">
-        <v>38.28</v>
+        <v>30.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:23:54</t>
+          <t>07:21:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="F32" t="n">
-        <v>4.83</v>
+        <v>8.74</v>
       </c>
       <c r="G32" t="n">
-        <v>71</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>67.7</v>
+        <v>66.5</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>30.94</v>
+        <v>45.93</v>
       </c>
       <c r="K32" t="n">
-        <v>-58.2</v>
+        <v>25.78</v>
       </c>
       <c r="L32" t="n">
-        <v>65.91</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:24:45</t>
+          <t>07:23:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1429,28 +1429,28 @@
         <v>8.74</v>
       </c>
       <c r="G33" t="n">
-        <v>78.2</v>
+        <v>82.3</v>
       </c>
       <c r="H33" t="n">
-        <v>33.8</v>
+        <v>69</v>
       </c>
       <c r="I33" t="n">
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>67.58</v>
+        <v>-20.09</v>
       </c>
       <c r="K33" t="n">
-        <v>-79.8</v>
+        <v>-41.34</v>
       </c>
       <c r="L33" t="n">
-        <v>104.57</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:26:01</t>
+          <t>07:24:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="F34" t="n">
-        <v>7.35</v>
+        <v>6.83</v>
       </c>
       <c r="G34" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>57.2</v>
+        <v>57.9</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>27.18</v>
+        <v>-30.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-63.02</v>
+        <v>-24.52</v>
       </c>
       <c r="L34" t="n">
-        <v>68.63</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:31:03</t>
+          <t>07:29:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="F35" t="n">
-        <v>8.74</v>
+        <v>6.75</v>
       </c>
       <c r="G35" t="n">
-        <v>77.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>25.2</v>
+        <v>62.1</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>101.28</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-14.6</v>
+        <v>-12.18</v>
       </c>
       <c r="L35" t="n">
-        <v>102.32</v>
+        <v>75.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:32:07</t>
+          <t>07:31:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="F36" t="n">
-        <v>7.32</v>
+        <v>5.95</v>
       </c>
       <c r="G36" t="n">
-        <v>78.2</v>
+        <v>72.2</v>
       </c>
       <c r="H36" t="n">
-        <v>52.7</v>
+        <v>80.2</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>116.14</v>
+        <v>-69.58</v>
       </c>
       <c r="K36" t="n">
-        <v>-10.29</v>
+        <v>-12.91</v>
       </c>
       <c r="L36" t="n">
-        <v>116.6</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:33:47</t>
+          <t>07:32:10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="F37" t="n">
-        <v>8.74</v>
+        <v>8.09</v>
       </c>
       <c r="G37" t="n">
-        <v>73.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>38</v>
+        <v>45.9</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>102.05</v>
+        <v>-93.53</v>
       </c>
       <c r="K37" t="n">
-        <v>43.6</v>
+        <v>-9.43</v>
       </c>
       <c r="L37" t="n">
-        <v>110.97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:39:18</t>
+          <t>07:36:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="F38" t="n">
-        <v>8.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>93</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>68.3</v>
+        <v>14.9</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>131.72</v>
+        <v>-97.91</v>
       </c>
       <c r="K38" t="n">
-        <v>4.72</v>
+        <v>53.7</v>
       </c>
       <c r="L38" t="n">
-        <v>131.81</v>
+        <v>111.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:40:48</t>
+          <t>07:37:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="F39" t="n">
-        <v>8.74</v>
+        <v>6.98</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>37.4</v>
+        <v>82.5</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-21.67</v>
+        <v>61.22</v>
       </c>
       <c r="K39" t="n">
-        <v>98.42</v>
+        <v>110.21</v>
       </c>
       <c r="L39" t="n">
-        <v>100.78</v>
+        <v>126.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:41:57</t>
+          <t>07:39:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="F40" t="n">
-        <v>8.130000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="G40" t="n">
-        <v>66.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="H40" t="n">
-        <v>36.4</v>
+        <v>55.8</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-19.78</v>
+        <v>81</v>
       </c>
       <c r="K40" t="n">
-        <v>-176.13</v>
+        <v>89.87</v>
       </c>
       <c r="L40" t="n">
-        <v>177.24</v>
+        <v>120.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:46:03</t>
+          <t>07:42:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="F41" t="n">
-        <v>8.74</v>
+        <v>5.62</v>
       </c>
       <c r="G41" t="n">
-        <v>72.3</v>
+        <v>69.3</v>
       </c>
       <c r="H41" t="n">
-        <v>46.4</v>
+        <v>33</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>214.5</v>
+        <v>172.65</v>
       </c>
       <c r="K41" t="n">
-        <v>-54.42</v>
+        <v>-73.42</v>
       </c>
       <c r="L41" t="n">
-        <v>221.3</v>
+        <v>187.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:47:00</t>
+          <t>07:44:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="F42" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="G42" t="n">
-        <v>70.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>77.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-183.68</v>
+        <v>105.99</v>
       </c>
       <c r="K42" t="n">
-        <v>106.37</v>
+        <v>-139.2</v>
       </c>
       <c r="L42" t="n">
-        <v>212.26</v>
+        <v>174.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:49:07</t>
+          <t>07:46:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="F43" t="n">
-        <v>7.38</v>
+        <v>8.32</v>
       </c>
       <c r="G43" t="n">
-        <v>73.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>30.8</v>
+        <v>33.7</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>153.76</v>
+        <v>153.64</v>
       </c>
       <c r="K43" t="n">
-        <v>78.12</v>
+        <v>-46.2</v>
       </c>
       <c r="L43" t="n">
-        <v>172.47</v>
+        <v>160.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:58:03</t>
+          <t>07:59:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="F44" t="n">
-        <v>4.31</v>
+        <v>6.49</v>
       </c>
       <c r="G44" t="n">
-        <v>77.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H44" t="n">
-        <v>51.7</v>
+        <v>55.5</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>15.52</v>
+        <v>-28.9</v>
       </c>
       <c r="K44" t="n">
-        <v>22.78</v>
+        <v>-12.21</v>
       </c>
       <c r="L44" t="n">
-        <v>27.57</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:00:12</t>
+          <t>08:00:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="F45" t="n">
-        <v>8.1</v>
+        <v>8.74</v>
       </c>
       <c r="G45" t="n">
-        <v>74.8</v>
+        <v>72.7</v>
       </c>
       <c r="H45" t="n">
-        <v>60.2</v>
+        <v>35.9</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.65</v>
+        <v>-20.55</v>
       </c>
       <c r="K45" t="n">
-        <v>21.93</v>
+        <v>-29.63</v>
       </c>
       <c r="L45" t="n">
-        <v>42.71</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:01:48</t>
+          <t>08:01:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="F46" t="n">
-        <v>8.359999999999999</v>
+        <v>6.22</v>
       </c>
       <c r="G46" t="n">
-        <v>63.1</v>
+        <v>71.5</v>
       </c>
       <c r="H46" t="n">
-        <v>10.2</v>
+        <v>36</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>28.15</v>
+        <v>-25.86</v>
       </c>
       <c r="K46" t="n">
-        <v>-28.66</v>
+        <v>-11.31</v>
       </c>
       <c r="L46" t="n">
-        <v>40.17</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:07:46</t>
+          <t>08:07:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="F47" t="n">
-        <v>6.21</v>
+        <v>8.74</v>
       </c>
       <c r="G47" t="n">
         <v>71.8</v>
       </c>
       <c r="H47" t="n">
-        <v>59.4</v>
+        <v>55.9</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-26.89</v>
+        <v>-54.29</v>
       </c>
       <c r="K47" t="n">
-        <v>55.48</v>
+        <v>7.29</v>
       </c>
       <c r="L47" t="n">
-        <v>61.65</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:09:10</t>
+          <t>08:08:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="F48" t="n">
-        <v>7.44</v>
+        <v>4.95</v>
       </c>
       <c r="G48" t="n">
-        <v>77.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>64.40000000000001</v>
+        <v>49.2</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-63.46</v>
+        <v>-45.09</v>
       </c>
       <c r="K48" t="n">
-        <v>-36.68</v>
+        <v>-38.17</v>
       </c>
       <c r="L48" t="n">
-        <v>73.3</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:11:43</t>
+          <t>08:10:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="F49" t="n">
-        <v>8.01</v>
+        <v>4.72</v>
       </c>
       <c r="G49" t="n">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="H49" t="n">
-        <v>54.6</v>
+        <v>35.2</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.08</v>
+        <v>-43.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-85.05</v>
+        <v>-23.26</v>
       </c>
       <c r="L49" t="n">
-        <v>89.88</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:17:10</t>
+          <t>08:14:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="F50" t="n">
-        <v>6.11</v>
+        <v>8.74</v>
       </c>
       <c r="G50" t="n">
-        <v>61</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>39.5</v>
+        <v>76</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-52.03</v>
+        <v>-54.53</v>
       </c>
       <c r="K50" t="n">
-        <v>83.95999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="L50" t="n">
-        <v>98.78</v>
+        <v>59.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:17:45</t>
+          <t>08:16:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="F51" t="n">
-        <v>8.74</v>
+        <v>5.34</v>
       </c>
       <c r="G51" t="n">
-        <v>72.3</v>
+        <v>67.8</v>
       </c>
       <c r="H51" t="n">
-        <v>36.3</v>
+        <v>31.1</v>
       </c>
       <c r="I51" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>30.55</v>
+        <v>75.36</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.20999999999999</v>
+        <v>-2.25</v>
       </c>
       <c r="L51" t="n">
-        <v>90.52</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:18:54</t>
+          <t>08:17:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="F52" t="n">
-        <v>3.52</v>
+        <v>8.74</v>
       </c>
       <c r="G52" t="n">
-        <v>79.8</v>
+        <v>74.3</v>
       </c>
       <c r="H52" t="n">
-        <v>40.1</v>
+        <v>46</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>13.89</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-84.01000000000001</v>
+        <v>18.97</v>
       </c>
       <c r="L52" t="n">
-        <v>85.15000000000001</v>
+        <v>87.13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:23:53</t>
+          <t>08:21:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="F53" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
       <c r="G53" t="n">
-        <v>78.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H53" t="n">
-        <v>57.4</v>
+        <v>47</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>46.83</v>
+        <v>56.8</v>
       </c>
       <c r="K53" t="n">
-        <v>-113.85</v>
+        <v>-113.39</v>
       </c>
       <c r="L53" t="n">
-        <v>123.11</v>
+        <v>126.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:25:28</t>
+          <t>08:22:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.63</v>
+        <v>3.22</v>
       </c>
       <c r="F54" t="n">
-        <v>6.39</v>
+        <v>8.74</v>
       </c>
       <c r="G54" t="n">
-        <v>88.3</v>
+        <v>69.8</v>
       </c>
       <c r="H54" t="n">
-        <v>76</v>
+        <v>40.1</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-135.52</v>
+        <v>120.87</v>
       </c>
       <c r="K54" t="n">
-        <v>25.22</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>137.84</v>
+        <v>139.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:26:31</t>
+          <t>08:24:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="F55" t="n">
-        <v>8.74</v>
+        <v>7.63</v>
       </c>
       <c r="G55" t="n">
-        <v>60.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>45.6</v>
+        <v>67</v>
       </c>
       <c r="I55" t="n">
         <v>29</v>
       </c>
       <c r="J55" t="n">
-        <v>144.33</v>
+        <v>-49.85</v>
       </c>
       <c r="K55" t="n">
-        <v>31.47</v>
+        <v>-12.05</v>
       </c>
       <c r="L55" t="n">
-        <v>147.73</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:30:47</t>
+          <t>08:29:44</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="F56" t="n">
-        <v>3.31</v>
+        <v>7.54</v>
       </c>
       <c r="G56" t="n">
-        <v>75</v>
+        <v>63.5</v>
       </c>
       <c r="H56" t="n">
-        <v>32.3</v>
+        <v>45</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-85.81999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="K56" t="n">
-        <v>-167.64</v>
+        <v>154.81</v>
       </c>
       <c r="L56" t="n">
-        <v>188.33</v>
+        <v>155.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:32:06</t>
+          <t>08:31:42</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="F57" t="n">
-        <v>8.66</v>
+        <v>8.74</v>
       </c>
       <c r="G57" t="n">
-        <v>71.3</v>
+        <v>79.7</v>
       </c>
       <c r="H57" t="n">
-        <v>80.2</v>
+        <v>67.5</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>157.95</v>
+        <v>-39.92</v>
       </c>
       <c r="K57" t="n">
-        <v>-102.25</v>
+        <v>-164.95</v>
       </c>
       <c r="L57" t="n">
-        <v>188.15</v>
+        <v>169.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:34:01</t>
+          <t>08:33:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.76</v>
+        <v>2.33</v>
       </c>
       <c r="F58" t="n">
-        <v>8.74</v>
+        <v>7.1</v>
       </c>
       <c r="G58" t="n">
-        <v>66</v>
+        <v>76.7</v>
       </c>
       <c r="H58" t="n">
-        <v>26.5</v>
+        <v>11.3</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>95.11</v>
+        <v>109.25</v>
       </c>
       <c r="K58" t="n">
-        <v>-135.16</v>
+        <v>-146.49</v>
       </c>
       <c r="L58" t="n">
-        <v>165.27</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:46:31</t>
+          <t>08:42:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="F59" t="n">
-        <v>7.67</v>
+        <v>8.74</v>
       </c>
       <c r="G59" t="n">
-        <v>76.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="H59" t="n">
-        <v>47.2</v>
+        <v>63.4</v>
       </c>
       <c r="I59" t="n">
         <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.380000000000001</v>
+        <v>-40.89</v>
       </c>
       <c r="K59" t="n">
-        <v>24.29</v>
+        <v>-26.37</v>
       </c>
       <c r="L59" t="n">
-        <v>26.03</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:48:49</t>
+          <t>08:44:51</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.39</v>
+        <v>2.78</v>
       </c>
       <c r="F60" t="n">
-        <v>6.13</v>
+        <v>8.1</v>
       </c>
       <c r="G60" t="n">
-        <v>70.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>21.9</v>
+        <v>34</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-31.2</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>6.61</v>
+        <v>21.34</v>
       </c>
       <c r="L60" t="n">
-        <v>31.89</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:50:15</t>
+          <t>08:46:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="F61" t="n">
-        <v>5.04</v>
+        <v>7.82</v>
       </c>
       <c r="G61" t="n">
-        <v>65</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>14.7</v>
+        <v>44.1</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J61" t="n">
-        <v>37.63</v>
+        <v>-32.35</v>
       </c>
       <c r="K61" t="n">
-        <v>-11.87</v>
+        <v>19.17</v>
       </c>
       <c r="L61" t="n">
-        <v>39.46</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:53:14</t>
+          <t>08:50:52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="F62" t="n">
-        <v>5.45</v>
+        <v>8.68</v>
       </c>
       <c r="G62" t="n">
-        <v>64.7</v>
+        <v>71.7</v>
       </c>
       <c r="H62" t="n">
-        <v>57</v>
+        <v>42.4</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-10.76</v>
+        <v>39.74</v>
       </c>
       <c r="K62" t="n">
-        <v>65.72</v>
+        <v>50.17</v>
       </c>
       <c r="L62" t="n">
-        <v>66.59999999999999</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:54:44</t>
+          <t>08:52:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="F63" t="n">
         <v>8.74</v>
       </c>
       <c r="G63" t="n">
-        <v>71.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>40.7</v>
+        <v>60.5</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>23.12</v>
+        <v>-7.97</v>
       </c>
       <c r="K63" t="n">
-        <v>52.33</v>
+        <v>43.45</v>
       </c>
       <c r="L63" t="n">
-        <v>57.21</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:56:43</t>
+          <t>08:53:50</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="F64" t="n">
-        <v>8.74</v>
+        <v>8.06</v>
       </c>
       <c r="G64" t="n">
-        <v>76.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>36.2</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>43.71</v>
+        <v>-1.19</v>
       </c>
       <c r="K64" t="n">
-        <v>12.16</v>
+        <v>-50.96</v>
       </c>
       <c r="L64" t="n">
-        <v>45.37</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:00:48</t>
+          <t>08:59:05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="F65" t="n">
-        <v>5.13</v>
+        <v>6.83</v>
       </c>
       <c r="G65" t="n">
-        <v>93.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="H65" t="n">
-        <v>76</v>
+        <v>56.9</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>53.45</v>
+        <v>26.04</v>
       </c>
       <c r="K65" t="n">
-        <v>-22.9</v>
+        <v>-87.78</v>
       </c>
       <c r="L65" t="n">
-        <v>58.15</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:02:55</t>
+          <t>09:00:58</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.67</v>
+        <v>3.02</v>
       </c>
       <c r="F66" t="n">
         <v>8.74</v>
       </c>
       <c r="G66" t="n">
-        <v>64.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="H66" t="n">
-        <v>42.7</v>
+        <v>49.3</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>89.59999999999999</v>
+        <v>-17.32</v>
       </c>
       <c r="K66" t="n">
-        <v>65.08</v>
+        <v>70.61</v>
       </c>
       <c r="L66" t="n">
-        <v>110.74</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:04:05</t>
+          <t>09:02:50</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="F67" t="n">
         <v>8.74</v>
       </c>
       <c r="G67" t="n">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H67" t="n">
-        <v>71</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>50.61</v>
+        <v>14.66</v>
       </c>
       <c r="K67" t="n">
-        <v>-85.13</v>
+        <v>-63.44</v>
       </c>
       <c r="L67" t="n">
-        <v>99.04000000000001</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:09:41</t>
+          <t>09:06:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="F68" t="n">
-        <v>8.48</v>
+        <v>6.68</v>
       </c>
       <c r="G68" t="n">
-        <v>83.59999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="H68" t="n">
-        <v>63</v>
+        <v>24.7</v>
       </c>
       <c r="I68" t="n">
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-37.2</v>
+        <v>75.19</v>
       </c>
       <c r="K68" t="n">
-        <v>-88.01000000000001</v>
+        <v>-149.94</v>
       </c>
       <c r="L68" t="n">
-        <v>95.55</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:11:42</t>
+          <t>09:07:46</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="F69" t="n">
-        <v>8.74</v>
+        <v>6.12</v>
       </c>
       <c r="G69" t="n">
-        <v>57.7</v>
+        <v>79</v>
       </c>
       <c r="H69" t="n">
-        <v>68.7</v>
+        <v>61.8</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J69" t="n">
-        <v>134.32</v>
+        <v>-138.36</v>
       </c>
       <c r="K69" t="n">
-        <v>-63.31</v>
+        <v>231.33</v>
       </c>
       <c r="L69" t="n">
-        <v>148.49</v>
+        <v>269.54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:12:27</t>
+          <t>09:10:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="F70" t="n">
-        <v>8.35</v>
+        <v>5.23</v>
       </c>
       <c r="G70" t="n">
-        <v>65.7</v>
+        <v>84.5</v>
       </c>
       <c r="H70" t="n">
-        <v>32.9</v>
+        <v>19</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>95.06999999999999</v>
+        <v>5.07</v>
       </c>
       <c r="K70" t="n">
-        <v>76.76000000000001</v>
+        <v>92.13</v>
       </c>
       <c r="L70" t="n">
-        <v>122.19</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:16:12</t>
+          <t>09:13:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.06</v>
+        <v>2.48</v>
       </c>
       <c r="F71" t="n">
-        <v>8.74</v>
+        <v>8.6</v>
       </c>
       <c r="G71" t="n">
-        <v>79.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>43.9</v>
+        <v>42.7</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>33.48</v>
+        <v>141.68</v>
       </c>
       <c r="K71" t="n">
-        <v>-44.09</v>
+        <v>113.55</v>
       </c>
       <c r="L71" t="n">
-        <v>55.36</v>
+        <v>181.57</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:17:40</t>
+          <t>09:15:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="F72" t="n">
-        <v>6.25</v>
+        <v>8.74</v>
       </c>
       <c r="G72" t="n">
-        <v>77.2</v>
+        <v>82.5</v>
       </c>
       <c r="H72" t="n">
-        <v>26.5</v>
+        <v>56</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-153.6</v>
+        <v>-184.36</v>
       </c>
       <c r="K72" t="n">
-        <v>-95.88</v>
+        <v>40.07</v>
       </c>
       <c r="L72" t="n">
-        <v>181.07</v>
+        <v>188.66</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:19:21</t>
+          <t>09:17:51</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="F73" t="n">
-        <v>8.74</v>
+        <v>7</v>
       </c>
       <c r="G73" t="n">
-        <v>63.7</v>
+        <v>73.3</v>
       </c>
       <c r="H73" t="n">
-        <v>36</v>
+        <v>73.7</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>87.68000000000001</v>
+        <v>132.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-178.45</v>
+        <v>101.43</v>
       </c>
       <c r="L73" t="n">
-        <v>198.83</v>
+        <v>166.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:28:50</t>
+          <t>09:27:06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="F74" t="n">
-        <v>6.79</v>
+        <v>8.52</v>
       </c>
       <c r="G74" t="n">
-        <v>76.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>72.3</v>
+        <v>8.9</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-50.14</v>
+        <v>-33.61</v>
       </c>
       <c r="K74" t="n">
-        <v>7.44</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>50.68</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:30:32</t>
+          <t>09:29:10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="F75" t="n">
-        <v>8.74</v>
+        <v>6.72</v>
       </c>
       <c r="G75" t="n">
-        <v>62.8</v>
+        <v>68.8</v>
       </c>
       <c r="H75" t="n">
-        <v>56.2</v>
+        <v>28.1</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.5</v>
+        <v>35.95</v>
       </c>
       <c r="K75" t="n">
-        <v>-25.91</v>
+        <v>-15.19</v>
       </c>
       <c r="L75" t="n">
-        <v>40.02</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:32:06</t>
+          <t>09:30:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="F76" t="n">
-        <v>7.91</v>
+        <v>8.34</v>
       </c>
       <c r="G76" t="n">
-        <v>78.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>60.7</v>
+        <v>63.9</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>9.85</v>
+        <v>-9.59</v>
       </c>
       <c r="K76" t="n">
-        <v>-56.34</v>
+        <v>38.41</v>
       </c>
       <c r="L76" t="n">
-        <v>57.19</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:36:09</t>
+          <t>09:34:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.47</v>
+        <v>2.41</v>
       </c>
       <c r="F77" t="n">
-        <v>8.5</v>
+        <v>8.74</v>
       </c>
       <c r="G77" t="n">
-        <v>72.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>46</v>
+        <v>54.6</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>37.63</v>
+        <v>64.19</v>
       </c>
       <c r="K77" t="n">
-        <v>69.39</v>
+        <v>-3.68</v>
       </c>
       <c r="L77" t="n">
-        <v>78.94</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:38:17</t>
+          <t>09:36:18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="F78" t="n">
-        <v>8.74</v>
+        <v>8.59</v>
       </c>
       <c r="G78" t="n">
-        <v>80.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>56.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-80.34</v>
+        <v>49.23</v>
       </c>
       <c r="K78" t="n">
-        <v>24.71</v>
+        <v>-31.13</v>
       </c>
       <c r="L78" t="n">
-        <v>84.06</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:40:36</t>
+          <t>09:38:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.54</v>
+        <v>2.97</v>
       </c>
       <c r="F79" t="n">
         <v>8.74</v>
       </c>
       <c r="G79" t="n">
-        <v>72.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>47.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>10.96</v>
+        <v>-35.98</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.3</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>11.2</v>
+        <v>80.27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:45:03</t>
+          <t>09:43:36</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="F80" t="n">
-        <v>8.33</v>
+        <v>6.17</v>
       </c>
       <c r="G80" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>-110.47</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-49.11</v>
+        <v>91.34</v>
       </c>
       <c r="L80" t="n">
-        <v>120.89</v>
+        <v>91.73999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:47:38</t>
+          <t>09:46:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="F81" t="n">
-        <v>8.06</v>
+        <v>7.87</v>
       </c>
       <c r="G81" t="n">
-        <v>79.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>40.1</v>
+        <v>93</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>50.63</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-74.52</v>
+        <v>22.46</v>
       </c>
       <c r="L81" t="n">
-        <v>90.09</v>
+        <v>97.55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:49:58</t>
+          <t>09:46:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="F82" t="n">
-        <v>8.74</v>
+        <v>7.67</v>
       </c>
       <c r="G82" t="n">
-        <v>78.2</v>
+        <v>72.3</v>
       </c>
       <c r="H82" t="n">
-        <v>44.6</v>
+        <v>37.7</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>101.32</v>
+        <v>79.69</v>
       </c>
       <c r="K82" t="n">
-        <v>76.69</v>
+        <v>33.08</v>
       </c>
       <c r="L82" t="n">
-        <v>127.07</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:56:14</t>
+          <t>09:51:11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="F83" t="n">
-        <v>8.74</v>
+        <v>8.35</v>
       </c>
       <c r="G83" t="n">
-        <v>68.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>60.1</v>
+        <v>63.2</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>110.31</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-83.97</v>
+        <v>-149.61</v>
       </c>
       <c r="L83" t="n">
-        <v>138.63</v>
+        <v>172.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:57:28</t>
+          <t>09:53:23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="F84" t="n">
         <v>8.74</v>
       </c>
       <c r="G84" t="n">
-        <v>76.59999999999999</v>
+        <v>56</v>
       </c>
       <c r="H84" t="n">
-        <v>29</v>
+        <v>47.1</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>147</v>
+        <v>112.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-22.54</v>
+        <v>-92.09999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>148.72</v>
+        <v>145.74</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:59:20</t>
+          <t>09:55:06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.68</v>
+        <v>2.09</v>
       </c>
       <c r="F85" t="n">
-        <v>8.74</v>
+        <v>6.05</v>
       </c>
       <c r="G85" t="n">
-        <v>73.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>56</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>195.49</v>
+        <v>123.32</v>
       </c>
       <c r="K85" t="n">
-        <v>35.36</v>
+        <v>70.2</v>
       </c>
       <c r="L85" t="n">
-        <v>198.66</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:03:02</t>
+          <t>09:59:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="F86" t="n">
-        <v>7.83</v>
+        <v>8.74</v>
       </c>
       <c r="G86" t="n">
-        <v>76</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>50.2</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>9.539999999999999</v>
+        <v>-51.8</v>
       </c>
       <c r="K86" t="n">
-        <v>126.19</v>
+        <v>123.33</v>
       </c>
       <c r="L86" t="n">
-        <v>126.55</v>
+        <v>133.77</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:05:27</t>
+          <t>10:01:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="F87" t="n">
         <v>8.74</v>
       </c>
       <c r="G87" t="n">
-        <v>69.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>35.3</v>
+        <v>86</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J87" t="n">
-        <v>206.99</v>
+        <v>-183.91</v>
       </c>
       <c r="K87" t="n">
-        <v>63.61</v>
+        <v>122.22</v>
       </c>
       <c r="L87" t="n">
-        <v>216.55</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:06:13</t>
+          <t>10:03:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3739,22 +3739,22 @@
         <v>8.74</v>
       </c>
       <c r="G88" t="n">
-        <v>64.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="H88" t="n">
-        <v>55.1</v>
+        <v>32.8</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-58.76</v>
+        <v>111.17</v>
       </c>
       <c r="K88" t="n">
-        <v>-195.68</v>
+        <v>130.24</v>
       </c>
       <c r="L88" t="n">
-        <v>204.32</v>
+        <v>171.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-05.xlsx
+++ b/output/2024-04-05.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.26</v>
+        <v>-12.04</v>
       </c>
       <c r="K14" t="n">
-        <v>37.62</v>
+        <v>40.23</v>
       </c>
       <c r="L14" t="n">
-        <v>39.27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>55.98</v>
+        <v>54.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.17</v>
+        <v>-16.7</v>
       </c>
       <c r="L15" t="n">
-        <v>58.56</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.43</v>
+        <v>-0.46</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.04</v>
+        <v>-43.51</v>
       </c>
       <c r="L16" t="n">
-        <v>40.04</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>-68.81</v>
+        <v>-71.67</v>
       </c>
       <c r="K17" t="n">
-        <v>-20.15</v>
+        <v>-20.99</v>
       </c>
       <c r="L17" t="n">
-        <v>71.7</v>
+        <v>74.68000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>69.40000000000001</v>
+        <v>71.63</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.65</v>
+        <v>-22.34</v>
       </c>
       <c r="L18" t="n">
-        <v>72.7</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>71.66</v>
+        <v>76.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.24</v>
+        <v>-13.08</v>
       </c>
       <c r="L19" t="n">
-        <v>72.7</v>
+        <v>77.73</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>75.64</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-106.35</v>
+        <v>-109.61</v>
       </c>
       <c r="L20" t="n">
-        <v>130.51</v>
+        <v>134.51</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>29.08</v>
+        <v>34.61</v>
       </c>
       <c r="K21" t="n">
-        <v>59.61</v>
+        <v>70.94</v>
       </c>
       <c r="L21" t="n">
-        <v>66.33</v>
+        <v>78.93000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-18.35</v>
+        <v>-21.74</v>
       </c>
       <c r="K22" t="n">
-        <v>59.67</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>62.43</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-15.55</v>
+        <v>-19.3</v>
       </c>
       <c r="K23" t="n">
-        <v>14.63</v>
+        <v>18.16</v>
       </c>
       <c r="L23" t="n">
-        <v>21.35</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-138.28</v>
+        <v>-151.78</v>
       </c>
       <c r="K24" t="n">
-        <v>18.03</v>
+        <v>19.79</v>
       </c>
       <c r="L24" t="n">
-        <v>139.45</v>
+        <v>153.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-89.75</v>
+        <v>-95.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>127.05</v>
+        <v>134.62</v>
       </c>
       <c r="L25" t="n">
-        <v>155.55</v>
+        <v>164.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>171.01</v>
+        <v>194.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-92.73999999999999</v>
+        <v>-105.27</v>
       </c>
       <c r="L26" t="n">
-        <v>194.54</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-9.59</v>
+        <v>-12.01</v>
       </c>
       <c r="K27" t="n">
-        <v>160.79</v>
+        <v>201.42</v>
       </c>
       <c r="L27" t="n">
-        <v>161.07</v>
+        <v>201.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>95.84</v>
+        <v>119.21</v>
       </c>
       <c r="K28" t="n">
-        <v>151.02</v>
+        <v>187.85</v>
       </c>
       <c r="L28" t="n">
-        <v>178.87</v>
+        <v>222.48</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-52.5</v>
+        <v>-49.98</v>
       </c>
       <c r="K29" t="n">
-        <v>51.13</v>
+        <v>48.68</v>
       </c>
       <c r="L29" t="n">
-        <v>73.28</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.7</v>
+        <v>-11.15</v>
       </c>
       <c r="K30" t="n">
-        <v>75.47</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>76.37</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>49.76</v>
+        <v>51.54</v>
       </c>
       <c r="K31" t="n">
-        <v>17.72</v>
+        <v>18.35</v>
       </c>
       <c r="L31" t="n">
-        <v>52.82</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.91</v>
+        <v>-6.53</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.64</v>
+        <v>-62.59</v>
       </c>
       <c r="L32" t="n">
-        <v>56.95</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-51.18</v>
+        <v>-57.15</v>
       </c>
       <c r="K33" t="n">
-        <v>-21.09</v>
+        <v>-23.55</v>
       </c>
       <c r="L33" t="n">
-        <v>55.35</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-80.19</v>
+        <v>-80.87</v>
       </c>
       <c r="K34" t="n">
-        <v>12.37</v>
+        <v>12.48</v>
       </c>
       <c r="L34" t="n">
-        <v>81.14</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-95.7</v>
+        <v>-102.68</v>
       </c>
       <c r="K35" t="n">
-        <v>53.95</v>
+        <v>57.89</v>
       </c>
       <c r="L35" t="n">
-        <v>109.85</v>
+        <v>117.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>11.74</v>
+        <v>14.13</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.75</v>
+        <v>-20.15</v>
       </c>
       <c r="L36" t="n">
-        <v>20.46</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-81.67</v>
+        <v>-93.38</v>
       </c>
       <c r="K37" t="n">
-        <v>45.71</v>
+        <v>52.27</v>
       </c>
       <c r="L37" t="n">
-        <v>93.59</v>
+        <v>107.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>115.26</v>
+        <v>129.66</v>
       </c>
       <c r="K38" t="n">
-        <v>57.52</v>
+        <v>64.7</v>
       </c>
       <c r="L38" t="n">
-        <v>128.82</v>
+        <v>144.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.23</v>
+        <v>-6.96</v>
       </c>
       <c r="K39" t="n">
-        <v>139.02</v>
+        <v>155.28</v>
       </c>
       <c r="L39" t="n">
-        <v>139.16</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-79.59</v>
+        <v>-91.54000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-149.92</v>
+        <v>-172.42</v>
       </c>
       <c r="L40" t="n">
-        <v>169.74</v>
+        <v>195.22</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>40.37</v>
+        <v>50.6</v>
       </c>
       <c r="K41" t="n">
-        <v>142.02</v>
+        <v>177.97</v>
       </c>
       <c r="L41" t="n">
-        <v>147.64</v>
+        <v>185.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-172.53</v>
+        <v>-201.08</v>
       </c>
       <c r="K42" t="n">
-        <v>-67.69</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>185.34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>86.36</v>
+        <v>107.95</v>
       </c>
       <c r="K43" t="n">
-        <v>111.36</v>
+        <v>139.2</v>
       </c>
       <c r="L43" t="n">
-        <v>140.93</v>
+        <v>176.16</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-32.7</v>
+        <v>-34.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-33.15</v>
+        <v>-35.18</v>
       </c>
       <c r="L44" t="n">
-        <v>46.56</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>42.85</v>
+        <v>43.68</v>
       </c>
       <c r="K45" t="n">
-        <v>-22.08</v>
+        <v>-22.51</v>
       </c>
       <c r="L45" t="n">
-        <v>48.2</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.44</v>
+        <v>-15.23</v>
       </c>
       <c r="K46" t="n">
-        <v>62.44</v>
+        <v>61.6</v>
       </c>
       <c r="L46" t="n">
-        <v>64.31999999999999</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>49.32</v>
+        <v>52.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-37.67</v>
+        <v>-40.36</v>
       </c>
       <c r="L47" t="n">
-        <v>62.06</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>15.83</v>
+        <v>16.66</v>
       </c>
       <c r="K48" t="n">
-        <v>-69.28</v>
+        <v>-72.91</v>
       </c>
       <c r="L48" t="n">
-        <v>71.06999999999999</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-64.56</v>
+        <v>-64.34999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>52.97</v>
+        <v>52.81</v>
       </c>
       <c r="L49" t="n">
-        <v>83.51000000000001</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.62</v>
+        <v>-18.01</v>
       </c>
       <c r="K50" t="n">
-        <v>46.7</v>
+        <v>57.54</v>
       </c>
       <c r="L50" t="n">
-        <v>48.93</v>
+        <v>60.29</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.64</v>
+        <v>-14.14</v>
       </c>
       <c r="K51" t="n">
-        <v>-128.53</v>
+        <v>-133.21</v>
       </c>
       <c r="L51" t="n">
-        <v>129.25</v>
+        <v>133.96</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-85.20999999999999</v>
+        <v>-93.68000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="L52" t="n">
-        <v>85.20999999999999</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>7.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>118.82</v>
+        <v>137.19</v>
       </c>
       <c r="L53" t="n">
-        <v>119.04</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-118.98</v>
+        <v>-133.31</v>
       </c>
       <c r="K54" t="n">
-        <v>-72.03</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>139.09</v>
+        <v>155.84</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-114.87</v>
+        <v>-129.46</v>
       </c>
       <c r="K55" t="n">
-        <v>-41.2</v>
+        <v>-46.43</v>
       </c>
       <c r="L55" t="n">
-        <v>122.03</v>
+        <v>137.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>7.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>256.04</v>
+        <v>285.68</v>
       </c>
       <c r="L56" t="n">
-        <v>256.14</v>
+        <v>285.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>85.01000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>209.6</v>
+        <v>237.07</v>
       </c>
       <c r="L57" t="n">
-        <v>226.19</v>
+        <v>255.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>83.48999999999999</v>
+        <v>91.56</v>
       </c>
       <c r="K58" t="n">
-        <v>242.94</v>
+        <v>266.43</v>
       </c>
       <c r="L58" t="n">
-        <v>256.89</v>
+        <v>281.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>12.28</v>
+        <v>12.01</v>
       </c>
       <c r="K59" t="n">
-        <v>-63.23</v>
+        <v>-61.83</v>
       </c>
       <c r="L59" t="n">
-        <v>64.42</v>
+        <v>62.98</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-24.41</v>
+        <v>-25.56</v>
       </c>
       <c r="K60" t="n">
-        <v>34.24</v>
+        <v>35.85</v>
       </c>
       <c r="L60" t="n">
-        <v>42.05</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>43.22</v>
+        <v>43.96</v>
       </c>
       <c r="K61" t="n">
-        <v>19.12</v>
+        <v>19.45</v>
       </c>
       <c r="L61" t="n">
-        <v>47.27</v>
+        <v>48.07</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.38</v>
+        <v>-55.48</v>
       </c>
       <c r="K62" t="n">
-        <v>-28.89</v>
+        <v>-31.19</v>
       </c>
       <c r="L62" t="n">
-        <v>58.95</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-47.63</v>
+        <v>-50.64</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.44</v>
+        <v>-50.43</v>
       </c>
       <c r="L63" t="n">
-        <v>67.23</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.1</v>
+        <v>-17.11</v>
       </c>
       <c r="K64" t="n">
-        <v>66.97</v>
+        <v>71.2</v>
       </c>
       <c r="L64" t="n">
-        <v>68.88</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>120.13</v>
+        <v>125.06</v>
       </c>
       <c r="K65" t="n">
-        <v>-46.42</v>
+        <v>-48.33</v>
       </c>
       <c r="L65" t="n">
-        <v>128.79</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="K66" t="n">
-        <v>-117.98</v>
+        <v>-126.98</v>
       </c>
       <c r="L66" t="n">
-        <v>118.05</v>
+        <v>127.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>55.75</v>
+        <v>60.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-80.5</v>
+        <v>-87.58</v>
       </c>
       <c r="L67" t="n">
-        <v>97.92</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-57.35</v>
+        <v>-62.56</v>
       </c>
       <c r="K68" t="n">
-        <v>151.44</v>
+        <v>165.19</v>
       </c>
       <c r="L68" t="n">
-        <v>161.93</v>
+        <v>176.64</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>80.58</v>
+        <v>91</v>
       </c>
       <c r="K69" t="n">
-        <v>99.48999999999999</v>
+        <v>112.35</v>
       </c>
       <c r="L69" t="n">
-        <v>128.03</v>
+        <v>144.58</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>33</v>
+        <v>37.65</v>
       </c>
       <c r="K70" t="n">
-        <v>124.54</v>
+        <v>142.08</v>
       </c>
       <c r="L70" t="n">
-        <v>128.84</v>
+        <v>146.99</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-178.64</v>
+        <v>-216.99</v>
       </c>
       <c r="K71" t="n">
-        <v>62.63</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>189.3</v>
+        <v>229.93</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>102.24</v>
+        <v>126.77</v>
       </c>
       <c r="K72" t="n">
-        <v>-130.7</v>
+        <v>-162.04</v>
       </c>
       <c r="L72" t="n">
-        <v>165.94</v>
+        <v>205.73</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>160.92</v>
+        <v>184.2</v>
       </c>
       <c r="K73" t="n">
-        <v>128.89</v>
+        <v>147.54</v>
       </c>
       <c r="L73" t="n">
-        <v>206.18</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-31.38</v>
+        <v>-35.37</v>
       </c>
       <c r="K74" t="n">
-        <v>30.73</v>
+        <v>34.65</v>
       </c>
       <c r="L74" t="n">
-        <v>43.92</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.59</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-45.69</v>
+        <v>-51.23</v>
       </c>
       <c r="L75" t="n">
-        <v>46.49</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>30.81</v>
+        <v>33.01</v>
       </c>
       <c r="K76" t="n">
-        <v>30.83</v>
+        <v>33.03</v>
       </c>
       <c r="L76" t="n">
-        <v>43.58</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>25</v>
       </c>
       <c r="J77" t="n">
-        <v>58.43</v>
+        <v>61.82</v>
       </c>
       <c r="K77" t="n">
-        <v>37.36</v>
+        <v>39.53</v>
       </c>
       <c r="L77" t="n">
-        <v>69.34999999999999</v>
+        <v>73.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>47.83</v>
+        <v>53.43</v>
       </c>
       <c r="K78" t="n">
-        <v>28.94</v>
+        <v>32.33</v>
       </c>
       <c r="L78" t="n">
-        <v>55.9</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-48</v>
+        <v>-53.08</v>
       </c>
       <c r="K79" t="n">
-        <v>-24.34</v>
+        <v>-26.92</v>
       </c>
       <c r="L79" t="n">
-        <v>53.82</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>71.27</v>
+        <v>76.16</v>
       </c>
       <c r="K80" t="n">
-        <v>-82.18000000000001</v>
+        <v>-87.81999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>108.78</v>
+        <v>116.24</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>61.74</v>
+        <v>72.98</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.83</v>
+        <v>-49.45</v>
       </c>
       <c r="L81" t="n">
-        <v>74.56999999999999</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>58.82</v>
+        <v>65.69</v>
       </c>
       <c r="K82" t="n">
-        <v>-76.47</v>
+        <v>-85.40000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>96.48</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>18.06</v>
+        <v>20.32</v>
       </c>
       <c r="K83" t="n">
-        <v>-153.87</v>
+        <v>-173.14</v>
       </c>
       <c r="L83" t="n">
-        <v>154.93</v>
+        <v>174.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-31.94</v>
+        <v>-36.15</v>
       </c>
       <c r="K84" t="n">
-        <v>151.3</v>
+        <v>171.2</v>
       </c>
       <c r="L84" t="n">
-        <v>154.64</v>
+        <v>174.98</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-91.92</v>
+        <v>-102.02</v>
       </c>
       <c r="K85" t="n">
-        <v>97.53</v>
+        <v>108.25</v>
       </c>
       <c r="L85" t="n">
-        <v>134.02</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-149.14</v>
+        <v>-172.76</v>
       </c>
       <c r="K86" t="n">
-        <v>109.23</v>
+        <v>126.53</v>
       </c>
       <c r="L86" t="n">
-        <v>184.86</v>
+        <v>214.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-58.45</v>
+        <v>-66.48</v>
       </c>
       <c r="K87" t="n">
-        <v>190.18</v>
+        <v>216.32</v>
       </c>
       <c r="L87" t="n">
-        <v>198.95</v>
+        <v>226.31</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-90.12</v>
+        <v>-114.45</v>
       </c>
       <c r="K88" t="n">
-        <v>107.05</v>
+        <v>135.95</v>
       </c>
       <c r="L88" t="n">
-        <v>139.94</v>
+        <v>177.71</v>
       </c>
     </row>
   </sheetData>
